--- a/content.xlsx
+++ b/content.xlsx
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3048" uniqueCount="1358">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3122" uniqueCount="1428">
   <si>
     <t>เนื้อหาเกมอโยธยา Idle — แก้ในไฟล์นี้แล้วรัน npm run xlsx:import เพื่อเขียนกลับเป็น data/*.json</t>
   </si>
@@ -58,7 +58,7 @@
     <t>ปรีชาญาณ</t>
   </si>
   <si>
-    <t>เกทอาชีพบริหาร + เพิ่มประสิทธิภาพการฝึกฝน (Study) ทุกด้าน</t>
+    <t>ทำให้การฝึกฝนทุกด้านได้ผลเร็วขึ้น (สูงสุด +30%) · สเตตัสหลักของสายบริหาร รองของสายเกษตรกร</t>
   </si>
   <si>
     <t>พละกำลัง</t>
@@ -67,7 +67,7 @@
     <t>พละวิริยะ</t>
   </si>
   <si>
-    <t>เกทอาชีพเกษตรกร + เพิ่มพลังงานสูงสุด</t>
+    <t>สเตตัสหลักของสายเกษตรกร รองของสายทหาร · ใช้รับมือโรคระบาดและงานหนักในเหตุการณ์</t>
   </si>
   <si>
     <t>ไหวพริบ</t>
@@ -76,7 +76,7 @@
     <t>เชาวน์ปฏิภาณ</t>
   </si>
   <si>
-    <t>เกทอาชีพพ่อค้า + เพิ่มอัตราเงิน/วัน</t>
+    <t>สเตตัสหลักของสายพ่อค้า รองของสายลับ · ต่อรองราคาในร้านค้าได้ถูกลงสูงสุด 25%</t>
   </si>
   <si>
     <t>ต่อสู้</t>
@@ -85,7 +85,7 @@
     <t>พิชัยยุทธ</t>
   </si>
   <si>
-    <t>เกทอาชีพทหาร + เกณฑ์เอนดิ้งที่ 5 ปกป้องกรุงศรี</t>
+    <t>สเตตัสหลักของสายทหาร · ใช้ในศึกสงคราม · เงื่อนไขหลักของเอนดิ้งปกป้องกรุงศรี</t>
   </si>
   <si>
     <t>ไสยเวทย์</t>
@@ -94,7 +94,7 @@
     <t>อาคมศาสตรา</t>
   </si>
   <si>
-    <t>เกทอาชีพปุโรหิต + ลดความเสียหายตอนเหตุการณ์ล้มเหลว (ร่วมกับโภคทรัพย์)</t>
+    <t>สเตตัสหลักของสายปุโรหิต · ใช้รับมือลางบอกเหตุ พิธีกรรม และเรื่องลี้ลับ</t>
   </si>
   <si>
     <t>หลบหลีก</t>
@@ -103,19 +103,19 @@
     <t>จารพรางกาย</t>
   </si>
   <si>
-    <t>เกทอาชีพสายลับ + เกณฑ์เอนดิ้ง หนี</t>
+    <t>สเตตัสหลักของสายลับ · ถ้าเคยฝึกถึง 60% ของเพดาน จะปลดล็อกเอนดิ้ง "หนี"</t>
   </si>
   <si>
     <t>บารมี</t>
   </si>
   <si>
-    <t>ขับเคลื่อนสูตรบุญ (merit) + เพิ่มจุดสมดุลความสำราญ + แปลงเป็นความชอบเล็กน้อยทุกครั้งที่ได้จาก event</t>
+    <t>สเตตัสรองของสายบริหารและปุโรหิต · เพิ่มบุญที่ได้ทุกวัน (สูงสุด 2 เท่า) · เลือกทางที่ได้บารมีแล้วได้ความชอบด้วย</t>
   </si>
   <si>
     <t>โภคทรัพย์</t>
   </si>
   <si>
-    <t>ลดราคาของในร้านค้า (ต่อรอง) + ลดความเสียหายตอนเหตุการณ์ล้มเหลว (ร่วมกับไสยเวทย์) + เร่งรายได้พาสซีฟรายวัน</t>
+    <t>สเตตัสรองของสายพ่อค้า · เพิ่มรายได้ (สูงสุด +50%) · เงื่อนไขของเอนดิ้งปกป้องกรุงศรี</t>
   </si>
   <si>
     <t>แถวสุดท้าย "บรรพชิต" คือสายพิเศษ</t>
@@ -979,186 +979,279 @@
     <t>ราคาเดิม</t>
   </si>
   <si>
+    <t>เรื่องราว</t>
+  </si>
+  <si>
     <t>ย่ามเครื่องปลอมเพศ</t>
   </si>
   <si>
     <t>ย่ามใส่เสื้อผ้าเก่าและบริขารสำหรับปลอมตัวเป็นคนยากหรือพระธุดงค์ลอบสืบข่าว</t>
   </si>
   <si>
+    <t>ย่ามผ้าเก่าซีดที่ข้างในซ่อนจีวรพับ ผ้านุ่งชาวนา และหมวกกุยเล้ย พอสะพายเดินเข้าตลาด ไม่มีใครจำหน้าคนเดิมได้</t>
+  </si>
+  <si>
     <t>นกต่อขานข่าว</t>
   </si>
   <si>
     <t>นกพิราบหรือสัตว์เลี้ยงฝึกสอนพิเศษสำหรับส่งรหัสลับกลับพระนคร</t>
   </si>
   <si>
+    <t>นกพิราบที่เลี้ยงไว้ตั้งแต่ยังไม่ลืมตา จำทางกลับรังได้แม่นกว่าคนนำทาง ผูกใบลานม้วนเล็กไว้ที่ข้อเท้า ข่าวถึงพระนครก่อนม้าเร็ว</t>
+  </si>
+  <si>
     <t>ปืนลมรางเหล็ก</t>
   </si>
   <si>
     <t>อาวุธพกพาเทคโนโลยีต่างชาติ ยิงเงียบไร้ควัน เหมาะสำหรับจารชน</t>
   </si>
   <si>
+    <t>ของแปลกที่พ่อค้าฝรั่งแลกมาด้วยพริกไทยหนึ่งเกวียน ยิงได้ไม่มีควันไม่มีเสียงดินปืน ใช้เฉพาะยามที่เสียงดังแปลว่าตาย</t>
+  </si>
+  <si>
     <t>กล้องส่องทางไกลนวรัตน์</t>
   </si>
   <si>
     <t>"กล้องส่องของไกล" ประดับพลอย ใช้สอดแนมค่ายข้าศึกจากระยะปลอดภัย</t>
   </si>
   <si>
+    <t>ท่อทองเหลืองประดับพลอยเก้าสี ส่องจากยอดไม้เห็นธงค่ายข้าศึกได้ทั้งแถว ผู้ถือได้ชื่อว่ามีตาทิพย์</t>
+  </si>
+  <si>
     <t>ตู้พระสมุดพรางกล</t>
   </si>
   <si>
     <t>ตู้ลายรดน้ำที่มีช่องลับสำหรับเก็บเอกสารคุยรหัสหรือใช้ซ่อนตัวยามฉุกเฉิน</t>
   </si>
   <si>
+    <t>ตู้ลายรดน้ำดูเหมือนเก็บคัมภีร์ แต่กดลายดอกบัวที่มุมล่างจะมีลิ้นชักลับ เก็บหนังสือลับได้ปลอดภัยกว่าหีบใด</t>
+  </si>
+  <si>
     <t>หีบเก็บเบี้ยอากร</t>
   </si>
   <si>
     <t>หีบไม้ลงรักสำหรับเก็บเงินตราและบัญชีรายรับรายวัน</t>
   </si>
   <si>
+    <t>หีบไม้สักลงรักกุญแจทองเหลืองสามดอก ข้างในแบ่งช่องเบี้ย พดด้วง และสมุดจดหนี้ พ่อค้าที่มีหีบนี้ถือว่าตั้งตัวได้แล้ว</t>
+  </si>
+  <si>
     <t>ชุดกาน้ำชาเครื่องถ้วยวิเทศ</t>
   </si>
   <si>
     <t>เครื่องโภชนาหารจากจีนหรือยุโรปสำหรับใช้รับรองแขกเมือง</t>
   </si>
   <si>
+    <t>กาน้ำชาลายครามจากเมืองจีนกับถ้วยเคลือบจากเมืองฝรั่ง ยกออกมารับแขกเมื่อไร การเจรจาก็ราบรื่นขึ้นครึ่งหนึ่ง</t>
+  </si>
+  <si>
     <t>แหวนเพชรลูกแก้ว</t>
   </si>
   <si>
     <t>แหวนประดับพลอยที่มีค่ามหาศาล ใช้เป็นทุนสำรองหรือของกำนัลขุนนาง</t>
   </si>
   <si>
+    <t>แหวนที่ไม่ได้ไว้สวมอวด แต่ไว้ถอดยื่นให้ขุนนางยามต้องการให้เรื่องผ่านเร็ว มูลค่าพอจะซื้อเรือนได้ทั้งหลัง</t>
+  </si>
+  <si>
     <t>ตราภูมิคุ้มห้ามส่วย</t>
   </si>
   <si>
     <t>หนังสือประกาศพระราชทานยกเว้นภาษีอากร ทำให้ค้าขายได้กำไรเต็มเม็ดเต็มหน่วย</t>
   </si>
   <si>
+    <t>หนังสือประทับตราที่บอกว่าสินค้าของผู้ถือไม่ต้องเสียภาษีระหว่างทาง ด่านขนอนทุกแห่งต้องเปิดให้ผ่าน</t>
+  </si>
+  <si>
     <t>สำเภาหลวงจำลองจองถนน</t>
   </si>
   <si>
     <t>เรือสำเภาส่วนตัวที่มีอำนาจการค้าผูกขาดกับต่างประเทศ</t>
   </si>
   <si>
+    <t>สำเภาจำลองฝีมือช่างหลวงที่เป็นทั้งของประดับและสัญญาณว่าเจ้าของมีสิทธิ์ส่งสินค้าไปกับสำเภาหลวงข้ามทะเล</t>
+  </si>
+  <si>
     <t>เคียวเหล็กน้ำพี้</t>
   </si>
   <si>
     <t>อุปกรณ์เก็บเกี่ยวส่วนตัวที่แข็งแกร่งและเป็นมงคล</t>
   </si>
   <si>
+    <t>ตีจากเหล็กน้ำพี้ที่ว่ากันว่าเหนียวที่สุดในแผ่นดิน เกี่ยวข้าวได้วันละหลายไร่โดยไม่ต้องลับใหม่</t>
+  </si>
+  <si>
     <t>กระบือลักษณะเผือก</t>
   </si>
   <si>
     <t>สัตว์แรงงานหายากที่เพิ่มทั้งผลผลิตและบารมีแก่เจ้าของ</t>
   </si>
   <si>
+    <t>ควายเผือกตาสีน้ำผึ้ง คนเฒ่าคนแก่ว่าเป็นมงคล ใครมีไว้ในคอก ข้าวในนาจะไม่เคยแห้งตาย</t>
+  </si>
+  <si>
     <t>ตราชูชั่งข้าวทองคำ</t>
   </si>
   <si>
     <t>เครื่องชั่งตวงข้าวเปลือกที่ได้รับมาตรฐานจากหลวง</t>
   </si>
   <si>
+    <t>ตราชูหลวงที่ผ่านการตรวจเที่ยงจากกรมนา ชาวบ้านยอมขายข้าวให้ผู้ที่มีตราชูนี้เพราะรู้ว่าไม่โกงตาชั่ง</t>
+  </si>
+  <si>
     <t>โฉนดตราแดงที่นาพระกัลปนา</t>
   </si>
   <si>
     <t>เอกสารสิทธิ์ถือครองที่ดินที่ได้รับการยกเว้นภาษีเพื่อบำรุงศาสนา</t>
   </si>
   <si>
+    <t>หนังสือสิทธิ์ที่นาซึ่งถวายบำรุงวัด ผู้ดูแลนาได้ยกเว้นส่วยและได้บุญจากการเลี้ยงพระไปพร้อมกัน</t>
+  </si>
+  <si>
     <t>ระหัดน้ำจำลองถมราชาวดี</t>
   </si>
   <si>
     <t>เครื่องมือกำกับการส่งน้ำในที่นาส่วนตัว สื่อถึงความรอบรู้ในการโยธา</t>
   </si>
   <si>
+    <t>ระหัดวิดน้ำจำลองลงยาประดับ เป็นของพระราชทานแก่ผู้คิดวิธีทดน้ำเข้านาได้ทั่วทุ่ง</t>
+  </si>
+  <si>
     <t>พานทองพระราชทาน</t>
   </si>
   <si>
     <t>พานสำหรับใส่หมากพลู แสดงถึงการได้รับความวางพระทัย</t>
   </si>
   <si>
+    <t>พานหมากทองคำที่ได้รับพระราชทานเป็นเครื่องยศ ตั้งไว้ข้างกายเมื่อไร ผู้มาติดต่อก็รู้ทันทีว่ากำลังพูดกับใคร</t>
+  </si>
+  <si>
     <t>เจียดทองจำหลักสรรพางค์</t>
   </si>
   <si>
     <t>หีบใส่ผ้าทรงหรือของมีค่า ประดับลายไทยอย่างประณีต</t>
   </si>
   <si>
+    <t>หีบใส่ผ้าลายทองจำหลักทั้งใบ ใช้เก็บเสื้อครุยสำหรับเข้าเฝ้า ขุนนางชั้นผู้ใหญ่เท่านั้นที่มีสิทธิ์ใช้</t>
+  </si>
+  <si>
     <t>คานหามทองมยุรฉัตร</t>
   </si>
   <si>
     <t>พาหนะส่วนตัวสำหรับเลียบหน้าที่และตรวจตราพระนคร</t>
   </si>
   <si>
+    <t>คานหามประดับฉัตรขนนกยูง แปดคนหามเดินตรวจราชการรอบพระนคร ชาวบ้านหลีกทางให้ตั้งแต่ยังไม่เห็นหน้า</t>
+  </si>
+  <si>
     <t>พระแสงกั้นหยั่นฝักคำ</t>
   </si>
   <si>
     <t>ดาบสั้นประดับอัญมณี สื่อถึงอำนาจในการตัดสินความเด็ดขาด</t>
   </si>
   <si>
+    <t>ดาบสั้นฝักทองที่บอกว่าผู้ถือมีอำนาจตัดสินความแทนพระองค์ในเขตที่ปกครอง</t>
+  </si>
+  <si>
     <t>ตราสิงห์บัวแก้วอาญาสิทธิ์</t>
   </si>
   <si>
     <t>ตราประจำตัวขุนนางชั้นสูงที่ใช้สั่งการทั่วราชอาณาจักร</t>
   </si>
   <si>
+    <t>ตราประจำตำแหน่งที่ประทับลงหนังสือฉบับใด หนังสือนั้นมีผลบังคับทั่วหัวเมือง</t>
+  </si>
+  <si>
     <t>ลูกประคำนวรัตน์</t>
   </si>
   <si>
     <t>เครื่องรางสำหรับใช้ทำสมาธิและบริกรรมคาถา</t>
   </si>
   <si>
+    <t>ลูกประคำร้อยแปดเม็ดสลับพลอยเก้าสี ใช้นับรอบคาถายามทำสมาธิก่อนประกอบพิธี</t>
+  </si>
+  <si>
     <t>สังข์ทักษิณวัตร</t>
   </si>
   <si>
     <t>สังข์มงคลใช้หลั่งน้ำสิโตทุกในพิธีสาบานหรืออภิเษก</t>
   </si>
   <si>
+    <t>สังข์เวียนขวาที่หาได้ยากยิ่ง ใช้หลั่งน้ำในพิธีถือน้ำพระพิพัฒน์สัตยา</t>
+  </si>
+  <si>
     <t>คัมภีร์ไตรเพทลงชาด</t>
   </si>
   <si>
     <t>ตำราความรู้ทางไสยศาสตร์และโหราศาสตร์ส่วนบุคคล</t>
   </si>
   <si>
+    <t>ตำราพระเวทเขียนด้วยชาดบนใบลาน รวมฤกษ์ยาม การอ่านลางดาว และคาถาที่สืบทอดกันมาหลายชั่วคน</t>
+  </si>
+  <si>
     <t>พระพุทธรูปทองนพคุณห้ามสมุทร</t>
   </si>
   <si>
     <t>พระพุทธรูปบูชาประจำตัวเพื่อสะสมบุญบารมี</t>
   </si>
   <si>
+    <t>พระพุทธรูปปางห้ามสมุทรเนื้อทองบริสุทธิ์ ตั้งบูชาที่หัวนอนเพื่อคุ้มครองผู้ประกอบพิธีจากอาถรรพ์</t>
+  </si>
+  <si>
     <t>ครอบเงินกลีบบัวลงเลขยันต์</t>
   </si>
   <si>
     <t>ภาชนะศักดิ์สิทธิ์สำหรับทำน้ำมนต์หรือประกอบพิธีลบศักราช</t>
   </si>
   <si>
+    <t>ขันครอบเงินจารยันต์รอบกลีบบัว ใช้ทำน้ำมนต์ในพิธีใหญ่ เชื่อกันว่าน้ำในขันนี้ไล่ได้ทั้งโรคและภัย</t>
+  </si>
+  <si>
     <t>ดาบฟ้าฟื้นถักหวาย</t>
   </si>
   <si>
     <t>ดาบลงอาคมที่มีความคมและทนทานเป็นพิเศษ</t>
   </si>
   <si>
+    <t>ดาบเหล็กกล้าด้ามถักหวายกันลื่น ลงอาคมไว้ที่โคนใบ ทหารใหม่ทุกคนฝันอยากได้สักเล่ม</t>
+  </si>
+  <si>
     <t>เกราะหนังแรดลงรัก</t>
   </si>
   <si>
     <t>ชุดป้องกันร่างกายที่เหนียวและเบา สำหรับขุนศึก</t>
   </si>
   <si>
+    <t>เกราะหนังแรดชุบรักหลายชั้นจนแข็งเหมือนไม้ แต่เบาพอให้วิ่งข้ามทุ่งได้ทั้งวัน</t>
+  </si>
+  <si>
     <t>หมวกสุวรรณรัตน์ยอดเงื้อม</t>
   </si>
   <si>
     <t>หมวกแม่ทัพที่มีลักษณะน่าเกรงขามดุจเศียรนาค</t>
   </si>
   <si>
+    <t>หมวกนายกองยอดแหลมประดับทองรูปเศียรนาค ทหารในกองมองหาหมวกใบนี้เป็นจุดรวมพลกลางสนามรบ</t>
+  </si>
+  <si>
     <t>ช้างต้นประจันตมิตร</t>
   </si>
   <si>
     <t>คชาธารส่วนตัวที่ผ่านพิธีคชกรรมและพร้อมทำยุทธหัตถี</t>
   </si>
   <si>
+    <t>ช้างพลายที่ผ่านพิธีคชกรรมแล้ว ไม่ตื่นเสียงปืน ไม่หันหลังให้ข้าศึก พร้อมพาเจ้าของเข้ายุทธหัตถี</t>
+  </si>
+  <si>
     <t>พระแสงดาบใจเพชร</t>
   </si>
   <si>
     <t>ดาบพระราชทานอาญาสิทธิ์ สื่อถึงการมีอำนาจบัญชาการทหารสูงสุด</t>
   </si>
   <si>
+    <t>ดาบพระราชทานที่ผู้ถือมีสิทธิ์บัญชาทัพแทนพระองค์ ทหารทั้งกองต้องฟังคำสั่งผู้ถือดาบเล่มนี้</t>
+  </si>
+  <si>
     <t>ราคาเดิม = ราคาใน v0.19 (บาท)</t>
   </si>
   <si>
@@ -1168,72 +1261,108 @@
     <t>อ้างอิงจากขุนนางที่เข้าเฝ้ากษัตริย์โดยนั่งหรือหมอบบนเสื่อหยาบ ๆ</t>
   </si>
   <si>
+    <t>เสื่อกกผืนเดียวปูนอนที่ศาลาริมทาง ไม่มีหลังคาของตัวเอง แต่ก็ดีกว่านอนบนดินเปล่า</t>
+  </si>
+  <si>
     <t>เพิงพักบนต้นไม้</t>
   </si>
   <si>
     <t>ที่พักชั่วคราวของนักบวชหรือผู้ปลีกวิเวกในป่าลึกเพื่อหนีอันตรายจากสัตว์ป่า</t>
   </si>
   <si>
+    <t>เพิงไม้ไผ่บนง่ามต้นไม้ใหญ่ หลบน้ำหลากและสัตว์ป่าได้ คืนที่ลมแรงต้องกอดเสาไว้ทั้งคืน</t>
+  </si>
+  <si>
     <t>กระท่อมไม้ไผ่ริมคลอง</t>
   </si>
   <si>
     <t>บ้านเรือนระดับพื้นฐานของชาวบ้านทั่วไปที่ปลูกสร้างเป็นกลุ่มตามแนวลำน้ำ</t>
   </si>
   <si>
+    <t>กระท่อมฝาขัดแตะหลังคามุงจาก ยกพื้นเหนือน้ำ มีที่ให้นั่งฝึกวิชายามเย็นโดยไม่มีใครรบกวน</t>
+  </si>
+  <si>
     <t>เรือนไทยเครื่องสับ</t>
   </si>
   <si>
     <t>เรือนไม้มาตรฐานที่จัดเป็นระเบียบตามแปลงที่ดินสี่เหลี่ยมในตัวเมือง</t>
   </si>
   <si>
+    <t>เรือนไม้สักฝาปะกน ใต้ถุนสูงโล่ง มีห้องหับเป็นสัดส่วน ฝึกวิชาและพักผ่อนได้เต็มที่</t>
+  </si>
+  <si>
     <t>ตึกดินก่ออิฐถือปูน</t>
   </si>
   <si>
     <t>อาคารแบบตะวันตกที่มักเป็นที่อยู่อาศัยของชาวต่างชาติหรือขุนนางผู้มีอำนาจ</t>
   </si>
   <si>
+    <t>ตึกแบบฝรั่งผนังหนาเย็นตลอดปี ปลอดภัยจากไฟไหม้ คนมีฐานะเท่านั้นที่สร้างได้</t>
+  </si>
+  <si>
     <t>จวนขุนนางรั้วขอบชิด</t>
   </si>
   <si>
     <t>บ้านพักขนาดใหญ่ในเขตวังที่แบ่งพื้นที่ไว้อย่างเป็นสัดส่วน</t>
   </si>
   <si>
+    <t>จวนหลายหลังล้อมกำแพง มีเรือนนอน เรือนรับแขก และหอสวดมนต์ ชีวิตในจวนมีเวลาให้ใฝ่รู้ทุกเรื่อง</t>
+  </si>
+  <si>
     <t>ไพร่ส่วย</t>
   </si>
   <si>
     <t>ผู้ที่จ่ายผลผลิตหรือภาษีแทนการเข้าเวรแรงงาน</t>
   </si>
   <si>
+    <t>ไพร่ที่ส่งของป่ามาแทนการเข้าเวร ทำให้มีรายได้งอกเงยโดยไม่ต้องลงแรงเอง</t>
+  </si>
+  <si>
     <t>ทาสในเรือนเบี้ย</t>
   </si>
   <si>
     <t>บริวารที่รับใช้ใกล้ชิดในบ้านเรือน</t>
   </si>
   <si>
+    <t>คนที่ขายตัวใช้หนี้มาอยู่ในเรือน ช่วยงานบ้านงานไร่จนกว่าจะไถ่ตัวได้</t>
+  </si>
+  <si>
     <t>ไพร่สม</t>
   </si>
   <si>
     <t>กำลังคนที่สังกัดอยู่กับมูลนายหรือขุนนางโดยตรง</t>
   </si>
   <si>
+    <t>ไพร่ที่ขึ้นสังกัดกับท่านโดยตรง ทำงานให้ท่านแลกกับการคุ้มครอง</t>
+  </si>
+  <si>
     <t>ทนายหน้าหอ / ทนายเลือก</t>
   </si>
   <si>
     <t>บริวารฝีมือดีที่ทำหน้าที่รับส่งคำสั่งและเป็นองครักษ์</t>
   </si>
   <si>
+    <t>คนสนิทที่คัดเลือกมาอย่างดี ทั้งรับส่งหนังสือ เป็นตาเป็นหู และเป็นองครักษ์ยามคับขัน</t>
+  </si>
+  <si>
     <t>ไพร่หลวงทแกล้วทหาร</t>
   </si>
   <si>
     <t>กำลังพลหลักที่ขึ้นตรงต่อพระมหากษัตริย์เพื่อการป้องกันพระนคร</t>
   </si>
   <si>
+    <t>กำลังพลฝีมือดีที่ถูกส่งมาอยู่ใต้บังคับบัญชา เพิ่มทั้งกำลังงานและหน้าตาของเจ้านาย</t>
+  </si>
+  <si>
     <t>กองอาสาต่างชาติ</t>
   </si>
   <si>
     <t>หน่วยรบพิเศษที่มีความชำนาญเฉพาะทาง เช่น อาสาญี่ปุ่น, ฝรั่งเศส หรือโปรตุเกส</t>
   </si>
   <si>
+    <t>กองอาสาชาวญี่ปุ่นและโปรตุเกสที่รับจ้างคุ้มกันกองเกวียนสินค้า มีปืนไฟและความชำนาญที่ไพร่ทั่วไปไม่มี</t>
+  </si>
+  <si>
     <t>ผล</t>
   </si>
   <si>
@@ -1246,30 +1375,45 @@
     <t>เพิ่มค่าบุญญาธิการระดับต่ำ เหมาะสำหรับกดใช้เพื่อรับโบนัสเล็กน้อยในแต่ละวัน</t>
   </si>
   <si>
+    <t>ข้าวสวย แกง และผลไม้ใส่สำรับไม้ ตื่นแต่เช้าใส่บาตรพระที่เดินผ่านหน้าบ้าน บุญเล็กๆ ที่ทำได้ทุกวัน</t>
+  </si>
+  <si>
     <t>เครื่องไทยทานทักษิณา (Thaksina Offering Set)</t>
   </si>
   <si>
     <t>เพิ่มค่าบุญญาธิการระดับกลาง และเพิ่มค่า "บารมี" ชั่วคราว</t>
   </si>
   <si>
+    <t>ชุดเครื่องไทยทานใส่ถาดเงิน ถวายพระในวันพระใหญ่ อุทิศส่วนกุศลให้บรรพบุรุษ</t>
+  </si>
+  <si>
     <t>สำรับข้าวยาคูมธุปายาส (Sacred Rice Gruel)</t>
   </si>
   <si>
     <t>เพิ่มค่าบุญญาธิการ และช่วยฟื้นฟูค่า "พละวิริยะ" (Energy/Stamina)</t>
   </si>
   <si>
+    <t>ข้าวยาคูกวนน้ำผึ้งนมสดในพิธีสารท ใช้เวลากวนทั้งคืน ผู้ร่วมกวนได้บุญทุกคน</t>
+  </si>
+  <si>
     <t>ลูกมะนาวกัลปพฤกษ์ (Kalpapruksha Fruit)</t>
   </si>
   <si>
     <t>เพิ่มค่าบุญญาธิการ และเพิ่มโอกาสในการได้รับ "เบี้ยอากร" หรือไอเทมสุ่มจากการทำทาน</t>
   </si>
   <si>
+    <t>ลูกมะนาวทำจากขี้ผึ้งบรรจุเงินพดด้วง โปรยทานในงานบุญใหญ่ให้ผู้ยากไร้แย่งเก็บ</t>
+  </si>
+  <si>
     <t>เครื่องไทยทานสัตดกมหาทาน (The Grand Sevenfold Gift)</t>
   </si>
   <si>
     <t>เพิ่มค่าบุญญาธิการระดับสูงสุดในครั้งเดียว (Rare/Expensive Item) ช่วยล้างค่าสถานะลบหรือลดโอกาสเกิดเหตุร้าย (อาเพศ) ในเกม</t>
   </si>
   <si>
+    <t>มหาทานเจ็ดอย่าง ทั้งช้าง ม้า รถ ทาส ผ้า อาหาร และเงินทอง ทำได้ครั้งหนึ่งในชีวิตก็ถือเป็นมหากุศล</t>
+  </si>
+  <si>
     <t>ค่าเดิม = ค่าใน v0.19</t>
   </si>
   <si>
@@ -1288,130 +1432,196 @@
     <t>ผ้าชิ้นบางเรียบง่ายที่ชาวบ้านใช้เคียนรอบศีรษะยามเดินทางไกล นำมาประยุกต์ปิดบังใบหน้าในความมืดได้</t>
   </si>
   <si>
+    <t>ผ้าฝ้ายสีหม่นผืนเล็ก โพกหัวปิดหน้ายามเดินกลางคืน ในความมืดแทบมองไม่เห็นว่าเป็นคน</t>
+  </si>
+  <si>
     <t>หลอดไม้ซางสอดแนม</t>
   </si>
   <si>
     <t>หลอดไม้ซางยาวน้ำหนักเบาที่ตัดจากไผ่ในป่า เครื่องมือหาอาหารและระวังภัยยามซุ่มซ่อนตัว</t>
   </si>
   <si>
+    <t>ไม้ซางยาวกลวง เป่าลูกดอกล่านกก็ได้ ซุ่มฟังเสียงคนคุยหลังฝาก็ได้</t>
+  </si>
+  <si>
     <t>ผงถ่านขัดตัว</t>
   </si>
   <si>
     <t>ผงถ่านธรรมดาที่ได้จากการเผากิ่งไม้ ใช้ผสมน้ำมันยางชโลมผิวเพื่อพรางตัวในความมืดของค่ายอพยพ</t>
   </si>
   <si>
+    <t>ถ่านป่นผสมน้ำมันยาง ทาตัวแล้วกลืนไปกับเงาไม้ยามค่ำ</t>
+  </si>
+  <si>
     <t>ผ้าขาวม้าลายพรางฝีมือดี</t>
   </si>
   <si>
     <t>ของฝากผูกมิตรกับผู้คุมด่าน/เพื่อนบ้านยามหลบซ่อนร่วมกัน ทอลายเฉพาะที่คนในวงในเท่านั้นจะรู้จัก</t>
   </si>
   <si>
+    <t>ผ้าขาวม้าทอลายตาหมากรุกสีดินสีใบไม้ คาดเอวก็ได้ คลุมหัวก็ได้ ยามจำเป็นใช้พรางตัวในพงหญ้า</t>
+  </si>
+  <si>
     <t>ห่อเมี่ยงหมากดิบ</t>
   </si>
   <si>
     <t>หมากพลูธรรมดาที่ห่อในผ้าเช็ดหน้าผืนเล็ก ของพกติดตัวสำหรับเจรจาผูกมิตรกับผู้คนตามย่านตลาด</t>
   </si>
   <si>
+    <t>หมากพลูห่อผ้าเช็ดหน้า ยื่นให้คนแปลกหน้าคำหนึ่ง แล้วบทสนทนาก็เริ่มขึ้นเอง</t>
+  </si>
+  <si>
     <t>เบี้ยหอยจักจั่น</t>
   </si>
   <si>
     <t>เบี้ยหอยย่อยทั่วไปที่ใช้ทอนเงินในตลาดนัด ยิ่งพกสะสมไว้มากยิ่งช่วยให้การจับจ่ายลื่นไหล</t>
   </si>
   <si>
+    <t>เบี้ยหอยเม็ดเล็กร้อยเป็นพวง ใช้ทอนเงินในตลาด ใครพกไว้มากก็ต่อรองได้คล่อง</t>
+  </si>
+  <si>
     <t>ก้อนดีบุกแลกเปลี่ยน</t>
   </si>
   <si>
     <t>แร่ดีบุกหลอมเป็นก้อนขนาดเล็กที่ยังไม่ได้ตีตรา สื่อกลางแลกเปลี่ยนข้าวของทั่วไปในยามยาก</t>
   </si>
   <si>
+    <t>ดีบุกหลอมเป็นก้อนยังไม่ตีตรา ยามเงินตราขาดแคลนก็ใช้แลกข้าวของแทนได้</t>
+  </si>
+  <si>
     <t>หมวกใบคาถัก</t>
   </si>
   <si>
     <t>หมวกสานธรรมดาทำจากหญ้าคาหรือฟางข้าว อุปกรณ์กันแดดฝนของไพร่ยามเกณฑ์แรงงานโยธาหลวง</t>
   </si>
   <si>
+    <t>หมวกสานจากใบคา กันแดดกันฝนยามถูกเกณฑ์ไปทำงานโยธาทั้งวัน</t>
+  </si>
+  <si>
     <t>เกลือแกงบรรจุไห</t>
   </si>
   <si>
     <t>เกลือสมุทรสีขาวที่ได้จากการตากน้ำเค็ม ใช้สะสมเพื่อปรุงรสถนอมเสบียงแห้งบำรุงกำลังไพร่</t>
   </si>
   <si>
+    <t>เกลือสมุทรใส่ไหดินเผา ถนอมปลาถนอมเนื้อไว้กินได้ทั้งฤดูแล้ง</t>
+  </si>
+  <si>
     <t>จอบเหล็กสยาม</t>
   </si>
   <si>
     <t>จอบเหล็กขุดดินรูปทรงมาตรฐาน ทรัพย์สินติดครัวเรือนที่ทุ่นแรงยามบุกเบิกนาป่า</t>
   </si>
   <si>
+    <t>จอบเหล็กด้ามไม้มะขาม ขุดดินแข็งได้ไม่บิ่น เครื่องมือคู่กายของคนบุกเบิกนา</t>
+  </si>
+  <si>
     <t>ข้าวเหนียวมูลห่อใบตอง</t>
   </si>
   <si>
     <t>ของฝากแบ่งปันกันยามลงแขกออกแรงร่วมกัน สร้างความคุ้นเคยในหมู่คนทำงานหนัก</t>
   </si>
   <si>
+    <t>ข้าวเหนียวมูลหอมกะทิห่อใบตอง แจกเพื่อนบ้านในวันงาน คนรับยิ้มทุกคน</t>
+  </si>
+  <si>
     <t>ก้อนขี้ผึ้งเหลืองดิบ</t>
   </si>
   <si>
     <t>ขี้ผึ้งแท้ที่รวบรวมไว้สำหรับฟั่นเทียนเหลืองใช้อ่านตำรากฎหมายและพงศาวดารยามค่ำคืน</t>
   </si>
   <si>
+    <t>ขี้ผึ้งแท้สำหรับฟั่นเทียน จุดอ่านตำรายามค่ำได้หลายคืน</t>
+  </si>
+  <si>
     <t>หินฝนหมึกจีน</t>
   </si>
   <si>
     <t>แผ่นหินดินดานเรียบง่ายสำหรับฝนหมึกสีดำ อุปกรณ์พื้นฐานในการหัดคัดเขียนหนังสือใบลาน</t>
   </si>
   <si>
+    <t>แผ่นหินเรียบสำหรับฝนหมึก ใช้หัดเขียนอักษรลงสมุดข่อย</t>
+  </si>
+  <si>
     <t>ผงครามวานิช</t>
   </si>
   <si>
     <t>ครามธรรมชาติที่ใช้ย้อมผ้าหรือใช้ผสมน้ำหมึก เป็นสัญลักษณ์ของความประณีตและการบันทึก</t>
   </si>
   <si>
+    <t>ครามป่นใช้ผสมหมึกหรือย้อมผ้า สีครามเข้มเป็นสีของคนที่ใส่ใจบันทึก</t>
+  </si>
+  <si>
     <t>สมุดข่อยจดบันทึกเปล่า</t>
   </si>
   <si>
     <t>ของกำนัลให้ครูบาอาจารย์/อาลักษณ์ แลกกับความไว้เนื้อเชื่อใจและโอกาสได้เรียนรู้เพิ่ม</t>
   </si>
   <si>
+    <t>สมุดข่อยพับไปมาหลายสิบหน้า จดเรื่องที่ได้ยินได้เห็นไว้ ไม่ต้องพึ่งความจำอย่างเดียว</t>
+  </si>
+  <si>
     <t>ดอกจำปาแห้งบูชา</t>
   </si>
   <si>
     <t>ดอกไม้สดที่เก็บจากต้นมาผึ่งลมจนแห้ง ของสามัญที่ชาวบ้านใช้จัดพานเครื่องบูชาผีเหย้าผีเรือน</t>
   </si>
   <si>
+    <t>ดอกจำปาตากแห้งจัดใส่พาน ถวายศาลผีบ้านผีเรือน เพื่อนบ้านเห็นก็นับถือว่าเป็นคนรู้ธรรมเนียม</t>
+  </si>
+  <si>
     <t>น้ำหวานก้านปาล์ม</t>
   </si>
   <si>
     <t>น้ำหวานที่คั้นจากลำต้นปาล์มป่า ใช้ตั้งเครื่องบวงสรวงเทพารักษ์ประจำบึงน้ำตามคติชาวบ้าน</t>
   </si>
   <si>
+    <t>น้ำหวานจากงวงตาล ตั้งบวงสรวงเทพารักษ์ประจำบึงน้ำ</t>
+  </si>
+  <si>
     <t>ปลาแห้งคลุกเกลือ</t>
   </si>
   <si>
     <t>ปลาเค็มตากแห้งธรรมดาที่ใช้เป็นเครื่องเซ่นไหว้สะเดาะเคราะห์ เพื่อลบล้างลางร้าย</t>
   </si>
   <si>
+    <t>ปลาเค็มตากแดดใช้เซ่นไหว้สะเดาะเคราะห์ ชาวบ้านเชื่อว่าช่วยแก้ลางร้าย</t>
+  </si>
+  <si>
     <t>หลาวไม้ไผ่เหลาแหลม</t>
   </si>
   <si>
     <t>ไม้ไผ่ตัดท่อนเหลาปลายให้คมกริบ อาวุธพื้นฐานที่สุดที่ใช้ฝึกปรือพละกำลังและการแทงฟัน</t>
   </si>
   <si>
+    <t>ไม้ไผ่ท่อนเดียวเหลาปลายคม อาวุธแรกของเด็กหนุ่มที่หัดแทงหุ่นฟาง</t>
+  </si>
+  <si>
     <t>โล่ไม้ระกากรุหนัง</t>
   </si>
   <si>
     <t>โล่ป้องกันตัวที่ทำจากแผ่นไม้แก่นเนื้อเบา ใช้สำหรับป้องกันตัวยามเริ่มหัดวิชาอาวุธ</t>
   </si>
   <si>
+    <t>โล่ไม้เนื้อเบากรุหนังวัว ใช้หัดรับดาบในลานฝึก</t>
+  </si>
+  <si>
     <t>ถุงดินประสิวดิบ</t>
   </si>
   <si>
     <t>ดินประสิวจากถ้ำหินปูนที่ราษฎรรวบรวมบรรจุถุง วัตถุดิบพื้นฐานสำหรับการทำดินปืนคาบชุด</t>
   </si>
   <si>
+    <t>ดินประสิวขูดจากผนังถ้ำ เป็นวัตถุดิบดินปืนที่กองทัพต้องการเสมอ</t>
+  </si>
+  <si>
     <t>ดาบไม้เล่นของฝากลูกหลานทหาร</t>
   </si>
   <si>
     <t>ของกำนัลผูกไมตรีกับครอบครัวนักรบ/หัวหน้ากองซ้อม แกะเป็นดาบไม้เล็กๆ ให้เด็กในบ้านเล่น</t>
+  </si>
+  <si>
+    <t>ดาบไม้แกะลายสวย ฝากลูกหลานบ้านทหาร พ่อแม่เขาจำน้ำใจท่านไว้</t>
   </si>
   <si>
     <t>ช่วงปีของแต่ละชาติคิดจากตารางนี้</t>
@@ -4533,28 +4743,30 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F24"/>
+  <dimension ref="A1:G24"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="2" width="10" style="1" customWidth="1"/>
     <col min="3" max="4" width="12" style="1" customWidth="1"/>
     <col min="5" max="5" width="14" style="1" customWidth="1"/>
     <col min="6" max="6" width="15" style="1" customWidth="1"/>
+    <col min="7" max="7" width="13" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>414</v>
+        <v>462</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
       <c r="D1" s="3"/>
       <c r="E1" s="3"/>
       <c r="F1" s="3"/>
-    </row>
-    <row r="2" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="G1" s="3"/>
+    </row>
+    <row r="2" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
-        <v>415</v>
+        <v>463</v>
       </c>
       <c r="B2" s="5" t="s">
         <v>291</v>
@@ -4566,21 +4778,24 @@
         <v>316</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>416</v>
+        <v>464</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>417</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+        <v>465</v>
+      </c>
+      <c r="G2" s="5" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>23</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>418</v>
+        <v>466</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>419</v>
+        <v>467</v>
       </c>
       <c r="D3" s="1">
         <v>0.009</v>
@@ -4591,16 +4806,19 @@
       <c r="F3" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G3" s="1" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>23</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>420</v>
+        <v>469</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>421</v>
+        <v>470</v>
       </c>
       <c r="D4" s="1">
         <v>0.018</v>
@@ -4611,16 +4829,19 @@
       <c r="F4" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G4" s="1" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>23</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>422</v>
+        <v>472</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>423</v>
+        <v>473</v>
       </c>
       <c r="D5" s="1">
         <v>0.033</v>
@@ -4631,16 +4852,19 @@
       <c r="F5" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G5" s="1" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>23</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>424</v>
+        <v>475</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>425</v>
+        <v>476</v>
       </c>
       <c r="D6" s="1">
         <v>0.02</v>
@@ -4651,16 +4875,19 @@
       <c r="F6" s="1">
         <v>0.02</v>
       </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G6" s="1" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>14</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>426</v>
+        <v>478</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>427</v>
+        <v>479</v>
       </c>
       <c r="D7" s="1">
         <v>0.009</v>
@@ -4671,16 +4898,19 @@
       <c r="F7" s="1">
         <v>0.01</v>
       </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G7" s="1" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>14</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>428</v>
+        <v>481</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>429</v>
+        <v>482</v>
       </c>
       <c r="D8" s="1">
         <v>0.018</v>
@@ -4691,16 +4921,19 @@
       <c r="F8" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G8" s="1" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>14</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>430</v>
+        <v>484</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>431</v>
+        <v>485</v>
       </c>
       <c r="D9" s="1">
         <v>0.033</v>
@@ -4711,16 +4944,19 @@
       <c r="F9" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G9" s="1" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>11</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>432</v>
+        <v>487</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>433</v>
+        <v>488</v>
       </c>
       <c r="D10" s="1">
         <v>0.009</v>
@@ -4731,16 +4967,19 @@
       <c r="F10" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G10" s="1" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>11</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>434</v>
+        <v>490</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>435</v>
+        <v>491</v>
       </c>
       <c r="D11" s="1">
         <v>0.018</v>
@@ -4751,16 +4990,19 @@
       <c r="F11" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G11" s="1" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>436</v>
+        <v>493</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>437</v>
+        <v>494</v>
       </c>
       <c r="D12" s="1">
         <v>0.033</v>
@@ -4771,16 +5013,19 @@
       <c r="F12" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G12" s="1" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>11</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>438</v>
+        <v>496</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>439</v>
+        <v>497</v>
       </c>
       <c r="D13" s="1">
         <v>0.02</v>
@@ -4791,16 +5036,19 @@
       <c r="F13" s="1">
         <v>0.02</v>
       </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G13" s="1" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>8</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>440</v>
+        <v>499</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>441</v>
+        <v>500</v>
       </c>
       <c r="D14" s="1">
         <v>0.009</v>
@@ -4811,16 +5059,19 @@
       <c r="F14" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G14" s="1" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>8</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>442</v>
+        <v>502</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>443</v>
+        <v>503</v>
       </c>
       <c r="D15" s="1">
         <v>0.018</v>
@@ -4831,16 +5082,19 @@
       <c r="F15" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G15" s="1" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>8</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>444</v>
+        <v>505</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>445</v>
+        <v>506</v>
       </c>
       <c r="D16" s="1">
         <v>0.033</v>
@@ -4851,16 +5105,19 @@
       <c r="F16" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G16" s="1" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>8</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>446</v>
+        <v>508</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>447</v>
+        <v>509</v>
       </c>
       <c r="D17" s="1">
         <v>0.02</v>
@@ -4871,16 +5128,19 @@
       <c r="F17" s="1">
         <v>0.02</v>
       </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G17" s="1" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>20</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>448</v>
+        <v>511</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>449</v>
+        <v>512</v>
       </c>
       <c r="D18" s="1">
         <v>0.009</v>
@@ -4891,16 +5151,19 @@
       <c r="F18" s="1">
         <v>0.01</v>
       </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G18" s="1" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>20</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>450</v>
+        <v>514</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>451</v>
+        <v>515</v>
       </c>
       <c r="D19" s="1">
         <v>0.018</v>
@@ -4911,16 +5174,19 @@
       <c r="F19" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G19" s="1" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>20</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>452</v>
+        <v>517</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>453</v>
+        <v>518</v>
       </c>
       <c r="D20" s="1">
         <v>0.033</v>
@@ -4931,16 +5197,19 @@
       <c r="F20" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G20" s="1" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>17</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>454</v>
+        <v>520</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>455</v>
+        <v>521</v>
       </c>
       <c r="D21" s="1">
         <v>0.009</v>
@@ -4951,16 +5220,19 @@
       <c r="F21" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G21" s="1" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>456</v>
+        <v>523</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>457</v>
+        <v>524</v>
       </c>
       <c r="D22" s="1">
         <v>0.018</v>
@@ -4971,16 +5243,19 @@
       <c r="F22" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G22" s="1" t="s">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
         <v>17</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>458</v>
+        <v>526</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>459</v>
+        <v>527</v>
       </c>
       <c r="D23" s="1">
         <v>0.033</v>
@@ -4991,16 +5266,19 @@
       <c r="F23" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G23" s="1" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
         <v>17</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>460</v>
+        <v>529</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>461</v>
+        <v>530</v>
       </c>
       <c r="D24" s="1">
         <v>0.02</v>
@@ -5010,6 +5288,9 @@
       </c>
       <c r="F24" s="1">
         <v>0.02</v>
+      </c>
+      <c r="G24" s="1" t="s">
+        <v>531</v>
       </c>
     </row>
   </sheetData>
@@ -5032,7 +5313,7 @@
   <sheetData>
     <row r="1" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>462</v>
+        <v>532</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
@@ -5041,19 +5322,19 @@
     </row>
     <row r="2" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
-        <v>463</v>
+        <v>533</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>464</v>
+        <v>534</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>465</v>
+        <v>535</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>466</v>
+        <v>536</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>467</v>
+        <v>537</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
@@ -5067,10 +5348,10 @@
         <v>1911</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>468</v>
+        <v>538</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>469</v>
+        <v>539</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
@@ -5084,10 +5365,10 @@
         <v>1912</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>470</v>
+        <v>540</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>471</v>
+        <v>541</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
@@ -5101,10 +5382,10 @@
         <v>1930</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>472</v>
+        <v>542</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>473</v>
+        <v>543</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
@@ -5118,10 +5399,10 @@
         <v>1931</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>474</v>
+        <v>544</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>475</v>
+        <v>545</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
@@ -5135,10 +5416,10 @@
         <v>1937</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>476</v>
+        <v>546</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>477</v>
+        <v>547</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
@@ -5152,10 +5433,10 @@
         <v>1938</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>478</v>
+        <v>548</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>479</v>
+        <v>549</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
@@ -5169,10 +5450,10 @@
         <v>1948</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>480</v>
+        <v>550</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>481</v>
+        <v>551</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
@@ -5186,10 +5467,10 @@
         <v>1951</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>482</v>
+        <v>552</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>483</v>
+        <v>553</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
@@ -5203,10 +5484,10 @@
         <v>1966</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>484</v>
+        <v>554</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>485</v>
+        <v>555</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
@@ -5220,10 +5501,10 @@
         <v>1990</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>486</v>
+        <v>556</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>487</v>
+        <v>557</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
@@ -5237,10 +5518,10 @@
         <v>2010</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>488</v>
+        <v>558</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>489</v>
+        <v>559</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
@@ -5254,10 +5535,10 @@
         <v>2031</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>490</v>
+        <v>560</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>491</v>
+        <v>561</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
@@ -5271,10 +5552,10 @@
         <v>2033</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>492</v>
+        <v>562</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>493</v>
+        <v>563</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
@@ -5288,10 +5569,10 @@
         <v>2072</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>494</v>
+        <v>564</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>495</v>
+        <v>565</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
@@ -5305,10 +5586,10 @@
         <v>2076</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>496</v>
+        <v>566</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>497</v>
+        <v>567</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
@@ -5322,10 +5603,10 @@
         <v>2088</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>498</v>
+        <v>568</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>499</v>
+        <v>569</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
@@ -5339,10 +5620,10 @@
         <v>2091</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>500</v>
+        <v>570</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>501</v>
+        <v>571</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
@@ -5356,10 +5637,10 @@
         <v>2110</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>502</v>
+        <v>572</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>503</v>
+        <v>573</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
@@ -5373,10 +5654,10 @@
         <v>2112</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>504</v>
+        <v>574</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>505</v>
+        <v>575</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
@@ -5390,10 +5671,10 @@
         <v>2132</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>506</v>
+        <v>576</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>507</v>
+        <v>577</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
@@ -5407,10 +5688,10 @@
         <v>2134</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>508</v>
+        <v>578</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>509</v>
+        <v>579</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
@@ -5424,10 +5705,10 @@
         <v>2147</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>508</v>
+        <v>578</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>510</v>
+        <v>580</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
@@ -5441,10 +5722,10 @@
         <v>2152</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>511</v>
+        <v>581</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>512</v>
+        <v>582</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
@@ -5458,10 +5739,10 @@
         <v>2154</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>513</v>
+        <v>583</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>514</v>
+        <v>584</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
@@ -5475,10 +5756,10 @@
         <v>2169</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>515</v>
+        <v>585</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>516</v>
+        <v>586</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
@@ -5492,10 +5773,10 @@
         <v>2172</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>517</v>
+        <v>587</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>518</v>
+        <v>588</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
@@ -5509,10 +5790,10 @@
         <v>2196</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>519</v>
+        <v>589</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>520</v>
+        <v>590</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
@@ -5526,10 +5807,10 @@
         <v>2198</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>521</v>
+        <v>591</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>522</v>
+        <v>592</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
@@ -5543,10 +5824,10 @@
         <v>2199</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>523</v>
+        <v>593</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>524</v>
+        <v>594</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
@@ -5560,10 +5841,10 @@
         <v>2230</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>525</v>
+        <v>595</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>526</v>
+        <v>596</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
@@ -5577,10 +5858,10 @@
         <v>2240</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>527</v>
+        <v>597</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>528</v>
+        <v>598</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
@@ -5594,10 +5875,10 @@
         <v>2250</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>529</v>
+        <v>599</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>530</v>
+        <v>600</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
@@ -5611,10 +5892,10 @@
         <v>2258</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>531</v>
+        <v>601</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>532</v>
+        <v>602</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
@@ -5628,10 +5909,10 @@
         <v>2274</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>531</v>
+        <v>601</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>533</v>
+        <v>603</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
@@ -5645,10 +5926,10 @@
         <v>2300</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>534</v>
+        <v>604</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>535</v>
+        <v>605</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
@@ -5662,10 +5943,10 @@
         <v>2301</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>536</v>
+        <v>606</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>537</v>
+        <v>607</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
@@ -5679,10 +5960,10 @@
         <v>2310</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>538</v>
+        <v>608</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>539</v>
+        <v>609</v>
       </c>
     </row>
   </sheetData>
@@ -5709,7 +5990,7 @@
   <sheetData>
     <row r="1" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>540</v>
+        <v>610</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
@@ -5726,48 +6007,48 @@
     </row>
     <row r="2" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
-        <v>541</v>
+        <v>611</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>463</v>
+        <v>533</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>542</v>
+        <v>612</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>543</v>
+        <v>613</v>
       </c>
       <c r="E2" s="5" t="s">
         <v>291</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>544</v>
+        <v>614</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>545</v>
+        <v>615</v>
       </c>
       <c r="H2" s="5" t="s">
-        <v>546</v>
+        <v>616</v>
       </c>
       <c r="I2" s="5" t="s">
-        <v>547</v>
+        <v>617</v>
       </c>
       <c r="J2" s="5" t="s">
-        <v>548</v>
+        <v>618</v>
       </c>
       <c r="K2" s="5" t="s">
-        <v>549</v>
+        <v>619</v>
       </c>
       <c r="L2" s="5" t="s">
-        <v>550</v>
+        <v>620</v>
       </c>
       <c r="M2" s="5" t="s">
-        <v>551</v>
+        <v>621</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>552</v>
+        <v>622</v>
       </c>
       <c r="B3" s="1">
         <v>1</v>
@@ -5779,25 +6060,25 @@
         <v>1887</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>553</v>
+        <v>623</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>554</v>
+        <v>624</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>555</v>
+        <v>625</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>556</v>
+        <v>626</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>557</v>
+        <v>627</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>558</v>
+        <v>628</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>559</v>
+        <v>629</v>
       </c>
       <c r="L3" s="1" t="s">
         <v>48</v>
@@ -5808,7 +6089,7 @@
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>560</v>
+        <v>630</v>
       </c>
       <c r="B4" s="1">
         <v>1</v>
@@ -5820,25 +6101,25 @@
         <v>1888</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>561</v>
+        <v>631</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>562</v>
+        <v>632</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>563</v>
+        <v>633</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>564</v>
+        <v>634</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>565</v>
+        <v>635</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>566</v>
+        <v>636</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>567</v>
+        <v>637</v>
       </c>
       <c r="L4" s="1" t="s">
         <v>48</v>
@@ -5849,7 +6130,7 @@
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>568</v>
+        <v>638</v>
       </c>
       <c r="B5" s="1">
         <v>1</v>
@@ -5861,25 +6142,25 @@
         <v>1889</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>569</v>
+        <v>639</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>570</v>
+        <v>640</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>571</v>
+        <v>641</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>572</v>
+        <v>642</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>557</v>
+        <v>627</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>573</v>
+        <v>643</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>574</v>
+        <v>644</v>
       </c>
       <c r="L5" s="1" t="s">
         <v>48</v>
@@ -5890,7 +6171,7 @@
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>575</v>
+        <v>645</v>
       </c>
       <c r="B6" s="1">
         <v>1</v>
@@ -5902,25 +6183,25 @@
         <v>1891</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>576</v>
+        <v>646</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>577</v>
+        <v>647</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>559</v>
+        <v>629</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>578</v>
+        <v>648</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>563</v>
+        <v>633</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>579</v>
+        <v>649</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>580</v>
+        <v>650</v>
       </c>
       <c r="L6" s="1" t="s">
         <v>48</v>
@@ -5931,7 +6212,7 @@
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>581</v>
+        <v>651</v>
       </c>
       <c r="B7" s="1">
         <v>1</v>
@@ -5943,25 +6224,25 @@
         <v>1892</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>582</v>
+        <v>652</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>583</v>
+        <v>653</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>584</v>
+        <v>654</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>585</v>
+        <v>655</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>557</v>
+        <v>627</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>586</v>
+        <v>656</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>587</v>
+        <v>657</v>
       </c>
       <c r="L7" s="1" t="s">
         <v>48</v>
@@ -5972,7 +6253,7 @@
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>588</v>
+        <v>658</v>
       </c>
       <c r="B8" s="1">
         <v>1</v>
@@ -5984,25 +6265,25 @@
         <v>1894</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>589</v>
+        <v>659</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>590</v>
+        <v>660</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>555</v>
+        <v>625</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>591</v>
+        <v>661</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>592</v>
+        <v>662</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>593</v>
+        <v>663</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>594</v>
+        <v>664</v>
       </c>
       <c r="L8" s="1" t="s">
         <v>48</v>
@@ -6013,7 +6294,7 @@
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>595</v>
+        <v>665</v>
       </c>
       <c r="B9" s="1">
         <v>1</v>
@@ -6025,25 +6306,25 @@
         <v>1895</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>596</v>
+        <v>666</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>597</v>
+        <v>667</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>598</v>
+        <v>668</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>599</v>
+        <v>669</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>559</v>
+        <v>629</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>600</v>
+        <v>670</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>601</v>
+        <v>671</v>
       </c>
       <c r="L9" s="1" t="s">
         <v>48</v>
@@ -6054,7 +6335,7 @@
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>602</v>
+        <v>672</v>
       </c>
       <c r="B10" s="1">
         <v>2</v>
@@ -6066,25 +6347,25 @@
         <v>1949</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>603</v>
+        <v>673</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>604</v>
+        <v>674</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>557</v>
+        <v>627</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>605</v>
+        <v>675</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>559</v>
+        <v>629</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>606</v>
+        <v>676</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>563</v>
+        <v>633</v>
       </c>
       <c r="L10" s="1" t="s">
         <v>48</v>
@@ -6095,7 +6376,7 @@
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>607</v>
+        <v>677</v>
       </c>
       <c r="B11" s="1">
         <v>2</v>
@@ -6107,25 +6388,25 @@
         <v>1950</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>608</v>
+        <v>678</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>609</v>
+        <v>679</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>559</v>
+        <v>629</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>610</v>
+        <v>680</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>563</v>
+        <v>633</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>611</v>
+        <v>681</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>567</v>
+        <v>637</v>
       </c>
       <c r="L11" s="1" t="s">
         <v>48</v>
@@ -6136,7 +6417,7 @@
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>612</v>
+        <v>682</v>
       </c>
       <c r="B12" s="1">
         <v>2</v>
@@ -6148,25 +6429,25 @@
         <v>1951</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>613</v>
+        <v>683</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>614</v>
+        <v>684</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>615</v>
+        <v>685</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>616</v>
+        <v>686</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>565</v>
+        <v>635</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>617</v>
+        <v>687</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>587</v>
+        <v>657</v>
       </c>
       <c r="L12" s="1" t="s">
         <v>48</v>
@@ -6177,7 +6458,7 @@
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>618</v>
+        <v>688</v>
       </c>
       <c r="B13" s="1">
         <v>2</v>
@@ -6189,25 +6470,25 @@
         <v>1953</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>619</v>
+        <v>689</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>620</v>
+        <v>690</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>598</v>
+        <v>668</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>621</v>
+        <v>691</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>555</v>
+        <v>625</v>
       </c>
       <c r="J13" s="1" t="s">
-        <v>622</v>
+        <v>692</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>601</v>
+        <v>671</v>
       </c>
       <c r="L13" s="1" t="s">
         <v>48</v>
@@ -6218,7 +6499,7 @@
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>623</v>
+        <v>693</v>
       </c>
       <c r="B14" s="1">
         <v>2</v>
@@ -6230,25 +6511,25 @@
         <v>1954</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>624</v>
+        <v>694</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>625</v>
+        <v>695</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>592</v>
+        <v>662</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>626</v>
+        <v>696</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>627</v>
+        <v>697</v>
       </c>
       <c r="J14" s="1" t="s">
-        <v>628</v>
+        <v>698</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>629</v>
+        <v>699</v>
       </c>
       <c r="L14" s="1" t="s">
         <v>48</v>
@@ -6259,7 +6540,7 @@
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>630</v>
+        <v>700</v>
       </c>
       <c r="B15" s="1">
         <v>2</v>
@@ -6271,25 +6552,25 @@
         <v>1956</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>631</v>
+        <v>701</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>632</v>
+        <v>702</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>633</v>
+        <v>703</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>634</v>
+        <v>704</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>559</v>
+        <v>629</v>
       </c>
       <c r="J15" s="1" t="s">
-        <v>635</v>
+        <v>705</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>601</v>
+        <v>671</v>
       </c>
       <c r="L15" s="1" t="s">
         <v>48</v>
@@ -6300,7 +6581,7 @@
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>636</v>
+        <v>706</v>
       </c>
       <c r="B16" s="1">
         <v>2</v>
@@ -6312,25 +6593,25 @@
         <v>1957</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>637</v>
+        <v>707</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>638</v>
+        <v>708</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>557</v>
+        <v>627</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>639</v>
+        <v>709</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>563</v>
+        <v>633</v>
       </c>
       <c r="J16" s="1" t="s">
-        <v>640</v>
+        <v>710</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>641</v>
+        <v>711</v>
       </c>
       <c r="L16" s="1" t="s">
         <v>48</v>
@@ -6341,7 +6622,7 @@
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>642</v>
+        <v>712</v>
       </c>
       <c r="B17" s="1">
         <v>3</v>
@@ -6353,25 +6634,25 @@
         <v>2011</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>643</v>
+        <v>713</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>644</v>
+        <v>714</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>645</v>
+        <v>715</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>646</v>
+        <v>716</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>555</v>
+        <v>625</v>
       </c>
       <c r="J17" s="1" t="s">
-        <v>647</v>
+        <v>717</v>
       </c>
       <c r="K17" s="1" t="s">
-        <v>559</v>
+        <v>629</v>
       </c>
       <c r="L17" s="1" t="s">
         <v>48</v>
@@ -6382,7 +6663,7 @@
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>648</v>
+        <v>718</v>
       </c>
       <c r="B18" s="1">
         <v>3</v>
@@ -6394,25 +6675,25 @@
         <v>2012</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>649</v>
+        <v>719</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>650</v>
+        <v>720</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>567</v>
+        <v>637</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>651</v>
+        <v>721</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>563</v>
+        <v>633</v>
       </c>
       <c r="J18" s="1" t="s">
-        <v>652</v>
+        <v>722</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>653</v>
+        <v>723</v>
       </c>
       <c r="L18" s="1" t="s">
         <v>48</v>
@@ -6423,7 +6704,7 @@
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>654</v>
+        <v>724</v>
       </c>
       <c r="B19" s="1">
         <v>3</v>
@@ -6435,25 +6716,25 @@
         <v>2013</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>655</v>
+        <v>725</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>656</v>
+        <v>726</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>645</v>
+        <v>715</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>657</v>
+        <v>727</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>557</v>
+        <v>627</v>
       </c>
       <c r="J19" s="1" t="s">
-        <v>658</v>
+        <v>728</v>
       </c>
       <c r="K19" s="1" t="s">
-        <v>567</v>
+        <v>637</v>
       </c>
       <c r="L19" s="1" t="s">
         <v>48</v>
@@ -6464,7 +6745,7 @@
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>659</v>
+        <v>729</v>
       </c>
       <c r="B20" s="1">
         <v>3</v>
@@ -6476,25 +6757,25 @@
         <v>2015</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>660</v>
+        <v>730</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>661</v>
+        <v>731</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>559</v>
+        <v>629</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>662</v>
+        <v>732</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>601</v>
+        <v>671</v>
       </c>
       <c r="J20" s="1" t="s">
-        <v>663</v>
+        <v>733</v>
       </c>
       <c r="K20" s="1" t="s">
-        <v>555</v>
+        <v>625</v>
       </c>
       <c r="L20" s="1" t="s">
         <v>48</v>
@@ -6505,7 +6786,7 @@
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>664</v>
+        <v>734</v>
       </c>
       <c r="B21" s="1">
         <v>3</v>
@@ -6517,25 +6798,25 @@
         <v>2016</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>665</v>
+        <v>735</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>666</v>
+        <v>736</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>559</v>
+        <v>629</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>667</v>
+        <v>737</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>645</v>
+        <v>715</v>
       </c>
       <c r="J21" s="1" t="s">
-        <v>668</v>
+        <v>738</v>
       </c>
       <c r="K21" s="1" t="s">
-        <v>565</v>
+        <v>635</v>
       </c>
       <c r="L21" s="1" t="s">
         <v>48</v>
@@ -6546,7 +6827,7 @@
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>669</v>
+        <v>739</v>
       </c>
       <c r="B22" s="1">
         <v>3</v>
@@ -6558,25 +6839,25 @@
         <v>2018</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>670</v>
+        <v>740</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>671</v>
+        <v>741</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>598</v>
+        <v>668</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>672</v>
+        <v>742</v>
       </c>
       <c r="I22" s="1" t="s">
-        <v>559</v>
+        <v>629</v>
       </c>
       <c r="J22" s="1" t="s">
-        <v>673</v>
+        <v>743</v>
       </c>
       <c r="K22" s="1" t="s">
-        <v>557</v>
+        <v>627</v>
       </c>
       <c r="L22" s="1" t="s">
         <v>48</v>
@@ -6587,7 +6868,7 @@
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>674</v>
+        <v>744</v>
       </c>
       <c r="B23" s="1">
         <v>3</v>
@@ -6599,25 +6880,25 @@
         <v>2019</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>675</v>
+        <v>745</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>676</v>
+        <v>746</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>677</v>
+        <v>747</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>678</v>
+        <v>748</v>
       </c>
       <c r="I23" s="1" t="s">
-        <v>559</v>
+        <v>629</v>
       </c>
       <c r="J23" s="1" t="s">
-        <v>679</v>
+        <v>749</v>
       </c>
       <c r="K23" s="1" t="s">
-        <v>680</v>
+        <v>750</v>
       </c>
       <c r="L23" s="1" t="s">
         <v>48</v>
@@ -6628,7 +6909,7 @@
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>681</v>
+        <v>751</v>
       </c>
       <c r="B24" s="1">
         <v>4</v>
@@ -6640,25 +6921,25 @@
         <v>2073</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>682</v>
+        <v>752</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>683</v>
+        <v>753</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>559</v>
+        <v>629</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>684</v>
+        <v>754</v>
       </c>
       <c r="I24" s="1" t="s">
-        <v>601</v>
+        <v>671</v>
       </c>
       <c r="J24" s="1" t="s">
-        <v>685</v>
+        <v>755</v>
       </c>
       <c r="K24" s="1" t="s">
-        <v>555</v>
+        <v>625</v>
       </c>
       <c r="L24" s="1" t="s">
         <v>48</v>
@@ -6669,7 +6950,7 @@
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>686</v>
+        <v>756</v>
       </c>
       <c r="B25" s="1">
         <v>4</v>
@@ -6681,25 +6962,25 @@
         <v>2074</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>687</v>
+        <v>757</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>688</v>
+        <v>758</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>567</v>
+        <v>637</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>689</v>
+        <v>759</v>
       </c>
       <c r="I25" s="1" t="s">
-        <v>557</v>
+        <v>627</v>
       </c>
       <c r="J25" s="1" t="s">
-        <v>690</v>
+        <v>760</v>
       </c>
       <c r="K25" s="1" t="s">
-        <v>563</v>
+        <v>633</v>
       </c>
       <c r="L25" s="1" t="s">
         <v>48</v>
@@ -6710,7 +6991,7 @@
     </row>
     <row r="26" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>691</v>
+        <v>761</v>
       </c>
       <c r="B26" s="1">
         <v>4</v>
@@ -6722,25 +7003,25 @@
         <v>2075</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>692</v>
+        <v>762</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>693</v>
+        <v>763</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>557</v>
+        <v>627</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>694</v>
+        <v>764</v>
       </c>
       <c r="I26" s="1" t="s">
-        <v>559</v>
+        <v>629</v>
       </c>
       <c r="J26" s="1" t="s">
-        <v>695</v>
+        <v>765</v>
       </c>
       <c r="K26" s="1" t="s">
-        <v>587</v>
+        <v>657</v>
       </c>
       <c r="L26" s="1" t="s">
         <v>48</v>
@@ -6751,7 +7032,7 @@
     </row>
     <row r="27" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>696</v>
+        <v>766</v>
       </c>
       <c r="B27" s="1">
         <v>4</v>
@@ -6763,25 +7044,25 @@
         <v>2077</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>697</v>
+        <v>767</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>698</v>
+        <v>768</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>592</v>
+        <v>662</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>699</v>
+        <v>769</v>
       </c>
       <c r="I27" s="1" t="s">
-        <v>559</v>
+        <v>629</v>
       </c>
       <c r="J27" s="1" t="s">
-        <v>700</v>
+        <v>770</v>
       </c>
       <c r="K27" s="1" t="s">
-        <v>555</v>
+        <v>625</v>
       </c>
       <c r="L27" s="1" t="s">
         <v>48</v>
@@ -6792,7 +7073,7 @@
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>701</v>
+        <v>771</v>
       </c>
       <c r="B28" s="1">
         <v>4</v>
@@ -6804,25 +7085,25 @@
         <v>2078</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>702</v>
+        <v>772</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>703</v>
+        <v>773</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>584</v>
+        <v>654</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>704</v>
+        <v>774</v>
       </c>
       <c r="I28" s="1" t="s">
-        <v>627</v>
+        <v>697</v>
       </c>
       <c r="J28" s="1" t="s">
-        <v>705</v>
+        <v>775</v>
       </c>
       <c r="K28" s="1" t="s">
-        <v>565</v>
+        <v>635</v>
       </c>
       <c r="L28" s="1" t="s">
         <v>48</v>
@@ -6833,7 +7114,7 @@
     </row>
     <row r="29" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>706</v>
+        <v>776</v>
       </c>
       <c r="B29" s="1">
         <v>4</v>
@@ -6845,25 +7126,25 @@
         <v>2080</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>707</v>
+        <v>777</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>708</v>
+        <v>778</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>555</v>
+        <v>625</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>709</v>
+        <v>779</v>
       </c>
       <c r="I29" s="1" t="s">
-        <v>645</v>
+        <v>715</v>
       </c>
       <c r="J29" s="1" t="s">
-        <v>710</v>
+        <v>780</v>
       </c>
       <c r="K29" s="1" t="s">
-        <v>567</v>
+        <v>637</v>
       </c>
       <c r="L29" s="1" t="s">
         <v>48</v>
@@ -6874,7 +7155,7 @@
     </row>
     <row r="30" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>711</v>
+        <v>781</v>
       </c>
       <c r="B30" s="1">
         <v>4</v>
@@ -6886,25 +7167,25 @@
         <v>2081</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>712</v>
+        <v>782</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>713</v>
+        <v>783</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>714</v>
+        <v>784</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>715</v>
+        <v>785</v>
       </c>
       <c r="I30" s="1" t="s">
-        <v>557</v>
+        <v>627</v>
       </c>
       <c r="J30" s="1" t="s">
-        <v>716</v>
+        <v>786</v>
       </c>
       <c r="K30" s="1" t="s">
-        <v>717</v>
+        <v>787</v>
       </c>
       <c r="L30" s="1" t="s">
         <v>48</v>
@@ -6915,7 +7196,7 @@
     </row>
     <row r="31" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>718</v>
+        <v>788</v>
       </c>
       <c r="B31" s="1">
         <v>5</v>
@@ -6927,25 +7208,25 @@
         <v>2135</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>719</v>
+        <v>789</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>720</v>
+        <v>790</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>598</v>
+        <v>668</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>721</v>
+        <v>791</v>
       </c>
       <c r="I31" s="1" t="s">
-        <v>645</v>
+        <v>715</v>
       </c>
       <c r="J31" s="1" t="s">
-        <v>722</v>
+        <v>792</v>
       </c>
       <c r="K31" s="1" t="s">
-        <v>559</v>
+        <v>629</v>
       </c>
       <c r="L31" s="1" t="s">
         <v>48</v>
@@ -6956,7 +7237,7 @@
     </row>
     <row r="32" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>723</v>
+        <v>793</v>
       </c>
       <c r="B32" s="1">
         <v>5</v>
@@ -6968,25 +7249,25 @@
         <v>2136</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>724</v>
+        <v>794</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>725</v>
+        <v>795</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>567</v>
+        <v>637</v>
       </c>
       <c r="H32" s="1" t="s">
-        <v>726</v>
+        <v>796</v>
       </c>
       <c r="I32" s="1" t="s">
-        <v>645</v>
+        <v>715</v>
       </c>
       <c r="J32" s="1" t="s">
-        <v>727</v>
+        <v>797</v>
       </c>
       <c r="K32" s="1" t="s">
-        <v>563</v>
+        <v>633</v>
       </c>
       <c r="L32" s="1" t="s">
         <v>48</v>
@@ -6997,7 +7278,7 @@
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>728</v>
+        <v>798</v>
       </c>
       <c r="B33" s="1">
         <v>5</v>
@@ -7009,25 +7290,25 @@
         <v>2137</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>729</v>
+        <v>799</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>730</v>
+        <v>800</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>563</v>
+        <v>633</v>
       </c>
       <c r="H33" s="1" t="s">
-        <v>731</v>
+        <v>801</v>
       </c>
       <c r="I33" s="1" t="s">
-        <v>559</v>
+        <v>629</v>
       </c>
       <c r="J33" s="1" t="s">
-        <v>732</v>
+        <v>802</v>
       </c>
       <c r="K33" s="1" t="s">
-        <v>555</v>
+        <v>625</v>
       </c>
       <c r="L33" s="1" t="s">
         <v>48</v>
@@ -7038,7 +7319,7 @@
     </row>
     <row r="34" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>733</v>
+        <v>803</v>
       </c>
       <c r="B34" s="1">
         <v>5</v>
@@ -7050,25 +7331,25 @@
         <v>2139</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>734</v>
+        <v>804</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>735</v>
+        <v>805</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>559</v>
+        <v>629</v>
       </c>
       <c r="H34" s="1" t="s">
-        <v>736</v>
+        <v>806</v>
       </c>
       <c r="I34" s="1" t="s">
-        <v>555</v>
+        <v>625</v>
       </c>
       <c r="J34" s="1" t="s">
-        <v>737</v>
+        <v>807</v>
       </c>
       <c r="K34" s="1" t="s">
-        <v>567</v>
+        <v>637</v>
       </c>
       <c r="L34" s="1" t="s">
         <v>48</v>
@@ -7079,7 +7360,7 @@
     </row>
     <row r="35" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>738</v>
+        <v>808</v>
       </c>
       <c r="B35" s="1">
         <v>5</v>
@@ -7091,25 +7372,25 @@
         <v>2140</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>739</v>
+        <v>809</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>740</v>
+        <v>810</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>584</v>
+        <v>654</v>
       </c>
       <c r="H35" s="1" t="s">
-        <v>741</v>
+        <v>811</v>
       </c>
       <c r="I35" s="1" t="s">
-        <v>645</v>
+        <v>715</v>
       </c>
       <c r="J35" s="1" t="s">
-        <v>742</v>
+        <v>812</v>
       </c>
       <c r="K35" s="1" t="s">
-        <v>565</v>
+        <v>635</v>
       </c>
       <c r="L35" s="1" t="s">
         <v>48</v>
@@ -7120,7 +7401,7 @@
     </row>
     <row r="36" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>743</v>
+        <v>813</v>
       </c>
       <c r="B36" s="1">
         <v>5</v>
@@ -7132,25 +7413,25 @@
         <v>2142</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>744</v>
+        <v>814</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>745</v>
+        <v>815</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>563</v>
+        <v>633</v>
       </c>
       <c r="H36" s="1" t="s">
-        <v>746</v>
+        <v>816</v>
       </c>
       <c r="I36" s="1" t="s">
-        <v>559</v>
+        <v>629</v>
       </c>
       <c r="J36" s="1" t="s">
-        <v>747</v>
+        <v>817</v>
       </c>
       <c r="K36" s="1" t="s">
-        <v>565</v>
+        <v>635</v>
       </c>
       <c r="L36" s="1" t="s">
         <v>48</v>
@@ -7161,7 +7442,7 @@
     </row>
     <row r="37" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>748</v>
+        <v>818</v>
       </c>
       <c r="B37" s="1">
         <v>5</v>
@@ -7173,25 +7454,25 @@
         <v>2143</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>749</v>
+        <v>819</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>750</v>
+        <v>820</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>598</v>
+        <v>668</v>
       </c>
       <c r="H37" s="1" t="s">
-        <v>751</v>
+        <v>821</v>
       </c>
       <c r="I37" s="1" t="s">
-        <v>559</v>
+        <v>629</v>
       </c>
       <c r="J37" s="1" t="s">
-        <v>752</v>
+        <v>822</v>
       </c>
       <c r="K37" s="1" t="s">
-        <v>557</v>
+        <v>627</v>
       </c>
       <c r="L37" s="1" t="s">
         <v>48</v>
@@ -7202,7 +7483,7 @@
     </row>
     <row r="38" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>753</v>
+        <v>823</v>
       </c>
       <c r="B38" s="1">
         <v>6</v>
@@ -7214,25 +7495,25 @@
         <v>2197</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>754</v>
+        <v>824</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>755</v>
+        <v>825</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>559</v>
+        <v>629</v>
       </c>
       <c r="H38" s="1" t="s">
-        <v>756</v>
+        <v>826</v>
       </c>
       <c r="I38" s="1" t="s">
-        <v>563</v>
+        <v>633</v>
       </c>
       <c r="J38" s="1" t="s">
-        <v>757</v>
+        <v>827</v>
       </c>
       <c r="K38" s="1" t="s">
-        <v>557</v>
+        <v>627</v>
       </c>
       <c r="L38" s="1" t="s">
         <v>48</v>
@@ -7243,7 +7524,7 @@
     </row>
     <row r="39" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
-        <v>758</v>
+        <v>828</v>
       </c>
       <c r="B39" s="1">
         <v>6</v>
@@ -7255,25 +7536,25 @@
         <v>2198</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>759</v>
+        <v>829</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>760</v>
+        <v>830</v>
       </c>
       <c r="G39" s="1" t="s">
-        <v>557</v>
+        <v>627</v>
       </c>
       <c r="H39" s="1" t="s">
-        <v>727</v>
+        <v>797</v>
       </c>
       <c r="I39" s="1" t="s">
-        <v>563</v>
+        <v>633</v>
       </c>
       <c r="J39" s="1" t="s">
-        <v>761</v>
+        <v>831</v>
       </c>
       <c r="K39" s="1" t="s">
-        <v>567</v>
+        <v>637</v>
       </c>
       <c r="L39" s="1" t="s">
         <v>48</v>
@@ -7284,7 +7565,7 @@
     </row>
     <row r="40" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
-        <v>762</v>
+        <v>832</v>
       </c>
       <c r="B40" s="1">
         <v>6</v>
@@ -7296,25 +7577,25 @@
         <v>2199</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>763</v>
+        <v>833</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>764</v>
+        <v>834</v>
       </c>
       <c r="G40" s="1" t="s">
-        <v>592</v>
+        <v>662</v>
       </c>
       <c r="H40" s="1" t="s">
-        <v>765</v>
+        <v>835</v>
       </c>
       <c r="I40" s="1" t="s">
-        <v>766</v>
+        <v>836</v>
       </c>
       <c r="J40" s="1" t="s">
-        <v>767</v>
+        <v>837</v>
       </c>
       <c r="K40" s="1" t="s">
-        <v>563</v>
+        <v>633</v>
       </c>
       <c r="L40" s="1" t="s">
         <v>48</v>
@@ -7325,7 +7606,7 @@
     </row>
     <row r="41" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
-        <v>768</v>
+        <v>838</v>
       </c>
       <c r="B41" s="1">
         <v>6</v>
@@ -7337,25 +7618,25 @@
         <v>2201</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>769</v>
+        <v>839</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>770</v>
+        <v>840</v>
       </c>
       <c r="G41" s="1" t="s">
-        <v>771</v>
+        <v>841</v>
       </c>
       <c r="H41" s="1" t="s">
-        <v>772</v>
+        <v>842</v>
       </c>
       <c r="I41" s="1" t="s">
-        <v>559</v>
+        <v>629</v>
       </c>
       <c r="J41" s="1" t="s">
-        <v>773</v>
+        <v>843</v>
       </c>
       <c r="K41" s="1" t="s">
-        <v>563</v>
+        <v>633</v>
       </c>
       <c r="L41" s="1" t="s">
         <v>48</v>
@@ -7366,7 +7647,7 @@
     </row>
     <row r="42" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
-        <v>774</v>
+        <v>844</v>
       </c>
       <c r="B42" s="1">
         <v>6</v>
@@ -7378,25 +7659,25 @@
         <v>2202</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>775</v>
+        <v>845</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>776</v>
+        <v>846</v>
       </c>
       <c r="G42" s="1" t="s">
-        <v>557</v>
+        <v>627</v>
       </c>
       <c r="H42" s="1" t="s">
-        <v>777</v>
+        <v>847</v>
       </c>
       <c r="I42" s="1" t="s">
-        <v>717</v>
+        <v>787</v>
       </c>
       <c r="J42" s="1" t="s">
-        <v>778</v>
+        <v>848</v>
       </c>
       <c r="K42" s="1" t="s">
-        <v>779</v>
+        <v>849</v>
       </c>
       <c r="L42" s="1" t="s">
         <v>48</v>
@@ -7407,7 +7688,7 @@
     </row>
     <row r="43" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
-        <v>780</v>
+        <v>850</v>
       </c>
       <c r="B43" s="1">
         <v>6</v>
@@ -7419,25 +7700,25 @@
         <v>2204</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>781</v>
+        <v>851</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>782</v>
+        <v>852</v>
       </c>
       <c r="G43" s="1" t="s">
-        <v>645</v>
+        <v>715</v>
       </c>
       <c r="H43" s="1" t="s">
-        <v>783</v>
+        <v>853</v>
       </c>
       <c r="I43" s="1" t="s">
-        <v>559</v>
+        <v>629</v>
       </c>
       <c r="J43" s="1" t="s">
-        <v>784</v>
+        <v>854</v>
       </c>
       <c r="K43" s="1" t="s">
-        <v>565</v>
+        <v>635</v>
       </c>
       <c r="L43" s="1" t="s">
         <v>48</v>
@@ -7448,7 +7729,7 @@
     </row>
     <row r="44" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
-        <v>785</v>
+        <v>855</v>
       </c>
       <c r="B44" s="1">
         <v>6</v>
@@ -7460,25 +7741,25 @@
         <v>2205</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>786</v>
+        <v>856</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>787</v>
+        <v>857</v>
       </c>
       <c r="G44" s="1" t="s">
-        <v>584</v>
+        <v>654</v>
       </c>
       <c r="H44" s="1" t="s">
-        <v>788</v>
+        <v>858</v>
       </c>
       <c r="I44" s="1" t="s">
-        <v>789</v>
+        <v>859</v>
       </c>
       <c r="J44" s="1" t="s">
-        <v>790</v>
+        <v>860</v>
       </c>
       <c r="K44" s="1" t="s">
-        <v>557</v>
+        <v>627</v>
       </c>
       <c r="L44" s="1" t="s">
         <v>48</v>
@@ -7489,7 +7770,7 @@
     </row>
     <row r="45" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
-        <v>791</v>
+        <v>861</v>
       </c>
       <c r="B45" s="1">
         <v>7</v>
@@ -7501,25 +7782,25 @@
         <v>2259</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>792</v>
+        <v>862</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>793</v>
+        <v>863</v>
       </c>
       <c r="G45" s="1" t="s">
-        <v>567</v>
+        <v>637</v>
       </c>
       <c r="H45" s="1" t="s">
-        <v>794</v>
+        <v>864</v>
       </c>
       <c r="I45" s="1" t="s">
-        <v>559</v>
+        <v>629</v>
       </c>
       <c r="J45" s="1" t="s">
-        <v>795</v>
+        <v>865</v>
       </c>
       <c r="K45" s="1" t="s">
-        <v>563</v>
+        <v>633</v>
       </c>
       <c r="L45" s="1" t="s">
         <v>48</v>
@@ -7530,7 +7811,7 @@
     </row>
     <row r="46" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
-        <v>796</v>
+        <v>866</v>
       </c>
       <c r="B46" s="1">
         <v>7</v>
@@ -7542,25 +7823,25 @@
         <v>2260</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>797</v>
+        <v>867</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>798</v>
+        <v>868</v>
       </c>
       <c r="G46" s="1" t="s">
-        <v>555</v>
+        <v>625</v>
       </c>
       <c r="H46" s="1" t="s">
-        <v>799</v>
+        <v>869</v>
       </c>
       <c r="I46" s="1" t="s">
-        <v>559</v>
+        <v>629</v>
       </c>
       <c r="J46" s="1" t="s">
-        <v>800</v>
+        <v>870</v>
       </c>
       <c r="K46" s="1" t="s">
-        <v>563</v>
+        <v>633</v>
       </c>
       <c r="L46" s="1" t="s">
         <v>48</v>
@@ -7571,7 +7852,7 @@
     </row>
     <row r="47" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
-        <v>801</v>
+        <v>871</v>
       </c>
       <c r="B47" s="1">
         <v>7</v>
@@ -7583,25 +7864,25 @@
         <v>2261</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>802</v>
+        <v>872</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>803</v>
+        <v>873</v>
       </c>
       <c r="G47" s="1" t="s">
-        <v>559</v>
+        <v>629</v>
       </c>
       <c r="H47" s="1" t="s">
-        <v>804</v>
+        <v>874</v>
       </c>
       <c r="I47" s="1" t="s">
-        <v>567</v>
+        <v>637</v>
       </c>
       <c r="J47" s="1" t="s">
-        <v>805</v>
+        <v>875</v>
       </c>
       <c r="K47" s="1" t="s">
-        <v>598</v>
+        <v>668</v>
       </c>
       <c r="L47" s="1" t="s">
         <v>48</v>
@@ -7612,7 +7893,7 @@
     </row>
     <row r="48" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
-        <v>806</v>
+        <v>876</v>
       </c>
       <c r="B48" s="1">
         <v>7</v>
@@ -7624,25 +7905,25 @@
         <v>2263</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>807</v>
+        <v>877</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>808</v>
+        <v>878</v>
       </c>
       <c r="G48" s="1" t="s">
-        <v>645</v>
+        <v>715</v>
       </c>
       <c r="H48" s="1" t="s">
-        <v>809</v>
+        <v>879</v>
       </c>
       <c r="I48" s="1" t="s">
-        <v>555</v>
+        <v>625</v>
       </c>
       <c r="J48" s="1" t="s">
-        <v>810</v>
+        <v>880</v>
       </c>
       <c r="K48" s="1" t="s">
-        <v>557</v>
+        <v>627</v>
       </c>
       <c r="L48" s="1" t="s">
         <v>48</v>
@@ -7653,7 +7934,7 @@
     </row>
     <row r="49" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
-        <v>811</v>
+        <v>881</v>
       </c>
       <c r="B49" s="1">
         <v>7</v>
@@ -7665,25 +7946,25 @@
         <v>2264</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>812</v>
+        <v>882</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>813</v>
+        <v>883</v>
       </c>
       <c r="G49" s="1" t="s">
-        <v>559</v>
+        <v>629</v>
       </c>
       <c r="H49" s="1" t="s">
-        <v>814</v>
+        <v>884</v>
       </c>
       <c r="I49" s="1" t="s">
-        <v>565</v>
+        <v>635</v>
       </c>
       <c r="J49" s="1" t="s">
-        <v>815</v>
+        <v>885</v>
       </c>
       <c r="K49" s="1" t="s">
-        <v>555</v>
+        <v>625</v>
       </c>
       <c r="L49" s="1" t="s">
         <v>48</v>
@@ -7694,7 +7975,7 @@
     </row>
     <row r="50" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
-        <v>816</v>
+        <v>886</v>
       </c>
       <c r="B50" s="1">
         <v>7</v>
@@ -7706,25 +7987,25 @@
         <v>2266</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>817</v>
+        <v>887</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>818</v>
+        <v>888</v>
       </c>
       <c r="G50" s="1" t="s">
-        <v>559</v>
+        <v>629</v>
       </c>
       <c r="H50" s="1" t="s">
-        <v>819</v>
+        <v>889</v>
       </c>
       <c r="I50" s="1" t="s">
-        <v>771</v>
+        <v>841</v>
       </c>
       <c r="J50" s="1" t="s">
-        <v>820</v>
+        <v>890</v>
       </c>
       <c r="K50" s="1" t="s">
-        <v>555</v>
+        <v>625</v>
       </c>
       <c r="L50" s="1" t="s">
         <v>48</v>
@@ -7735,7 +8016,7 @@
     </row>
     <row r="51" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
-        <v>821</v>
+        <v>891</v>
       </c>
       <c r="B51" s="1">
         <v>7</v>
@@ -7747,25 +8028,25 @@
         <v>2267</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>822</v>
+        <v>892</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>823</v>
+        <v>893</v>
       </c>
       <c r="G51" s="1" t="s">
-        <v>824</v>
+        <v>894</v>
       </c>
       <c r="H51" s="1" t="s">
-        <v>825</v>
+        <v>895</v>
       </c>
       <c r="I51" s="1" t="s">
-        <v>598</v>
+        <v>668</v>
       </c>
       <c r="J51" s="1" t="s">
-        <v>826</v>
+        <v>896</v>
       </c>
       <c r="K51" s="1" t="s">
-        <v>827</v>
+        <v>897</v>
       </c>
       <c r="L51" s="1" t="s">
         <v>48</v>
@@ -7803,7 +8084,7 @@
   <sheetData>
     <row r="1" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>828</v>
+        <v>898</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
@@ -7822,75 +8103,75 @@
     </row>
     <row r="2" spans="1:15" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
-        <v>541</v>
+        <v>611</v>
       </c>
       <c r="B2" s="5" t="s">
         <v>291</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>544</v>
+        <v>614</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>545</v>
+        <v>615</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>546</v>
+        <v>616</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>547</v>
+        <v>617</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>548</v>
+        <v>618</v>
       </c>
       <c r="H2" s="5" t="s">
-        <v>549</v>
+        <v>619</v>
       </c>
       <c r="I2" s="5" t="s">
-        <v>550</v>
+        <v>620</v>
       </c>
       <c r="J2" s="5" t="s">
-        <v>551</v>
+        <v>621</v>
       </c>
       <c r="K2" s="5" t="s">
-        <v>829</v>
+        <v>899</v>
       </c>
       <c r="L2" s="5" t="s">
-        <v>830</v>
+        <v>900</v>
       </c>
       <c r="M2" s="5" t="s">
-        <v>831</v>
+        <v>901</v>
       </c>
       <c r="N2" s="5" t="s">
-        <v>832</v>
+        <v>902</v>
       </c>
       <c r="O2" s="5" t="s">
-        <v>833</v>
+        <v>903</v>
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>834</v>
+        <v>904</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>835</v>
+        <v>905</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>836</v>
+        <v>906</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>563</v>
+        <v>633</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>837</v>
+        <v>907</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>555</v>
+        <v>625</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>838</v>
+        <v>908</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>839</v>
+        <v>909</v>
       </c>
       <c r="I3" s="1" t="s">
         <v>48</v>
@@ -7899,7 +8180,7 @@
         <v>48</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>840</v>
+        <v>910</v>
       </c>
       <c r="L3" s="1">
         <v>0.5</v>
@@ -7908,36 +8189,36 @@
         <v>15</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>841</v>
+        <v>911</v>
       </c>
       <c r="O3" s="1" t="s">
-        <v>842</v>
+        <v>912</v>
       </c>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>843</v>
+        <v>913</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>844</v>
+        <v>914</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>845</v>
+        <v>915</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>559</v>
+        <v>629</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>846</v>
+        <v>916</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>557</v>
+        <v>627</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>847</v>
+        <v>917</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>571</v>
+        <v>641</v>
       </c>
       <c r="I4" s="1" t="s">
         <v>48</v>
@@ -7946,7 +8227,7 @@
         <v>48</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>848</v>
+        <v>918</v>
       </c>
       <c r="L4" s="1">
         <v>0.45</v>
@@ -7955,36 +8236,36 @@
         <v>10</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>849</v>
+        <v>919</v>
       </c>
       <c r="O4" s="1" t="s">
-        <v>850</v>
+        <v>920</v>
       </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>851</v>
+        <v>921</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>852</v>
+        <v>922</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>853</v>
+        <v>923</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>563</v>
+        <v>633</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>854</v>
+        <v>924</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>565</v>
+        <v>635</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>855</v>
+        <v>925</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>629</v>
+        <v>699</v>
       </c>
       <c r="I5" s="1" t="s">
         <v>48</v>
@@ -7993,7 +8274,7 @@
         <v>48</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>856</v>
+        <v>926</v>
       </c>
       <c r="L5" s="1">
         <v>0.5</v>
@@ -8002,36 +8283,36 @@
         <v>10</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>857</v>
+        <v>927</v>
       </c>
       <c r="O5" s="1" t="s">
-        <v>842</v>
+        <v>912</v>
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>858</v>
+        <v>928</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>859</v>
+        <v>929</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>860</v>
+        <v>930</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>555</v>
+        <v>625</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>861</v>
+        <v>931</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>862</v>
+        <v>932</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>863</v>
+        <v>933</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>601</v>
+        <v>671</v>
       </c>
       <c r="I6" s="1" t="s">
         <v>48</v>
@@ -8040,7 +8321,7 @@
         <v>48</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>864</v>
+        <v>934</v>
       </c>
       <c r="L6" s="1">
         <v>0.5</v>
@@ -8049,36 +8330,36 @@
         <v>20</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>865</v>
+        <v>935</v>
       </c>
       <c r="O6" s="1" t="s">
-        <v>866</v>
+        <v>936</v>
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>867</v>
+        <v>937</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>868</v>
+        <v>938</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>869</v>
+        <v>939</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>565</v>
+        <v>635</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>870</v>
+        <v>940</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>559</v>
+        <v>629</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>871</v>
+        <v>941</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>557</v>
+        <v>627</v>
       </c>
       <c r="I7" s="1" t="s">
         <v>48</v>
@@ -8087,7 +8368,7 @@
         <v>48</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>872</v>
+        <v>942</v>
       </c>
       <c r="L7" s="1">
         <v>0.45</v>
@@ -8096,36 +8377,36 @@
         <v>10</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>873</v>
+        <v>943</v>
       </c>
       <c r="O7" s="1" t="s">
-        <v>874</v>
+        <v>944</v>
       </c>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>875</v>
+        <v>945</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>876</v>
+        <v>946</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>877</v>
+        <v>947</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>563</v>
+        <v>633</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>878</v>
+        <v>948</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>559</v>
+        <v>629</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>879</v>
+        <v>949</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>557</v>
+        <v>627</v>
       </c>
       <c r="I8" s="1" t="s">
         <v>48</v>
@@ -8134,7 +8415,7 @@
         <v>48</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>880</v>
+        <v>950</v>
       </c>
       <c r="L8" s="1">
         <v>0.5</v>
@@ -8143,36 +8424,36 @@
         <v>15</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>881</v>
+        <v>951</v>
       </c>
       <c r="O8" s="1" t="s">
-        <v>882</v>
+        <v>952</v>
       </c>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>883</v>
+        <v>953</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>884</v>
+        <v>954</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>885</v>
+        <v>955</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>645</v>
+        <v>715</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>886</v>
+        <v>956</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>601</v>
+        <v>671</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>887</v>
+        <v>957</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>565</v>
+        <v>635</v>
       </c>
       <c r="I9" s="1" t="s">
         <v>48</v>
@@ -8181,7 +8462,7 @@
         <v>48</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>888</v>
+        <v>958</v>
       </c>
       <c r="L9" s="1">
         <v>0.4</v>
@@ -8190,36 +8471,36 @@
         <v>15</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>889</v>
+        <v>959</v>
       </c>
       <c r="O9" s="1" t="s">
-        <v>890</v>
+        <v>960</v>
       </c>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>891</v>
+        <v>961</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>892</v>
+        <v>962</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>893</v>
+        <v>963</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>567</v>
+        <v>637</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>894</v>
+        <v>964</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>563</v>
+        <v>633</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>895</v>
+        <v>965</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>555</v>
+        <v>625</v>
       </c>
       <c r="I10" s="1" t="s">
         <v>48</v>
@@ -8228,7 +8509,7 @@
         <v>48</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>896</v>
+        <v>966</v>
       </c>
       <c r="L10" s="1">
         <v>0.5</v>
@@ -8237,36 +8518,36 @@
         <v>10</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>897</v>
+        <v>967</v>
       </c>
       <c r="O10" s="1" t="s">
-        <v>874</v>
+        <v>944</v>
       </c>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>898</v>
+        <v>968</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>899</v>
+        <v>969</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>900</v>
+        <v>970</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>559</v>
+        <v>629</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>901</v>
+        <v>971</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>601</v>
+        <v>671</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>902</v>
+        <v>972</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>587</v>
+        <v>657</v>
       </c>
       <c r="I11" s="1" t="s">
         <v>48</v>
@@ -8275,7 +8556,7 @@
         <v>48</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>903</v>
+        <v>973</v>
       </c>
       <c r="L11" s="1">
         <v>0.45</v>
@@ -8284,36 +8565,36 @@
         <v>20</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>904</v>
+        <v>974</v>
       </c>
       <c r="O11" s="1" t="s">
-        <v>866</v>
+        <v>936</v>
       </c>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>905</v>
+        <v>975</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>906</v>
+        <v>976</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>907</v>
+        <v>977</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>563</v>
+        <v>633</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>908</v>
+        <v>978</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>565</v>
+        <v>635</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>909</v>
+        <v>979</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>557</v>
+        <v>627</v>
       </c>
       <c r="I12" s="1" t="s">
         <v>48</v>
@@ -8322,7 +8603,7 @@
         <v>48</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>910</v>
+        <v>980</v>
       </c>
       <c r="L12" s="1">
         <v>0.5</v>
@@ -8331,36 +8612,36 @@
         <v>15</v>
       </c>
       <c r="N12" s="1" t="s">
-        <v>911</v>
+        <v>981</v>
       </c>
       <c r="O12" s="1" t="s">
-        <v>850</v>
+        <v>920</v>
       </c>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>912</v>
+        <v>982</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>913</v>
+        <v>983</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>914</v>
+        <v>984</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>567</v>
+        <v>637</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>915</v>
+        <v>985</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>601</v>
+        <v>671</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>916</v>
+        <v>986</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>555</v>
+        <v>625</v>
       </c>
       <c r="I13" s="1" t="s">
         <v>48</v>
@@ -8369,7 +8650,7 @@
         <v>48</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>917</v>
+        <v>987</v>
       </c>
       <c r="L13" s="1">
         <v>0.45</v>
@@ -8378,36 +8659,36 @@
         <v>20</v>
       </c>
       <c r="N13" s="1" t="s">
-        <v>918</v>
+        <v>988</v>
       </c>
       <c r="O13" s="1" t="s">
-        <v>866</v>
+        <v>936</v>
       </c>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>919</v>
+        <v>989</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>920</v>
+        <v>990</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>921</v>
+        <v>991</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>559</v>
+        <v>629</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>922</v>
+        <v>992</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>645</v>
+        <v>715</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>923</v>
+        <v>993</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>565</v>
+        <v>635</v>
       </c>
       <c r="I14" s="1" t="s">
         <v>48</v>
@@ -8416,7 +8697,7 @@
         <v>48</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>924</v>
+        <v>994</v>
       </c>
       <c r="L14" s="1">
         <v>0.5</v>
@@ -8425,36 +8706,36 @@
         <v>10</v>
       </c>
       <c r="N14" s="1" t="s">
-        <v>925</v>
+        <v>995</v>
       </c>
       <c r="O14" s="1" t="s">
-        <v>842</v>
+        <v>912</v>
       </c>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>926</v>
+        <v>996</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>927</v>
+        <v>997</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>928</v>
+        <v>998</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>645</v>
+        <v>715</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>929</v>
+        <v>999</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>557</v>
+        <v>627</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>930</v>
+        <v>1000</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>931</v>
+        <v>1001</v>
       </c>
       <c r="I15" s="1" t="s">
         <v>48</v>
@@ -8463,7 +8744,7 @@
         <v>48</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>932</v>
+        <v>1002</v>
       </c>
       <c r="L15" s="1">
         <v>0.45</v>
@@ -8472,10 +8753,10 @@
         <v>20</v>
       </c>
       <c r="N15" s="1" t="s">
-        <v>933</v>
+        <v>1003</v>
       </c>
       <c r="O15" s="1" t="s">
-        <v>934</v>
+        <v>1004</v>
       </c>
     </row>
   </sheetData>
@@ -8506,7 +8787,7 @@
   <sheetData>
     <row r="1" spans="1:18" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>935</v>
+        <v>1005</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
@@ -8528,13 +8809,13 @@
     </row>
     <row r="2" spans="1:18" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
-        <v>541</v>
+        <v>611</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>463</v>
+        <v>533</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>936</v>
+        <v>1006</v>
       </c>
       <c r="D2" s="5" t="s">
         <v>291</v>
@@ -8543,57 +8824,57 @@
         <v>292</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>464</v>
+        <v>534</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>465</v>
+        <v>535</v>
       </c>
       <c r="H2" s="5" t="s">
-        <v>937</v>
+        <v>1007</v>
       </c>
       <c r="I2" s="5" t="s">
-        <v>938</v>
+        <v>1008</v>
       </c>
       <c r="J2" s="5" t="s">
-        <v>939</v>
+        <v>1009</v>
       </c>
       <c r="K2" s="5" t="s">
-        <v>544</v>
+        <v>614</v>
       </c>
       <c r="L2" s="5" t="s">
-        <v>545</v>
+        <v>615</v>
       </c>
       <c r="M2" s="5" t="s">
-        <v>546</v>
+        <v>616</v>
       </c>
       <c r="N2" s="5" t="s">
-        <v>547</v>
+        <v>617</v>
       </c>
       <c r="O2" s="5" t="s">
-        <v>548</v>
+        <v>618</v>
       </c>
       <c r="P2" s="5" t="s">
-        <v>549</v>
+        <v>619</v>
       </c>
       <c r="Q2" s="5" t="s">
-        <v>550</v>
+        <v>620</v>
       </c>
       <c r="R2" s="5" t="s">
-        <v>551</v>
+        <v>621</v>
       </c>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>940</v>
+        <v>1010</v>
       </c>
       <c r="B3" s="1">
         <v>1</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>941</v>
+        <v>1011</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>942</v>
+        <v>1012</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>48</v>
@@ -8640,19 +8921,19 @@
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>943</v>
+        <v>1013</v>
       </c>
       <c r="B4" s="1">
         <v>1</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>941</v>
+        <v>1011</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>944</v>
+        <v>1014</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>945</v>
+        <v>1015</v>
       </c>
       <c r="F4" s="1">
         <v>1893</v>
@@ -8696,19 +8977,19 @@
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>946</v>
+        <v>1016</v>
       </c>
       <c r="B5" s="1">
         <v>1</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>947</v>
+        <v>1017</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>948</v>
+        <v>1018</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>949</v>
+        <v>1019</v>
       </c>
       <c r="F5" s="1">
         <v>1894</v>
@@ -8752,16 +9033,16 @@
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>950</v>
+        <v>1020</v>
       </c>
       <c r="B6" s="1">
         <v>1</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>947</v>
+        <v>1017</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>951</v>
+        <v>1021</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>48</v>
@@ -8808,16 +9089,16 @@
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>952</v>
+        <v>1022</v>
       </c>
       <c r="B7" s="1">
         <v>1</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>947</v>
+        <v>1017</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>953</v>
+        <v>1023</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>48</v>
@@ -8864,19 +9145,19 @@
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>954</v>
+        <v>1024</v>
       </c>
       <c r="B8" s="1">
         <v>1</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>955</v>
+        <v>1025</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>956</v>
+        <v>1026</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>957</v>
+        <v>1027</v>
       </c>
       <c r="F8" s="1">
         <v>1912</v>
@@ -8894,22 +9175,22 @@
         <v>48</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>958</v>
+        <v>1028</v>
       </c>
       <c r="L8" s="1" t="s">
-        <v>580</v>
+        <v>650</v>
       </c>
       <c r="M8" s="1" t="s">
-        <v>959</v>
+        <v>1029</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>960</v>
+        <v>1030</v>
       </c>
       <c r="O8" s="1" t="s">
-        <v>961</v>
+        <v>1031</v>
       </c>
       <c r="P8" s="1" t="s">
-        <v>571</v>
+        <v>641</v>
       </c>
       <c r="Q8" s="1" t="s">
         <v>48</v>
@@ -8920,19 +9201,19 @@
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>962</v>
+        <v>1032</v>
       </c>
       <c r="B9" s="1">
         <v>1</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>947</v>
+        <v>1017</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>963</v>
+        <v>1033</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>964</v>
+        <v>1034</v>
       </c>
       <c r="F9" s="1">
         <v>1913</v>
@@ -8976,19 +9257,19 @@
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>965</v>
+        <v>1035</v>
       </c>
       <c r="B10" s="1">
         <v>1</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>947</v>
+        <v>1017</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>966</v>
+        <v>1036</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>967</v>
+        <v>1037</v>
       </c>
       <c r="F10" s="1">
         <v>1917</v>
@@ -9032,19 +9313,19 @@
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>968</v>
+        <v>1038</v>
       </c>
       <c r="B11" s="1">
         <v>1</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>955</v>
+        <v>1025</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>969</v>
+        <v>1039</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>970</v>
+        <v>1040</v>
       </c>
       <c r="F11" s="1">
         <v>1931</v>
@@ -9062,22 +9343,22 @@
         <v>48</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>971</v>
+        <v>1041</v>
       </c>
       <c r="L11" s="1" t="s">
-        <v>557</v>
+        <v>627</v>
       </c>
       <c r="M11" s="1" t="s">
-        <v>972</v>
+        <v>1042</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>559</v>
+        <v>629</v>
       </c>
       <c r="O11" s="1" t="s">
-        <v>973</v>
+        <v>1043</v>
       </c>
       <c r="P11" s="1" t="s">
-        <v>563</v>
+        <v>633</v>
       </c>
       <c r="Q11" s="1" t="s">
         <v>48</v>
@@ -9088,19 +9369,19 @@
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>974</v>
+        <v>1044</v>
       </c>
       <c r="B12" s="1">
         <v>1</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>947</v>
+        <v>1017</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>975</v>
+        <v>1045</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>976</v>
+        <v>1046</v>
       </c>
       <c r="F12" s="1">
         <v>1932</v>
@@ -9144,16 +9425,16 @@
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>977</v>
+        <v>1047</v>
       </c>
       <c r="B13" s="1">
         <v>1</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>947</v>
+        <v>1017</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>978</v>
+        <v>1048</v>
       </c>
       <c r="E13" s="1" t="s">
         <v>48</v>
@@ -9200,19 +9481,19 @@
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>979</v>
+        <v>1049</v>
       </c>
       <c r="B14" s="1">
         <v>1</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>955</v>
+        <v>1025</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>980</v>
+        <v>1050</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>981</v>
+        <v>1051</v>
       </c>
       <c r="F14" s="1">
         <v>1939</v>
@@ -9230,22 +9511,22 @@
         <v>48</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>982</v>
+        <v>1052</v>
       </c>
       <c r="L14" s="1" t="s">
-        <v>557</v>
+        <v>627</v>
       </c>
       <c r="M14" s="1" t="s">
-        <v>983</v>
+        <v>1053</v>
       </c>
       <c r="N14" s="1" t="s">
-        <v>563</v>
+        <v>633</v>
       </c>
       <c r="O14" s="1" t="s">
-        <v>984</v>
+        <v>1054</v>
       </c>
       <c r="P14" s="1" t="s">
-        <v>985</v>
+        <v>1055</v>
       </c>
       <c r="Q14" s="1" t="s">
         <v>48</v>
@@ -9256,16 +9537,16 @@
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>986</v>
+        <v>1056</v>
       </c>
       <c r="B15" s="1">
         <v>1</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>941</v>
+        <v>1011</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>987</v>
+        <v>1057</v>
       </c>
       <c r="E15" s="1" t="s">
         <v>48</v>
@@ -9312,16 +9593,16 @@
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>988</v>
+        <v>1058</v>
       </c>
       <c r="B16" s="1">
         <v>2</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>941</v>
+        <v>1011</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>989</v>
+        <v>1059</v>
       </c>
       <c r="E16" s="1" t="s">
         <v>48</v>
@@ -9368,16 +9649,16 @@
     </row>
     <row r="17" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>990</v>
+        <v>1060</v>
       </c>
       <c r="B17" s="1">
         <v>2</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>941</v>
+        <v>1011</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>991</v>
+        <v>1061</v>
       </c>
       <c r="E17" s="1" t="s">
         <v>48</v>
@@ -9424,16 +9705,16 @@
     </row>
     <row r="18" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>992</v>
+        <v>1062</v>
       </c>
       <c r="B18" s="1">
         <v>2</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>955</v>
+        <v>1025</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>993</v>
+        <v>1063</v>
       </c>
       <c r="E18" s="1" t="s">
         <v>48</v>
@@ -9454,22 +9735,22 @@
         <v>48</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>994</v>
+        <v>1064</v>
       </c>
       <c r="L18" s="1" t="s">
-        <v>567</v>
+        <v>637</v>
       </c>
       <c r="M18" s="1" t="s">
-        <v>995</v>
+        <v>1065</v>
       </c>
       <c r="N18" s="1" t="s">
-        <v>559</v>
+        <v>629</v>
       </c>
       <c r="O18" s="1" t="s">
-        <v>996</v>
+        <v>1066</v>
       </c>
       <c r="P18" s="1" t="s">
-        <v>555</v>
+        <v>625</v>
       </c>
       <c r="Q18" s="1" t="s">
         <v>48</v>
@@ -9480,19 +9761,19 @@
     </row>
     <row r="19" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>997</v>
+        <v>1067</v>
       </c>
       <c r="B19" s="1">
         <v>2</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>955</v>
+        <v>1025</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>998</v>
+        <v>1068</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>999</v>
+        <v>1069</v>
       </c>
       <c r="F19" s="1">
         <v>1967</v>
@@ -9510,22 +9791,22 @@
         <v>48</v>
       </c>
       <c r="K19" s="1" t="s">
-        <v>1000</v>
+        <v>1070</v>
       </c>
       <c r="L19" s="1" t="s">
-        <v>557</v>
+        <v>627</v>
       </c>
       <c r="M19" s="1" t="s">
-        <v>1001</v>
+        <v>1071</v>
       </c>
       <c r="N19" s="1" t="s">
-        <v>1002</v>
+        <v>1072</v>
       </c>
       <c r="O19" s="1" t="s">
-        <v>1003</v>
+        <v>1073</v>
       </c>
       <c r="P19" s="1" t="s">
-        <v>563</v>
+        <v>633</v>
       </c>
       <c r="Q19" s="1" t="s">
         <v>48</v>
@@ -9536,19 +9817,19 @@
     </row>
     <row r="20" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>1004</v>
+        <v>1074</v>
       </c>
       <c r="B20" s="1">
         <v>2</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>947</v>
+        <v>1017</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>1005</v>
+        <v>1075</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>976</v>
+        <v>1046</v>
       </c>
       <c r="F20" s="1">
         <v>1968</v>
@@ -9592,16 +9873,16 @@
     </row>
     <row r="21" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>1006</v>
+        <v>1076</v>
       </c>
       <c r="B21" s="1">
         <v>2</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>947</v>
+        <v>1017</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>1007</v>
+        <v>1077</v>
       </c>
       <c r="E21" s="1" t="s">
         <v>48</v>
@@ -9648,16 +9929,16 @@
     </row>
     <row r="22" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>1008</v>
+        <v>1078</v>
       </c>
       <c r="B22" s="1">
         <v>2</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>941</v>
+        <v>1011</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>1009</v>
+        <v>1079</v>
       </c>
       <c r="E22" s="1" t="s">
         <v>48</v>
@@ -9704,19 +9985,19 @@
     </row>
     <row r="23" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>1010</v>
+        <v>1080</v>
       </c>
       <c r="B23" s="1">
         <v>2</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>955</v>
+        <v>1025</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>1011</v>
+        <v>1081</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>1012</v>
+        <v>1082</v>
       </c>
       <c r="F23" s="1">
         <v>1991</v>
@@ -9734,22 +10015,22 @@
         <v>48</v>
       </c>
       <c r="K23" s="1" t="s">
-        <v>1013</v>
+        <v>1083</v>
       </c>
       <c r="L23" s="1" t="s">
-        <v>563</v>
+        <v>633</v>
       </c>
       <c r="M23" s="1" t="s">
-        <v>1014</v>
+        <v>1084</v>
       </c>
       <c r="N23" s="1" t="s">
-        <v>559</v>
+        <v>629</v>
       </c>
       <c r="O23" s="1" t="s">
-        <v>1015</v>
+        <v>1085</v>
       </c>
       <c r="P23" s="1" t="s">
-        <v>565</v>
+        <v>635</v>
       </c>
       <c r="Q23" s="1" t="s">
         <v>48</v>
@@ -9760,16 +10041,16 @@
     </row>
     <row r="24" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>1016</v>
+        <v>1086</v>
       </c>
       <c r="B24" s="1">
         <v>2</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>955</v>
+        <v>1025</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>1017</v>
+        <v>1087</v>
       </c>
       <c r="E24" s="1" t="s">
         <v>48</v>
@@ -9790,22 +10071,22 @@
         <v>48</v>
       </c>
       <c r="K24" s="1" t="s">
-        <v>1018</v>
+        <v>1088</v>
       </c>
       <c r="L24" s="1" t="s">
-        <v>1019</v>
+        <v>1089</v>
       </c>
       <c r="M24" s="1" t="s">
-        <v>1020</v>
+        <v>1090</v>
       </c>
       <c r="N24" s="1" t="s">
-        <v>592</v>
+        <v>662</v>
       </c>
       <c r="O24" s="1" t="s">
-        <v>1021</v>
+        <v>1091</v>
       </c>
       <c r="P24" s="1" t="s">
-        <v>641</v>
+        <v>711</v>
       </c>
       <c r="Q24" s="1" t="s">
         <v>48</v>
@@ -9816,19 +10097,19 @@
     </row>
     <row r="25" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>1022</v>
+        <v>1092</v>
       </c>
       <c r="B25" s="1">
         <v>2</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>947</v>
+        <v>1017</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>1023</v>
+        <v>1093</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>976</v>
+        <v>1046</v>
       </c>
       <c r="F25" s="1">
         <v>2006</v>
@@ -9872,16 +10153,16 @@
     </row>
     <row r="26" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>1024</v>
+        <v>1094</v>
       </c>
       <c r="B26" s="1">
         <v>2</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>941</v>
+        <v>1011</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>1025</v>
+        <v>1095</v>
       </c>
       <c r="E26" s="1" t="s">
         <v>48</v>
@@ -9928,19 +10209,19 @@
     </row>
     <row r="27" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>1026</v>
+        <v>1096</v>
       </c>
       <c r="B27" s="1">
         <v>3</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>947</v>
+        <v>1017</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>1027</v>
+        <v>1097</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>1028</v>
+        <v>1098</v>
       </c>
       <c r="F27" s="1">
         <v>2011</v>
@@ -9984,16 +10265,16 @@
     </row>
     <row r="28" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>1029</v>
+        <v>1099</v>
       </c>
       <c r="B28" s="1">
         <v>3</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>955</v>
+        <v>1025</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>1030</v>
+        <v>1100</v>
       </c>
       <c r="E28" s="1" t="s">
         <v>48</v>
@@ -10014,22 +10295,22 @@
         <v>48</v>
       </c>
       <c r="K28" s="1" t="s">
-        <v>1031</v>
+        <v>1101</v>
       </c>
       <c r="L28" s="1" t="s">
-        <v>563</v>
+        <v>633</v>
       </c>
       <c r="M28" s="1" t="s">
-        <v>1032</v>
+        <v>1102</v>
       </c>
       <c r="N28" s="1" t="s">
-        <v>557</v>
+        <v>627</v>
       </c>
       <c r="O28" s="1" t="s">
-        <v>1033</v>
+        <v>1103</v>
       </c>
       <c r="P28" s="1" t="s">
-        <v>565</v>
+        <v>635</v>
       </c>
       <c r="Q28" s="1" t="s">
         <v>48</v>
@@ -10040,19 +10321,19 @@
     </row>
     <row r="29" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>1034</v>
+        <v>1104</v>
       </c>
       <c r="B29" s="1">
         <v>3</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>955</v>
+        <v>1025</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>1035</v>
+        <v>1105</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>1036</v>
+        <v>1106</v>
       </c>
       <c r="F29" s="1">
         <v>2034</v>
@@ -10070,22 +10351,22 @@
         <v>48</v>
       </c>
       <c r="K29" s="1" t="s">
-        <v>1037</v>
+        <v>1107</v>
       </c>
       <c r="L29" s="1" t="s">
-        <v>1038</v>
+        <v>1108</v>
       </c>
       <c r="M29" s="1" t="s">
-        <v>1039</v>
+        <v>1109</v>
       </c>
       <c r="N29" s="1" t="s">
-        <v>592</v>
+        <v>662</v>
       </c>
       <c r="O29" s="1" t="s">
-        <v>1040</v>
+        <v>1110</v>
       </c>
       <c r="P29" s="1" t="s">
-        <v>1041</v>
+        <v>1111</v>
       </c>
       <c r="Q29" s="1" t="s">
         <v>48</v>
@@ -10096,16 +10377,16 @@
     </row>
     <row r="30" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>1042</v>
+        <v>1112</v>
       </c>
       <c r="B30" s="1">
         <v>3</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>941</v>
+        <v>1011</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>1043</v>
+        <v>1113</v>
       </c>
       <c r="E30" s="1" t="s">
         <v>48</v>
@@ -10152,16 +10433,16 @@
     </row>
     <row r="31" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>1044</v>
+        <v>1114</v>
       </c>
       <c r="B31" s="1">
         <v>3</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>947</v>
+        <v>1017</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>1045</v>
+        <v>1115</v>
       </c>
       <c r="E31" s="1" t="s">
         <v>48</v>
@@ -10208,19 +10489,19 @@
     </row>
     <row r="32" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>1046</v>
+        <v>1116</v>
       </c>
       <c r="B32" s="1">
         <v>3</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>955</v>
+        <v>1025</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>1047</v>
+        <v>1117</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>1048</v>
+        <v>1118</v>
       </c>
       <c r="F32" s="1">
         <v>2054</v>
@@ -10238,22 +10519,22 @@
         <v>48</v>
       </c>
       <c r="K32" s="1" t="s">
-        <v>1049</v>
+        <v>1119</v>
       </c>
       <c r="L32" s="1" t="s">
-        <v>584</v>
+        <v>654</v>
       </c>
       <c r="M32" s="1" t="s">
-        <v>1050</v>
+        <v>1120</v>
       </c>
       <c r="N32" s="1" t="s">
-        <v>1051</v>
+        <v>1121</v>
       </c>
       <c r="O32" s="1" t="s">
-        <v>1052</v>
+        <v>1122</v>
       </c>
       <c r="P32" s="1" t="s">
-        <v>580</v>
+        <v>650</v>
       </c>
       <c r="Q32" s="1" t="s">
         <v>48</v>
@@ -10264,19 +10545,19 @@
     </row>
     <row r="33" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>1053</v>
+        <v>1123</v>
       </c>
       <c r="B33" s="1">
         <v>3</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>947</v>
+        <v>1017</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>1054</v>
+        <v>1124</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>976</v>
+        <v>1046</v>
       </c>
       <c r="F33" s="1">
         <v>2055</v>
@@ -10320,16 +10601,16 @@
     </row>
     <row r="34" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>1055</v>
+        <v>1125</v>
       </c>
       <c r="B34" s="1">
         <v>3</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>941</v>
+        <v>1011</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>1056</v>
+        <v>1126</v>
       </c>
       <c r="E34" s="1" t="s">
         <v>48</v>
@@ -10376,16 +10657,16 @@
     </row>
     <row r="35" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>1057</v>
+        <v>1127</v>
       </c>
       <c r="B35" s="1">
         <v>4</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>941</v>
+        <v>1011</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>1058</v>
+        <v>1128</v>
       </c>
       <c r="E35" s="1" t="s">
         <v>48</v>
@@ -10432,19 +10713,19 @@
     </row>
     <row r="36" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>1059</v>
+        <v>1129</v>
       </c>
       <c r="B36" s="1">
         <v>4</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>955</v>
+        <v>1025</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>1060</v>
+        <v>1130</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>1061</v>
+        <v>1131</v>
       </c>
       <c r="F36" s="1">
         <v>2077</v>
@@ -10462,22 +10743,22 @@
         <v>48</v>
       </c>
       <c r="K36" s="1" t="s">
-        <v>1062</v>
+        <v>1132</v>
       </c>
       <c r="L36" s="1" t="s">
-        <v>557</v>
+        <v>627</v>
       </c>
       <c r="M36" s="1" t="s">
-        <v>1063</v>
+        <v>1133</v>
       </c>
       <c r="N36" s="1" t="s">
-        <v>559</v>
+        <v>629</v>
       </c>
       <c r="O36" s="1" t="s">
-        <v>1064</v>
+        <v>1134</v>
       </c>
       <c r="P36" s="1" t="s">
-        <v>567</v>
+        <v>637</v>
       </c>
       <c r="Q36" s="1" t="s">
         <v>48</v>
@@ -10488,16 +10769,16 @@
     </row>
     <row r="37" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>1065</v>
+        <v>1135</v>
       </c>
       <c r="B37" s="1">
         <v>4</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>947</v>
+        <v>1017</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>1066</v>
+        <v>1136</v>
       </c>
       <c r="E37" s="1" t="s">
         <v>48</v>
@@ -10544,16 +10825,16 @@
     </row>
     <row r="38" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>1067</v>
+        <v>1137</v>
       </c>
       <c r="B38" s="1">
         <v>4</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>941</v>
+        <v>1011</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>1068</v>
+        <v>1138</v>
       </c>
       <c r="E38" s="1" t="s">
         <v>48</v>
@@ -10600,19 +10881,19 @@
     </row>
     <row r="39" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
-        <v>1069</v>
+        <v>1139</v>
       </c>
       <c r="B39" s="1">
         <v>4</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>955</v>
+        <v>1025</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>1070</v>
+        <v>1140</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>1071</v>
+        <v>1141</v>
       </c>
       <c r="F39" s="1">
         <v>2089</v>
@@ -10630,22 +10911,22 @@
         <v>48</v>
       </c>
       <c r="K39" s="1" t="s">
-        <v>1072</v>
+        <v>1142</v>
       </c>
       <c r="L39" s="1" t="s">
-        <v>592</v>
+        <v>662</v>
       </c>
       <c r="M39" s="1" t="s">
-        <v>1073</v>
+        <v>1143</v>
       </c>
       <c r="N39" s="1" t="s">
-        <v>766</v>
+        <v>836</v>
       </c>
       <c r="O39" s="1" t="s">
-        <v>1074</v>
+        <v>1144</v>
       </c>
       <c r="P39" s="1" t="s">
-        <v>598</v>
+        <v>668</v>
       </c>
       <c r="Q39" s="1" t="s">
         <v>48</v>
@@ -10656,16 +10937,16 @@
     </row>
     <row r="40" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
-        <v>1075</v>
+        <v>1145</v>
       </c>
       <c r="B40" s="1">
         <v>4</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>947</v>
+        <v>1017</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>1076</v>
+        <v>1146</v>
       </c>
       <c r="E40" s="1" t="s">
         <v>48</v>
@@ -10712,16 +10993,16 @@
     </row>
     <row r="41" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
-        <v>1077</v>
+        <v>1147</v>
       </c>
       <c r="B41" s="1">
         <v>4</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>941</v>
+        <v>1011</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>1078</v>
+        <v>1148</v>
       </c>
       <c r="E41" s="1" t="s">
         <v>48</v>
@@ -10768,19 +11049,19 @@
     </row>
     <row r="42" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
-        <v>1079</v>
+        <v>1149</v>
       </c>
       <c r="B42" s="1">
         <v>4</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>955</v>
+        <v>1025</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>1080</v>
+        <v>1150</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>1081</v>
+        <v>1151</v>
       </c>
       <c r="F42" s="1">
         <v>2106</v>
@@ -10798,22 +11079,22 @@
         <v>48</v>
       </c>
       <c r="K42" s="1" t="s">
-        <v>1082</v>
+        <v>1152</v>
       </c>
       <c r="L42" s="1" t="s">
-        <v>557</v>
+        <v>627</v>
       </c>
       <c r="M42" s="1" t="s">
-        <v>1083</v>
+        <v>1153</v>
       </c>
       <c r="N42" s="1" t="s">
-        <v>1084</v>
+        <v>1154</v>
       </c>
       <c r="O42" s="1" t="s">
-        <v>1085</v>
+        <v>1155</v>
       </c>
       <c r="P42" s="1" t="s">
-        <v>587</v>
+        <v>657</v>
       </c>
       <c r="Q42" s="1" t="s">
         <v>48</v>
@@ -10824,19 +11105,19 @@
     </row>
     <row r="43" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
-        <v>1086</v>
+        <v>1156</v>
       </c>
       <c r="B43" s="1">
         <v>4</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>955</v>
+        <v>1025</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>1087</v>
+        <v>1157</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>1088</v>
+        <v>1158</v>
       </c>
       <c r="F43" s="1">
         <v>2111</v>
@@ -10854,22 +11135,22 @@
         <v>48</v>
       </c>
       <c r="K43" s="1" t="s">
-        <v>1089</v>
+        <v>1159</v>
       </c>
       <c r="L43" s="1" t="s">
-        <v>592</v>
+        <v>662</v>
       </c>
       <c r="M43" s="1" t="s">
-        <v>1090</v>
+        <v>1160</v>
       </c>
       <c r="N43" s="1" t="s">
-        <v>1091</v>
+        <v>1161</v>
       </c>
       <c r="O43" s="1" t="s">
-        <v>1092</v>
+        <v>1162</v>
       </c>
       <c r="P43" s="1" t="s">
-        <v>1093</v>
+        <v>1163</v>
       </c>
       <c r="Q43" s="1" t="s">
         <v>48</v>
@@ -10880,19 +11161,19 @@
     </row>
     <row r="44" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
-        <v>1094</v>
+        <v>1164</v>
       </c>
       <c r="B44" s="1">
         <v>4</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>947</v>
+        <v>1017</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>1095</v>
+        <v>1165</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>976</v>
+        <v>1046</v>
       </c>
       <c r="F44" s="1">
         <v>2113</v>
@@ -10936,19 +11217,19 @@
     </row>
     <row r="45" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
-        <v>1096</v>
+        <v>1166</v>
       </c>
       <c r="B45" s="1">
         <v>4</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>955</v>
+        <v>1025</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>1097</v>
+        <v>1167</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>1098</v>
+        <v>1168</v>
       </c>
       <c r="F45" s="1">
         <v>2127</v>
@@ -10966,22 +11247,22 @@
         <v>48</v>
       </c>
       <c r="K45" s="1" t="s">
-        <v>1099</v>
+        <v>1169</v>
       </c>
       <c r="L45" s="1" t="s">
-        <v>677</v>
+        <v>747</v>
       </c>
       <c r="M45" s="1" t="s">
-        <v>1100</v>
+        <v>1170</v>
       </c>
       <c r="N45" s="1" t="s">
-        <v>598</v>
+        <v>668</v>
       </c>
       <c r="O45" s="1" t="s">
-        <v>1101</v>
+        <v>1171</v>
       </c>
       <c r="P45" s="1" t="s">
-        <v>1102</v>
+        <v>1172</v>
       </c>
       <c r="Q45" s="1" t="s">
         <v>48</v>
@@ -10992,19 +11273,19 @@
     </row>
     <row r="46" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
-        <v>1103</v>
+        <v>1173</v>
       </c>
       <c r="B46" s="1">
         <v>4</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>947</v>
+        <v>1017</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>1104</v>
+        <v>1174</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>1105</v>
+        <v>1175</v>
       </c>
       <c r="F46" s="1">
         <v>2128</v>
@@ -11048,16 +11329,16 @@
     </row>
     <row r="47" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
-        <v>1106</v>
+        <v>1176</v>
       </c>
       <c r="B47" s="1">
         <v>4</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>941</v>
+        <v>1011</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>1107</v>
+        <v>1177</v>
       </c>
       <c r="E47" s="1" t="s">
         <v>48</v>
@@ -11104,16 +11385,16 @@
     </row>
     <row r="48" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
-        <v>1108</v>
+        <v>1178</v>
       </c>
       <c r="B48" s="1">
         <v>4</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>941</v>
+        <v>1011</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>1109</v>
+        <v>1179</v>
       </c>
       <c r="E48" s="1" t="s">
         <v>48</v>
@@ -11160,19 +11441,19 @@
     </row>
     <row r="49" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
-        <v>1110</v>
+        <v>1180</v>
       </c>
       <c r="B49" s="1">
         <v>5</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>947</v>
+        <v>1017</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>1111</v>
+        <v>1181</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>1112</v>
+        <v>1182</v>
       </c>
       <c r="F49" s="1">
         <v>2136</v>
@@ -11216,19 +11497,19 @@
     </row>
     <row r="50" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
-        <v>1113</v>
+        <v>1183</v>
       </c>
       <c r="B50" s="1">
         <v>5</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>955</v>
+        <v>1025</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>1114</v>
+        <v>1184</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>1115</v>
+        <v>1185</v>
       </c>
       <c r="F50" s="1">
         <v>2148</v>
@@ -11246,22 +11527,22 @@
         <v>48</v>
       </c>
       <c r="K50" s="1" t="s">
-        <v>1116</v>
+        <v>1186</v>
       </c>
       <c r="L50" s="1" t="s">
-        <v>598</v>
+        <v>668</v>
       </c>
       <c r="M50" s="1" t="s">
-        <v>1117</v>
+        <v>1187</v>
       </c>
       <c r="N50" s="1" t="s">
-        <v>557</v>
+        <v>627</v>
       </c>
       <c r="O50" s="1" t="s">
-        <v>1118</v>
+        <v>1188</v>
       </c>
       <c r="P50" s="1" t="s">
-        <v>565</v>
+        <v>635</v>
       </c>
       <c r="Q50" s="1" t="s">
         <v>48</v>
@@ -11272,16 +11553,16 @@
     </row>
     <row r="51" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
-        <v>1119</v>
+        <v>1189</v>
       </c>
       <c r="B51" s="1">
         <v>5</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>941</v>
+        <v>1011</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>1120</v>
+        <v>1190</v>
       </c>
       <c r="E51" s="1" t="s">
         <v>48</v>
@@ -11328,19 +11609,19 @@
     </row>
     <row r="52" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
-        <v>1121</v>
+        <v>1191</v>
       </c>
       <c r="B52" s="1">
         <v>5</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>955</v>
+        <v>1025</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>1122</v>
+        <v>1192</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>1123</v>
+        <v>1193</v>
       </c>
       <c r="F52" s="1">
         <v>2153</v>
@@ -11358,22 +11639,22 @@
         <v>48</v>
       </c>
       <c r="K52" s="1" t="s">
-        <v>1124</v>
+        <v>1194</v>
       </c>
       <c r="L52" s="1" t="s">
-        <v>592</v>
+        <v>662</v>
       </c>
       <c r="M52" s="1" t="s">
-        <v>1125</v>
+        <v>1195</v>
       </c>
       <c r="N52" s="1" t="s">
-        <v>559</v>
+        <v>629</v>
       </c>
       <c r="O52" s="1" t="s">
-        <v>1126</v>
+        <v>1196</v>
       </c>
       <c r="P52" s="1" t="s">
-        <v>563</v>
+        <v>633</v>
       </c>
       <c r="Q52" s="1" t="s">
         <v>48</v>
@@ -11384,16 +11665,16 @@
     </row>
     <row r="53" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
-        <v>1127</v>
+        <v>1197</v>
       </c>
       <c r="B53" s="1">
         <v>5</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>941</v>
+        <v>1011</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>1128</v>
+        <v>1198</v>
       </c>
       <c r="E53" s="1" t="s">
         <v>48</v>
@@ -11440,19 +11721,19 @@
     </row>
     <row r="54" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
-        <v>1129</v>
+        <v>1199</v>
       </c>
       <c r="B54" s="1">
         <v>5</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>955</v>
+        <v>1025</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>1130</v>
+        <v>1200</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>1131</v>
+        <v>1201</v>
       </c>
       <c r="F54" s="1">
         <v>2156</v>
@@ -11470,22 +11751,22 @@
         <v>48</v>
       </c>
       <c r="K54" s="1" t="s">
-        <v>1132</v>
+        <v>1202</v>
       </c>
       <c r="L54" s="1" t="s">
-        <v>598</v>
+        <v>668</v>
       </c>
       <c r="M54" s="1" t="s">
-        <v>1133</v>
+        <v>1203</v>
       </c>
       <c r="N54" s="1" t="s">
-        <v>584</v>
+        <v>654</v>
       </c>
       <c r="O54" s="1" t="s">
-        <v>1134</v>
+        <v>1204</v>
       </c>
       <c r="P54" s="1" t="s">
-        <v>1135</v>
+        <v>1205</v>
       </c>
       <c r="Q54" s="1" t="s">
         <v>48</v>
@@ -11496,16 +11777,16 @@
     </row>
     <row r="55" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
-        <v>1136</v>
+        <v>1206</v>
       </c>
       <c r="B55" s="1">
         <v>5</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>955</v>
+        <v>1025</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>1137</v>
+        <v>1207</v>
       </c>
       <c r="E55" s="1" t="s">
         <v>48</v>
@@ -11526,22 +11807,22 @@
         <v>48</v>
       </c>
       <c r="K55" s="1" t="s">
-        <v>1138</v>
+        <v>1208</v>
       </c>
       <c r="L55" s="1" t="s">
-        <v>592</v>
+        <v>662</v>
       </c>
       <c r="M55" s="1" t="s">
-        <v>1139</v>
+        <v>1209</v>
       </c>
       <c r="N55" s="1" t="s">
-        <v>766</v>
+        <v>836</v>
       </c>
       <c r="O55" s="1" t="s">
-        <v>961</v>
+        <v>1031</v>
       </c>
       <c r="P55" s="1" t="s">
-        <v>571</v>
+        <v>641</v>
       </c>
       <c r="Q55" s="1" t="s">
         <v>48</v>
@@ -11552,16 +11833,16 @@
     </row>
     <row r="56" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
-        <v>1140</v>
+        <v>1210</v>
       </c>
       <c r="B56" s="1">
         <v>5</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>941</v>
+        <v>1011</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>1141</v>
+        <v>1211</v>
       </c>
       <c r="E56" s="1" t="s">
         <v>48</v>
@@ -11608,16 +11889,16 @@
     </row>
     <row r="57" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
-        <v>1142</v>
+        <v>1212</v>
       </c>
       <c r="B57" s="1">
         <v>5</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>941</v>
+        <v>1011</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>1143</v>
+        <v>1213</v>
       </c>
       <c r="E57" s="1" t="s">
         <v>48</v>
@@ -11664,16 +11945,16 @@
     </row>
     <row r="58" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
-        <v>1144</v>
+        <v>1214</v>
       </c>
       <c r="B58" s="1">
         <v>5</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>955</v>
+        <v>1025</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>1145</v>
+        <v>1215</v>
       </c>
       <c r="E58" s="1" t="s">
         <v>48</v>
@@ -11694,22 +11975,22 @@
         <v>48</v>
       </c>
       <c r="K58" s="1" t="s">
-        <v>1146</v>
+        <v>1216</v>
       </c>
       <c r="L58" s="1" t="s">
-        <v>592</v>
+        <v>662</v>
       </c>
       <c r="M58" s="1" t="s">
-        <v>1147</v>
+        <v>1217</v>
       </c>
       <c r="N58" s="1" t="s">
-        <v>1148</v>
+        <v>1218</v>
       </c>
       <c r="O58" s="1" t="s">
-        <v>1149</v>
+        <v>1219</v>
       </c>
       <c r="P58" s="1" t="s">
-        <v>563</v>
+        <v>633</v>
       </c>
       <c r="Q58" s="1" t="s">
         <v>48</v>
@@ -11720,16 +12001,16 @@
     </row>
     <row r="59" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
-        <v>1150</v>
+        <v>1220</v>
       </c>
       <c r="B59" s="1">
         <v>5</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>947</v>
+        <v>1017</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>1151</v>
+        <v>1221</v>
       </c>
       <c r="E59" s="1" t="s">
         <v>48</v>
@@ -11776,16 +12057,16 @@
     </row>
     <row r="60" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
-        <v>1152</v>
+        <v>1222</v>
       </c>
       <c r="B60" s="1">
         <v>5</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>941</v>
+        <v>1011</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>1153</v>
+        <v>1223</v>
       </c>
       <c r="E60" s="1" t="s">
         <v>48</v>
@@ -11832,16 +12113,16 @@
     </row>
     <row r="61" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
-        <v>1154</v>
+        <v>1224</v>
       </c>
       <c r="B61" s="1">
         <v>5</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>941</v>
+        <v>1011</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>1155</v>
+        <v>1225</v>
       </c>
       <c r="E61" s="1" t="s">
         <v>48</v>
@@ -11888,16 +12169,16 @@
     </row>
     <row r="62" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
-        <v>1156</v>
+        <v>1226</v>
       </c>
       <c r="B62" s="1">
         <v>6</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>941</v>
+        <v>1011</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>1157</v>
+        <v>1227</v>
       </c>
       <c r="E62" s="1" t="s">
         <v>48</v>
@@ -11944,19 +12225,19 @@
     </row>
     <row r="63" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
-        <v>1158</v>
+        <v>1228</v>
       </c>
       <c r="B63" s="1">
         <v>6</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>955</v>
+        <v>1025</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>1159</v>
+        <v>1229</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>1160</v>
+        <v>1230</v>
       </c>
       <c r="F63" s="1">
         <v>2199</v>
@@ -11974,22 +12255,22 @@
         <v>48</v>
       </c>
       <c r="K63" s="1" t="s">
-        <v>1161</v>
+        <v>1231</v>
       </c>
       <c r="L63" s="1" t="s">
-        <v>592</v>
+        <v>662</v>
       </c>
       <c r="M63" s="1" t="s">
-        <v>1162</v>
+        <v>1232</v>
       </c>
       <c r="N63" s="1" t="s">
-        <v>584</v>
+        <v>654</v>
       </c>
       <c r="O63" s="1" t="s">
-        <v>1163</v>
+        <v>1233</v>
       </c>
       <c r="P63" s="1" t="s">
-        <v>598</v>
+        <v>668</v>
       </c>
       <c r="Q63" s="1" t="s">
         <v>48</v>
@@ -12000,16 +12281,16 @@
     </row>
     <row r="64" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
-        <v>1164</v>
+        <v>1234</v>
       </c>
       <c r="B64" s="1">
         <v>6</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>941</v>
+        <v>1011</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>1165</v>
+        <v>1235</v>
       </c>
       <c r="E64" s="1" t="s">
         <v>48</v>
@@ -12056,16 +12337,16 @@
     </row>
     <row r="65" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
-        <v>1166</v>
+        <v>1236</v>
       </c>
       <c r="B65" s="1">
         <v>6</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>947</v>
+        <v>1017</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>1167</v>
+        <v>1237</v>
       </c>
       <c r="E65" s="1" t="s">
         <v>48</v>
@@ -12112,16 +12393,16 @@
     </row>
     <row r="66" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
-        <v>1168</v>
+        <v>1238</v>
       </c>
       <c r="B66" s="1">
         <v>6</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>941</v>
+        <v>1011</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>1169</v>
+        <v>1239</v>
       </c>
       <c r="E66" s="1" t="s">
         <v>48</v>
@@ -12168,16 +12449,16 @@
     </row>
     <row r="67" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
-        <v>1170</v>
+        <v>1240</v>
       </c>
       <c r="B67" s="1">
         <v>6</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>955</v>
+        <v>1025</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>1171</v>
+        <v>1241</v>
       </c>
       <c r="E67" s="1" t="s">
         <v>48</v>
@@ -12198,22 +12479,22 @@
         <v>48</v>
       </c>
       <c r="K67" s="1" t="s">
-        <v>1172</v>
+        <v>1242</v>
       </c>
       <c r="L67" s="1" t="s">
-        <v>584</v>
+        <v>654</v>
       </c>
       <c r="M67" s="1" t="s">
-        <v>1173</v>
+        <v>1243</v>
       </c>
       <c r="N67" s="1" t="s">
-        <v>717</v>
+        <v>787</v>
       </c>
       <c r="O67" s="1" t="s">
-        <v>1174</v>
+        <v>1244</v>
       </c>
       <c r="P67" s="1" t="s">
-        <v>771</v>
+        <v>841</v>
       </c>
       <c r="Q67" s="1" t="s">
         <v>48</v>
@@ -12224,19 +12505,19 @@
     </row>
     <row r="68" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
-        <v>1175</v>
+        <v>1245</v>
       </c>
       <c r="B68" s="1">
         <v>6</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>955</v>
+        <v>1025</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>1176</v>
+        <v>1246</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>1177</v>
+        <v>1247</v>
       </c>
       <c r="F68" s="1">
         <v>2228</v>
@@ -12254,22 +12535,22 @@
         <v>48</v>
       </c>
       <c r="K68" s="1" t="s">
-        <v>1178</v>
+        <v>1248</v>
       </c>
       <c r="L68" s="1" t="s">
-        <v>598</v>
+        <v>668</v>
       </c>
       <c r="M68" s="1" t="s">
-        <v>1179</v>
+        <v>1249</v>
       </c>
       <c r="N68" s="1" t="s">
-        <v>1180</v>
+        <v>1250</v>
       </c>
       <c r="O68" s="1" t="s">
-        <v>1181</v>
+        <v>1251</v>
       </c>
       <c r="P68" s="1" t="s">
-        <v>567</v>
+        <v>637</v>
       </c>
       <c r="Q68" s="1" t="s">
         <v>48</v>
@@ -12280,16 +12561,16 @@
     </row>
     <row r="69" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="s">
-        <v>1182</v>
+        <v>1252</v>
       </c>
       <c r="B69" s="1">
         <v>6</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>941</v>
+        <v>1011</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>1183</v>
+        <v>1253</v>
       </c>
       <c r="E69" s="1" t="s">
         <v>48</v>
@@ -12336,19 +12617,19 @@
     </row>
     <row r="70" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
-        <v>1184</v>
+        <v>1254</v>
       </c>
       <c r="B70" s="1">
         <v>6</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>955</v>
+        <v>1025</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>1185</v>
+        <v>1255</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>1186</v>
+        <v>1256</v>
       </c>
       <c r="F70" s="1">
         <v>2231</v>
@@ -12366,22 +12647,22 @@
         <v>48</v>
       </c>
       <c r="K70" s="1" t="s">
-        <v>1187</v>
+        <v>1257</v>
       </c>
       <c r="L70" s="1" t="s">
-        <v>592</v>
+        <v>662</v>
       </c>
       <c r="M70" s="1" t="s">
-        <v>1188</v>
+        <v>1258</v>
       </c>
       <c r="N70" s="1" t="s">
-        <v>1038</v>
+        <v>1108</v>
       </c>
       <c r="O70" s="1" t="s">
-        <v>1189</v>
+        <v>1259</v>
       </c>
       <c r="P70" s="1" t="s">
-        <v>1190</v>
+        <v>1260</v>
       </c>
       <c r="Q70" s="1" t="s">
         <v>48</v>
@@ -12392,19 +12673,19 @@
     </row>
     <row r="71" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
-        <v>1191</v>
+        <v>1261</v>
       </c>
       <c r="B71" s="1">
         <v>6</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>947</v>
+        <v>1017</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>1192</v>
+        <v>1262</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>1193</v>
+        <v>1263</v>
       </c>
       <c r="F71" s="1">
         <v>2232</v>
@@ -12448,16 +12729,16 @@
     </row>
     <row r="72" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
-        <v>1194</v>
+        <v>1264</v>
       </c>
       <c r="B72" s="1">
         <v>6</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>941</v>
+        <v>1011</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>1195</v>
+        <v>1265</v>
       </c>
       <c r="E72" s="1" t="s">
         <v>48</v>
@@ -12504,16 +12785,16 @@
     </row>
     <row r="73" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
-        <v>1196</v>
+        <v>1266</v>
       </c>
       <c r="B73" s="1">
         <v>6</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>941</v>
+        <v>1011</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>1197</v>
+        <v>1267</v>
       </c>
       <c r="E73" s="1" t="s">
         <v>48</v>
@@ -12560,16 +12841,16 @@
     </row>
     <row r="74" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
-        <v>1198</v>
+        <v>1268</v>
       </c>
       <c r="B74" s="1">
         <v>6</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>955</v>
+        <v>1025</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>1199</v>
+        <v>1269</v>
       </c>
       <c r="E74" s="1" t="s">
         <v>48</v>
@@ -12590,22 +12871,22 @@
         <v>48</v>
       </c>
       <c r="K74" s="1" t="s">
-        <v>1200</v>
+        <v>1270</v>
       </c>
       <c r="L74" s="1" t="s">
-        <v>598</v>
+        <v>668</v>
       </c>
       <c r="M74" s="1" t="s">
-        <v>1201</v>
+        <v>1271</v>
       </c>
       <c r="N74" s="1" t="s">
-        <v>1202</v>
+        <v>1272</v>
       </c>
       <c r="O74" s="1" t="s">
-        <v>1203</v>
+        <v>1273</v>
       </c>
       <c r="P74" s="1" t="s">
-        <v>627</v>
+        <v>697</v>
       </c>
       <c r="Q74" s="1" t="s">
         <v>48</v>
@@ -12616,16 +12897,16 @@
     </row>
     <row r="75" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="s">
-        <v>1204</v>
+        <v>1274</v>
       </c>
       <c r="B75" s="1">
         <v>6</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>941</v>
+        <v>1011</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>1205</v>
+        <v>1275</v>
       </c>
       <c r="E75" s="1" t="s">
         <v>48</v>
@@ -12672,16 +12953,16 @@
     </row>
     <row r="76" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
-        <v>1206</v>
+        <v>1276</v>
       </c>
       <c r="B76" s="1">
         <v>6</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>955</v>
+        <v>1025</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>1207</v>
+        <v>1277</v>
       </c>
       <c r="E76" s="1" t="s">
         <v>48</v>
@@ -12702,22 +12983,22 @@
         <v>48</v>
       </c>
       <c r="K76" s="1" t="s">
-        <v>1208</v>
+        <v>1278</v>
       </c>
       <c r="L76" s="1" t="s">
-        <v>1209</v>
+        <v>1279</v>
       </c>
       <c r="M76" s="1" t="s">
-        <v>1210</v>
+        <v>1280</v>
       </c>
       <c r="N76" s="1" t="s">
-        <v>555</v>
+        <v>625</v>
       </c>
       <c r="O76" s="1" t="s">
-        <v>1211</v>
+        <v>1281</v>
       </c>
       <c r="P76" s="1" t="s">
-        <v>565</v>
+        <v>635</v>
       </c>
       <c r="Q76" s="1" t="s">
         <v>48</v>
@@ -12728,16 +13009,16 @@
     </row>
     <row r="77" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A77" s="1" t="s">
-        <v>1212</v>
+        <v>1282</v>
       </c>
       <c r="B77" s="1">
         <v>6</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>941</v>
+        <v>1011</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>1213</v>
+        <v>1283</v>
       </c>
       <c r="E77" s="1" t="s">
         <v>48</v>
@@ -12784,19 +13065,19 @@
     </row>
     <row r="78" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A78" s="1" t="s">
-        <v>1214</v>
+        <v>1284</v>
       </c>
       <c r="B78" s="1">
         <v>7</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>947</v>
+        <v>1017</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>1215</v>
+        <v>1285</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>976</v>
+        <v>1046</v>
       </c>
       <c r="F78" s="1">
         <v>2261</v>
@@ -12840,19 +13121,19 @@
     </row>
     <row r="79" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A79" s="1" t="s">
-        <v>1216</v>
+        <v>1286</v>
       </c>
       <c r="B79" s="1">
         <v>7</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>955</v>
+        <v>1025</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>1217</v>
+        <v>1287</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>1218</v>
+        <v>1288</v>
       </c>
       <c r="F79" s="1">
         <v>2275</v>
@@ -12870,22 +13151,22 @@
         <v>48</v>
       </c>
       <c r="K79" s="1" t="s">
-        <v>1219</v>
+        <v>1289</v>
       </c>
       <c r="L79" s="1" t="s">
-        <v>592</v>
+        <v>662</v>
       </c>
       <c r="M79" s="1" t="s">
-        <v>1220</v>
+        <v>1290</v>
       </c>
       <c r="N79" s="1" t="s">
-        <v>1221</v>
+        <v>1291</v>
       </c>
       <c r="O79" s="1" t="s">
-        <v>1222</v>
+        <v>1292</v>
       </c>
       <c r="P79" s="1" t="s">
-        <v>598</v>
+        <v>668</v>
       </c>
       <c r="Q79" s="1" t="s">
         <v>48</v>
@@ -12896,16 +13177,16 @@
     </row>
     <row r="80" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A80" s="1" t="s">
-        <v>1223</v>
+        <v>1293</v>
       </c>
       <c r="B80" s="1">
         <v>7</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>955</v>
+        <v>1025</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>1224</v>
+        <v>1294</v>
       </c>
       <c r="E80" s="1" t="s">
         <v>48</v>
@@ -12926,22 +13207,22 @@
         <v>48</v>
       </c>
       <c r="K80" s="1" t="s">
-        <v>1225</v>
+        <v>1295</v>
       </c>
       <c r="L80" s="1" t="s">
-        <v>1226</v>
+        <v>1296</v>
       </c>
       <c r="M80" s="1" t="s">
-        <v>1227</v>
+        <v>1297</v>
       </c>
       <c r="N80" s="1" t="s">
-        <v>598</v>
+        <v>668</v>
       </c>
       <c r="O80" s="1" t="s">
-        <v>1228</v>
+        <v>1298</v>
       </c>
       <c r="P80" s="1" t="s">
-        <v>771</v>
+        <v>841</v>
       </c>
       <c r="Q80" s="1" t="s">
         <v>48</v>
@@ -12952,16 +13233,16 @@
     </row>
     <row r="81" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="s">
-        <v>1229</v>
+        <v>1299</v>
       </c>
       <c r="B81" s="1">
         <v>7</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>941</v>
+        <v>1011</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>1230</v>
+        <v>1300</v>
       </c>
       <c r="E81" s="1" t="s">
         <v>48</v>
@@ -13008,16 +13289,16 @@
     </row>
     <row r="82" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A82" s="1" t="s">
-        <v>1231</v>
+        <v>1301</v>
       </c>
       <c r="B82" s="1">
         <v>7</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>955</v>
+        <v>1025</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>1232</v>
+        <v>1302</v>
       </c>
       <c r="E82" s="1" t="s">
         <v>48</v>
@@ -13038,22 +13319,22 @@
         <v>48</v>
       </c>
       <c r="K82" s="1" t="s">
-        <v>1233</v>
+        <v>1303</v>
       </c>
       <c r="L82" s="1" t="s">
-        <v>1234</v>
+        <v>1304</v>
       </c>
       <c r="M82" s="1" t="s">
-        <v>1235</v>
+        <v>1305</v>
       </c>
       <c r="N82" s="1" t="s">
-        <v>1236</v>
+        <v>1306</v>
       </c>
       <c r="O82" s="1" t="s">
-        <v>1237</v>
+        <v>1307</v>
       </c>
       <c r="P82" s="1" t="s">
-        <v>584</v>
+        <v>654</v>
       </c>
       <c r="Q82" s="1" t="s">
         <v>48</v>
@@ -13064,16 +13345,16 @@
     </row>
     <row r="83" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A83" s="1" t="s">
-        <v>1238</v>
+        <v>1308</v>
       </c>
       <c r="B83" s="1">
         <v>7</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>955</v>
+        <v>1025</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>1239</v>
+        <v>1309</v>
       </c>
       <c r="E83" s="1" t="s">
         <v>48</v>
@@ -13094,22 +13375,22 @@
         <v>48</v>
       </c>
       <c r="K83" s="1" t="s">
-        <v>1240</v>
+        <v>1310</v>
       </c>
       <c r="L83" s="1" t="s">
-        <v>598</v>
+        <v>668</v>
       </c>
       <c r="M83" s="1" t="s">
-        <v>1241</v>
+        <v>1311</v>
       </c>
       <c r="N83" s="1" t="s">
-        <v>1242</v>
+        <v>1312</v>
       </c>
       <c r="O83" s="1" t="s">
-        <v>1243</v>
+        <v>1313</v>
       </c>
       <c r="P83" s="1" t="s">
-        <v>1244</v>
+        <v>1314</v>
       </c>
       <c r="Q83" s="1" t="s">
         <v>48</v>
@@ -13120,16 +13401,16 @@
     </row>
     <row r="84" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A84" s="1" t="s">
-        <v>1245</v>
+        <v>1315</v>
       </c>
       <c r="B84" s="1">
         <v>7</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>941</v>
+        <v>1011</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>1246</v>
+        <v>1316</v>
       </c>
       <c r="E84" s="1" t="s">
         <v>48</v>
@@ -13176,16 +13457,16 @@
     </row>
     <row r="85" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A85" s="1" t="s">
-        <v>1247</v>
+        <v>1317</v>
       </c>
       <c r="B85" s="1">
         <v>7</v>
       </c>
       <c r="C85" s="1" t="s">
-        <v>941</v>
+        <v>1011</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>1248</v>
+        <v>1318</v>
       </c>
       <c r="E85" s="1" t="s">
         <v>48</v>
@@ -13232,16 +13513,16 @@
     </row>
     <row r="86" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A86" s="1" t="s">
-        <v>1249</v>
+        <v>1319</v>
       </c>
       <c r="B86" s="1">
         <v>7</v>
       </c>
       <c r="C86" s="1" t="s">
-        <v>955</v>
+        <v>1025</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>1250</v>
+        <v>1320</v>
       </c>
       <c r="E86" s="1" t="s">
         <v>48</v>
@@ -13262,22 +13543,22 @@
         <v>48</v>
       </c>
       <c r="K86" s="1" t="s">
-        <v>1251</v>
+        <v>1321</v>
       </c>
       <c r="L86" s="1" t="s">
-        <v>557</v>
+        <v>627</v>
       </c>
       <c r="M86" s="1" t="s">
-        <v>1252</v>
+        <v>1322</v>
       </c>
       <c r="N86" s="1" t="s">
-        <v>1234</v>
+        <v>1304</v>
       </c>
       <c r="O86" s="1" t="s">
-        <v>1253</v>
+        <v>1323</v>
       </c>
       <c r="P86" s="1" t="s">
-        <v>1254</v>
+        <v>1324</v>
       </c>
       <c r="Q86" s="1" t="s">
         <v>48</v>
@@ -13288,16 +13569,16 @@
     </row>
     <row r="87" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A87" s="1" t="s">
-        <v>1255</v>
+        <v>1325</v>
       </c>
       <c r="B87" s="1">
         <v>7</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>941</v>
+        <v>1011</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>1256</v>
+        <v>1326</v>
       </c>
       <c r="E87" s="1" t="s">
         <v>48</v>
@@ -13344,16 +13625,16 @@
     </row>
     <row r="88" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A88" s="1" t="s">
-        <v>1257</v>
+        <v>1327</v>
       </c>
       <c r="B88" s="1">
         <v>7</v>
       </c>
       <c r="C88" s="1" t="s">
-        <v>947</v>
+        <v>1017</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>1258</v>
+        <v>1328</v>
       </c>
       <c r="E88" s="1" t="s">
         <v>48</v>
@@ -13400,19 +13681,19 @@
     </row>
     <row r="89" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A89" s="1" t="s">
-        <v>1259</v>
+        <v>1329</v>
       </c>
       <c r="B89" s="1">
         <v>7</v>
       </c>
       <c r="C89" s="1" t="s">
-        <v>955</v>
+        <v>1025</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>1260</v>
+        <v>1330</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>1261</v>
+        <v>1331</v>
       </c>
       <c r="F89" s="1">
         <v>2304</v>
@@ -13430,22 +13711,22 @@
         <v>48</v>
       </c>
       <c r="K89" s="1" t="s">
-        <v>1262</v>
+        <v>1332</v>
       </c>
       <c r="L89" s="1" t="s">
-        <v>1263</v>
+        <v>1333</v>
       </c>
       <c r="M89" s="1" t="s">
-        <v>1264</v>
+        <v>1334</v>
       </c>
       <c r="N89" s="1" t="s">
-        <v>1265</v>
+        <v>1335</v>
       </c>
       <c r="O89" s="1" t="s">
-        <v>1266</v>
+        <v>1336</v>
       </c>
       <c r="P89" s="1" t="s">
-        <v>1267</v>
+        <v>1337</v>
       </c>
       <c r="Q89" s="1" t="s">
         <v>48</v>
@@ -13456,19 +13737,19 @@
     </row>
     <row r="90" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A90" s="1" t="s">
-        <v>1268</v>
+        <v>1338</v>
       </c>
       <c r="B90" s="1">
         <v>7</v>
       </c>
       <c r="C90" s="1" t="s">
-        <v>947</v>
+        <v>1017</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>1269</v>
+        <v>1339</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>1270</v>
+        <v>1340</v>
       </c>
       <c r="F90" s="1">
         <v>2308</v>
@@ -13512,19 +13793,19 @@
     </row>
     <row r="91" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
-        <v>1271</v>
+        <v>1341</v>
       </c>
       <c r="B91" s="1">
         <v>7</v>
       </c>
       <c r="C91" s="1" t="s">
-        <v>941</v>
+        <v>1011</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>1272</v>
+        <v>1342</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>1273</v>
+        <v>1343</v>
       </c>
       <c r="F91" s="1">
         <v>2310</v>
@@ -13585,7 +13866,7 @@
   <sheetData>
     <row r="1" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>1274</v>
+        <v>1344</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
@@ -13593,16 +13874,16 @@
     </row>
     <row r="2" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
-        <v>1275</v>
+        <v>1345</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>1276</v>
+        <v>1346</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>832</v>
+        <v>902</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>833</v>
+        <v>903</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -13610,13 +13891,13 @@
         <v>1</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>1277</v>
+        <v>1347</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>1278</v>
+        <v>1348</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>1279</v>
+        <v>1349</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -13624,13 +13905,13 @@
         <v>2</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>1280</v>
+        <v>1350</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>1281</v>
+        <v>1351</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>1282</v>
+        <v>1352</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -13638,13 +13919,13 @@
         <v>3</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>1283</v>
+        <v>1353</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>1284</v>
+        <v>1354</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>1285</v>
+        <v>1355</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -13652,13 +13933,13 @@
         <v>4</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>1286</v>
+        <v>1356</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>1287</v>
+        <v>1357</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>1288</v>
+        <v>1358</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -13666,13 +13947,13 @@
         <v>5</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>1289</v>
+        <v>1359</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>1290</v>
+        <v>1360</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>1291</v>
+        <v>1361</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -13680,13 +13961,13 @@
         <v>6</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>1292</v>
+        <v>1362</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>1293</v>
+        <v>1363</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>1294</v>
+        <v>1364</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -13694,13 +13975,13 @@
         <v>7</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>1295</v>
+        <v>1365</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>1296</v>
+        <v>1366</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>1297</v>
+        <v>1367</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -13708,13 +13989,13 @@
         <v>8</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>1298</v>
+        <v>1368</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>1299</v>
+        <v>1369</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>1300</v>
+        <v>1370</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -13722,13 +14003,13 @@
         <v>9</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>1301</v>
+        <v>1371</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>1302</v>
+        <v>1372</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>1303</v>
+        <v>1373</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -13736,13 +14017,13 @@
         <v>10</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>1304</v>
+        <v>1374</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>1305</v>
+        <v>1375</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>1306</v>
+        <v>1376</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -13750,13 +14031,13 @@
         <v>11</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>1307</v>
+        <v>1377</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>1308</v>
+        <v>1378</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>1309</v>
+        <v>1379</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -13764,13 +14045,13 @@
         <v>12</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>1310</v>
+        <v>1380</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>1311</v>
+        <v>1381</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>1312</v>
+        <v>1382</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -13778,13 +14059,13 @@
         <v>13</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>1313</v>
+        <v>1383</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>1314</v>
+        <v>1384</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>1315</v>
+        <v>1385</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -13792,13 +14073,13 @@
         <v>14</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>1316</v>
+        <v>1386</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>1317</v>
+        <v>1387</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>1318</v>
+        <v>1388</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
@@ -13806,13 +14087,13 @@
         <v>15</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>1319</v>
+        <v>1389</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>1320</v>
+        <v>1390</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>1321</v>
+        <v>1391</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
@@ -13820,13 +14101,13 @@
         <v>16</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>1322</v>
+        <v>1392</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>1323</v>
+        <v>1393</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>1324</v>
+        <v>1394</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -13834,13 +14115,13 @@
         <v>17</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>1325</v>
+        <v>1395</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>1326</v>
+        <v>1396</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>1327</v>
+        <v>1397</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -13848,13 +14129,13 @@
         <v>18</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>1328</v>
+        <v>1398</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>1329</v>
+        <v>1399</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>1330</v>
+        <v>1400</v>
       </c>
     </row>
   </sheetData>
@@ -13876,7 +14157,7 @@
   <sheetData>
     <row r="1" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>1331</v>
+        <v>1401</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
@@ -13885,16 +14166,16 @@
     </row>
     <row r="2" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
-        <v>541</v>
+        <v>611</v>
       </c>
       <c r="B2" s="5" t="s">
         <v>291</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>1332</v>
+        <v>1402</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>1333</v>
+        <v>1403</v>
       </c>
       <c r="E2" s="5" t="s">
         <v>295</v>
@@ -13902,33 +14183,33 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>1334</v>
+        <v>1404</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>1335</v>
+        <v>1405</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>1336</v>
+        <v>1406</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>1337</v>
+        <v>1407</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>1338</v>
+        <v>1408</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>1339</v>
+        <v>1409</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>1340</v>
+        <v>1410</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>1341</v>
+        <v>1411</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>1342</v>
+        <v>1412</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>48</v>
@@ -13936,53 +14217,53 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>1343</v>
+        <v>1413</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>1344</v>
+        <v>1414</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>1345</v>
+        <v>1415</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>1346</v>
+        <v>1416</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>1347</v>
+        <v>1417</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>1348</v>
+        <v>1418</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>1349</v>
+        <v>1419</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>1350</v>
+        <v>1420</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>1351</v>
+        <v>1421</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>1352</v>
+        <v>1422</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>1353</v>
+        <v>1423</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>1354</v>
+        <v>1424</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>1355</v>
+        <v>1425</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>1356</v>
+        <v>1426</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>1357</v>
+        <v>1427</v>
       </c>
     </row>
   </sheetData>
@@ -17658,14 +17939,15 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E32"/>
+  <dimension ref="A1:F32"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="3" width="10" style="1" customWidth="1"/>
     <col min="4" max="5" width="12" style="1" customWidth="1"/>
+    <col min="6" max="6" width="13" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>314</v>
       </c>
@@ -17673,8 +17955,9 @@
       <c r="C1" s="3"/>
       <c r="D1" s="3"/>
       <c r="E1" s="3"/>
-    </row>
-    <row r="2" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="F1" s="3"/>
+    </row>
+    <row r="2" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
         <v>50</v>
       </c>
@@ -17690,8 +17973,11 @@
       <c r="E2" s="5" t="s">
         <v>316</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F2" s="5" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>34</v>
       </c>
@@ -17699,16 +17985,19 @@
         <v>1</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="E3" s="1">
         <v>0.35</v>
       </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F3" s="1" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>34</v>
       </c>
@@ -17716,16 +18005,19 @@
         <v>2</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="E4" s="1">
         <v>1.8</v>
       </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F4" s="1" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>34</v>
       </c>
@@ -17733,16 +18025,19 @@
         <v>3</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="E5" s="1">
         <v>9</v>
       </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F5" s="1" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>34</v>
       </c>
@@ -17750,16 +18045,19 @@
         <v>4</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="E6" s="1">
         <v>45</v>
       </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F6" s="1" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>34</v>
       </c>
@@ -17767,16 +18065,19 @@
         <v>5</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>325</v>
+        <v>330</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>326</v>
+        <v>331</v>
       </c>
       <c r="E7" s="1">
         <v>220</v>
       </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F7" s="1" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>36</v>
       </c>
@@ -17784,16 +18085,19 @@
         <v>1</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>327</v>
+        <v>333</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>328</v>
+        <v>334</v>
       </c>
       <c r="E8" s="1">
         <v>0.35</v>
       </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F8" s="1" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>36</v>
       </c>
@@ -17801,16 +18105,19 @@
         <v>2</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>329</v>
+        <v>336</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>330</v>
+        <v>337</v>
       </c>
       <c r="E9" s="1">
         <v>1.8</v>
       </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F9" s="1" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>36</v>
       </c>
@@ -17818,16 +18125,19 @@
         <v>3</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>331</v>
+        <v>339</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>332</v>
+        <v>340</v>
       </c>
       <c r="E10" s="1">
         <v>9</v>
       </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F10" s="1" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>36</v>
       </c>
@@ -17835,16 +18145,19 @@
         <v>4</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>333</v>
+        <v>342</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>334</v>
+        <v>343</v>
       </c>
       <c r="E11" s="1">
         <v>45</v>
       </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F11" s="1" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>36</v>
       </c>
@@ -17852,16 +18165,19 @@
         <v>5</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>335</v>
+        <v>345</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>336</v>
+        <v>346</v>
       </c>
       <c r="E12" s="1">
         <v>220</v>
       </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F12" s="1" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>38</v>
       </c>
@@ -17869,16 +18185,19 @@
         <v>1</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>337</v>
+        <v>348</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>338</v>
+        <v>349</v>
       </c>
       <c r="E13" s="1">
         <v>0.35</v>
       </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F13" s="1" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>38</v>
       </c>
@@ -17886,16 +18205,19 @@
         <v>2</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>339</v>
+        <v>351</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>340</v>
+        <v>352</v>
       </c>
       <c r="E14" s="1">
         <v>1.8</v>
       </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F14" s="1" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>38</v>
       </c>
@@ -17903,16 +18225,19 @@
         <v>3</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>341</v>
+        <v>354</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>342</v>
+        <v>355</v>
       </c>
       <c r="E15" s="1">
         <v>9</v>
       </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F15" s="1" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>38</v>
       </c>
@@ -17920,16 +18245,19 @@
         <v>4</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>343</v>
+        <v>357</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>344</v>
+        <v>358</v>
       </c>
       <c r="E16" s="1">
         <v>45</v>
       </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F16" s="1" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>38</v>
       </c>
@@ -17937,16 +18265,19 @@
         <v>5</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>345</v>
+        <v>360</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>346</v>
+        <v>361</v>
       </c>
       <c r="E17" s="1">
         <v>220</v>
       </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F17" s="1" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>40</v>
       </c>
@@ -17954,16 +18285,19 @@
         <v>1</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>347</v>
+        <v>363</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>348</v>
+        <v>364</v>
       </c>
       <c r="E18" s="1">
         <v>0.35</v>
       </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F18" s="1" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>40</v>
       </c>
@@ -17971,16 +18305,19 @@
         <v>2</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>349</v>
+        <v>366</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>350</v>
+        <v>367</v>
       </c>
       <c r="E19" s="1">
         <v>1.8</v>
       </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F19" s="1" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>40</v>
       </c>
@@ -17988,16 +18325,19 @@
         <v>3</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>351</v>
+        <v>369</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>352</v>
+        <v>370</v>
       </c>
       <c r="E20" s="1">
         <v>9</v>
       </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F20" s="1" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>40</v>
       </c>
@@ -18005,16 +18345,19 @@
         <v>4</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>353</v>
+        <v>372</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>354</v>
+        <v>373</v>
       </c>
       <c r="E21" s="1">
         <v>45</v>
       </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F21" s="1" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
         <v>40</v>
       </c>
@@ -18022,16 +18365,19 @@
         <v>5</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>355</v>
+        <v>375</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>356</v>
+        <v>376</v>
       </c>
       <c r="E22" s="1">
         <v>220</v>
       </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F22" s="1" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
         <v>42</v>
       </c>
@@ -18039,16 +18385,19 @@
         <v>1</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>357</v>
+        <v>378</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>358</v>
+        <v>379</v>
       </c>
       <c r="E23" s="1">
         <v>0.35</v>
       </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F23" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
         <v>42</v>
       </c>
@@ -18056,16 +18405,19 @@
         <v>2</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>359</v>
+        <v>381</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>360</v>
+        <v>382</v>
       </c>
       <c r="E24" s="1">
         <v>1.8</v>
       </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F24" s="1" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
         <v>42</v>
       </c>
@@ -18073,16 +18425,19 @@
         <v>3</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>361</v>
+        <v>384</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>362</v>
+        <v>385</v>
       </c>
       <c r="E25" s="1">
         <v>9</v>
       </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F25" s="1" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
         <v>42</v>
       </c>
@@ -18090,16 +18445,19 @@
         <v>4</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>363</v>
+        <v>387</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>364</v>
+        <v>388</v>
       </c>
       <c r="E26" s="1">
         <v>45</v>
       </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F26" s="1" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
         <v>42</v>
       </c>
@@ -18107,16 +18465,19 @@
         <v>5</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>365</v>
+        <v>390</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>366</v>
+        <v>391</v>
       </c>
       <c r="E27" s="1">
         <v>220</v>
       </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F27" s="1" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
         <v>44</v>
       </c>
@@ -18124,16 +18485,19 @@
         <v>1</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>367</v>
+        <v>393</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>368</v>
+        <v>394</v>
       </c>
       <c r="E28" s="1">
         <v>0.35</v>
       </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F28" s="1" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
         <v>44</v>
       </c>
@@ -18141,16 +18505,19 @@
         <v>2</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>369</v>
+        <v>396</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>370</v>
+        <v>397</v>
       </c>
       <c r="E29" s="1">
         <v>1.8</v>
       </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F29" s="1" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
         <v>44</v>
       </c>
@@ -18158,16 +18525,19 @@
         <v>3</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>371</v>
+        <v>399</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>372</v>
+        <v>400</v>
       </c>
       <c r="E30" s="1">
         <v>9</v>
       </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F30" s="1" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
         <v>44</v>
       </c>
@@ -18175,16 +18545,19 @@
         <v>4</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>373</v>
+        <v>402</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>374</v>
+        <v>403</v>
       </c>
       <c r="E31" s="1">
         <v>45</v>
       </c>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F31" s="1" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
         <v>44</v>
       </c>
@@ -18192,13 +18565,16 @@
         <v>5</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>375</v>
+        <v>405</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>376</v>
+        <v>406</v>
       </c>
       <c r="E32" s="1">
         <v>220</v>
+      </c>
+      <c r="F32" s="1" t="s">
+        <v>407</v>
       </c>
     </row>
   </sheetData>
@@ -18209,22 +18585,24 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D8"/>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="2" width="10" style="1" customWidth="1"/>
     <col min="3" max="4" width="12" style="1" customWidth="1"/>
+    <col min="5" max="5" width="13" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>377</v>
+        <v>408</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
       <c r="D1" s="3"/>
-    </row>
-    <row r="2" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E1" s="3"/>
+    </row>
+    <row r="2" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
         <v>315</v>
       </c>
@@ -18237,89 +18615,110 @@
       <c r="D2" s="5" t="s">
         <v>316</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E2" s="5" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>1</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>378</v>
+        <v>409</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>379</v>
+        <v>410</v>
       </c>
       <c r="D3" s="1">
         <v>0.6</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E3" s="1" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>2</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>380</v>
+        <v>412</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>381</v>
+        <v>413</v>
       </c>
       <c r="D4" s="1">
         <v>2.6</v>
       </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E4" s="1" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>3</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>382</v>
+        <v>415</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>383</v>
+        <v>416</v>
       </c>
       <c r="D5" s="1">
         <v>11</v>
       </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E5" s="1" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>4</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>384</v>
+        <v>418</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>385</v>
+        <v>419</v>
       </c>
       <c r="D6" s="1">
         <v>42</v>
       </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E6" s="1" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>5</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>386</v>
+        <v>421</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>387</v>
+        <v>422</v>
       </c>
       <c r="D7" s="1">
         <v>160</v>
       </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E7" s="1" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>6</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>388</v>
+        <v>424</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>389</v>
+        <v>425</v>
       </c>
       <c r="D8" s="1">
         <v>600</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>426</v>
       </c>
     </row>
   </sheetData>
@@ -18330,22 +18729,24 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D8"/>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="2" width="10" style="1" customWidth="1"/>
     <col min="3" max="4" width="12" style="1" customWidth="1"/>
+    <col min="5" max="5" width="13" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>377</v>
+        <v>408</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
       <c r="D1" s="3"/>
-    </row>
-    <row r="2" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E1" s="3"/>
+    </row>
+    <row r="2" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
         <v>315</v>
       </c>
@@ -18358,89 +18759,110 @@
       <c r="D2" s="5" t="s">
         <v>316</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E2" s="5" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>1</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>390</v>
+        <v>427</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>391</v>
+        <v>428</v>
       </c>
       <c r="D3" s="1">
         <v>0.6</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E3" s="1" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>2</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>392</v>
+        <v>430</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>393</v>
+        <v>431</v>
       </c>
       <c r="D4" s="1">
         <v>2.6</v>
       </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E4" s="1" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>3</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>394</v>
+        <v>433</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>395</v>
+        <v>434</v>
       </c>
       <c r="D5" s="1">
         <v>11</v>
       </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E5" s="1" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>4</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>396</v>
+        <v>436</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>397</v>
+        <v>437</v>
       </c>
       <c r="D6" s="1">
         <v>42</v>
       </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E6" s="1" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>5</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>398</v>
+        <v>439</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>399</v>
+        <v>440</v>
       </c>
       <c r="D7" s="1">
         <v>160</v>
       </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E7" s="1" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>6</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>400</v>
+        <v>442</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>401</v>
+        <v>443</v>
       </c>
       <c r="D8" s="1">
         <v>600</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>444</v>
       </c>
     </row>
   </sheetData>
@@ -18451,15 +18873,16 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="3" width="10" style="1" customWidth="1"/>
     <col min="4" max="4" width="12" style="1" customWidth="1"/>
     <col min="5" max="5" width="11" style="1" customWidth="1"/>
+    <col min="6" max="6" width="13" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>48</v>
       </c>
@@ -18467,8 +18890,9 @@
       <c r="C1" s="3"/>
       <c r="D1" s="3"/>
       <c r="E1" s="3"/>
-    </row>
-    <row r="2" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="F1" s="3"/>
+    </row>
+    <row r="2" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
         <v>315</v>
       </c>
@@ -18476,24 +18900,27 @@
         <v>291</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>402</v>
+        <v>445</v>
       </c>
       <c r="D2" s="5" t="s">
         <v>316</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>403</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+        <v>446</v>
+      </c>
+      <c r="F2" s="5" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>1</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>404</v>
+        <v>447</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>405</v>
+        <v>448</v>
       </c>
       <c r="D3" s="1">
         <v>0.015</v>
@@ -18501,16 +18928,19 @@
       <c r="E3" s="1">
         <v>5</v>
       </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F3" s="1" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>2</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>406</v>
+        <v>450</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>407</v>
+        <v>451</v>
       </c>
       <c r="D4" s="1">
         <v>0.06</v>
@@ -18518,16 +18948,19 @@
       <c r="E4" s="1">
         <v>15</v>
       </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F4" s="1" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>3</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>408</v>
+        <v>453</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>409</v>
+        <v>454</v>
       </c>
       <c r="D5" s="1">
         <v>0.25</v>
@@ -18535,16 +18968,19 @@
       <c r="E5" s="1">
         <v>30</v>
       </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F5" s="1" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>4</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>410</v>
+        <v>456</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>411</v>
+        <v>457</v>
       </c>
       <c r="D6" s="1">
         <v>0.8</v>
@@ -18552,22 +18988,28 @@
       <c r="E6" s="1">
         <v>60</v>
       </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F6" s="1" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>5</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>412</v>
+        <v>459</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>413</v>
+        <v>460</v>
       </c>
       <c r="D7" s="1">
         <v>3.2</v>
       </c>
       <c r="E7" s="1">
         <v>120</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>461</v>
       </c>
     </row>
   </sheetData>

--- a/content.xlsx
+++ b/content.xlsx
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3130" uniqueCount="1434">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3499" uniqueCount="1630">
   <si>
     <t>เนื้อหาเกมอโยธยา Idle — แก้ในไฟล์นี้แล้วรัน npm run xlsx:import เพื่อเขียนกลับเป็น data/*.json</t>
   </si>
@@ -3059,6 +3059,594 @@
   </si>
   <si>
     <t>พละกำลัง-2, หลบหลีก-1</t>
+  </si>
+  <si>
+    <t>G14</t>
+  </si>
+  <si>
+    <t>พระธุดงค์มาปักกลดชายหมู่บ้าน</t>
+  </si>
+  <si>
+    <t>ถวายภัตตาหาร</t>
+  </si>
+  <si>
+    <t>ขอเรียนธรรมะ</t>
+  </si>
+  <si>
+    <t>ความรู้+1, ไสยเวทย์+1</t>
+  </si>
+  <si>
+    <t>ขอเครื่องรางของขลัง</t>
+  </si>
+  <si>
+    <t>ขอติดตามธุดงค์หนึ่งพรรษา</t>
+  </si>
+  <si>
+    <t>ไสยเวทย์+4, บารมี+2, บุญ+3</t>
+  </si>
+  <si>
+    <t>พละกำลัง-1, โภคทรัพย์-1</t>
+  </si>
+  <si>
+    <t>G15</t>
+  </si>
+  <si>
+    <t>สำเภาจีนเข้าเทียบท่า</t>
+  </si>
+  <si>
+    <t>ไปดูสินค้าแปลกตา</t>
+  </si>
+  <si>
+    <t>รับจ้างขนสินค้า</t>
+  </si>
+  <si>
+    <t>ซื้อของมาขายต่อ</t>
+  </si>
+  <si>
+    <t>ฝากสินค้าไปกับสำเภาเที่ยวหน้า</t>
+  </si>
+  <si>
+    <t>G16</t>
+  </si>
+  <si>
+    <t>เจอถุงเงินตกอยู่กลางตลาด</t>
+  </si>
+  <si>
+    <t>ประกาศหาเจ้าของ</t>
+  </si>
+  <si>
+    <t>เก็บไว้เอง</t>
+  </si>
+  <si>
+    <t>โภคทรัพย์+2, บาป+2</t>
+  </si>
+  <si>
+    <t>นำไปถวายวัด</t>
+  </si>
+  <si>
+    <t>บารมี+1, ไสยเวทย์+1</t>
+  </si>
+  <si>
+    <t>G17</t>
+  </si>
+  <si>
+    <t>นักเลงหัวไม้ท้าตีกัน</t>
+  </si>
+  <si>
+    <t>ตอบโต้ไม่ยอมใคร</t>
+  </si>
+  <si>
+    <t>เลี่ยงออกไปเงียบๆ</t>
+  </si>
+  <si>
+    <t>เจรจาให้เลิกรา</t>
+  </si>
+  <si>
+    <t>ไหวพริบ+1, บารมี+1</t>
+  </si>
+  <si>
+    <t>ท้าดวลต่อหน้าคนทั้งตลาด</t>
+  </si>
+  <si>
+    <t>ต่อสู้+4, บารมี+2</t>
+  </si>
+  <si>
+    <t>G18</t>
+  </si>
+  <si>
+    <t>น้ำหลากท่วมทุ่ง</t>
+  </si>
+  <si>
+    <t>ช่วยเพื่อนบ้านขนของหนีน้ำ</t>
+  </si>
+  <si>
+    <t>พละกำลัง+1, บารมี+1</t>
+  </si>
+  <si>
+    <t>ย้ายของขึ้นที่สูงก่อนใคร</t>
+  </si>
+  <si>
+    <t>ออกเรือหาปลาช่วงน้ำมาก</t>
+  </si>
+  <si>
+    <t>พายเรือฝ่ากระแสช่วยคนติดค้าง</t>
+  </si>
+  <si>
+    <t>บารมี+4, บุญ+2</t>
+  </si>
+  <si>
+    <t>G19</t>
+  </si>
+  <si>
+    <t>หมอยาเร่มาขายยาวิเศษ</t>
+  </si>
+  <si>
+    <t>ซื้อมาลองใช้</t>
+  </si>
+  <si>
+    <t>ขอเรียนตำรับยา</t>
+  </si>
+  <si>
+    <t>จับพิรุธว่าเป็นของปลอม</t>
+  </si>
+  <si>
+    <t>ซื้อตำรับลับทั้งหมด</t>
+  </si>
+  <si>
+    <t>ความรู้+3, ไสยเวทย์+3</t>
+  </si>
+  <si>
+    <t>G20</t>
+  </si>
+  <si>
+    <t>งานบวชลูกชายผู้ใหญ่บ้าน</t>
+  </si>
+  <si>
+    <t>ช่วยแห่นาครอบโบสถ์</t>
+  </si>
+  <si>
+    <t>ร่วมทำบุญ</t>
+  </si>
+  <si>
+    <t>ช่วยงานครัว</t>
+  </si>
+  <si>
+    <t>ไหวพริบ+1, พละกำลัง+1</t>
+  </si>
+  <si>
+    <t>G21</t>
+  </si>
+  <si>
+    <t>ถูกเกณฑ์ไปขุดคลอง</t>
+  </si>
+  <si>
+    <t>ทำงานเต็มแรง</t>
+  </si>
+  <si>
+    <t>ติดสินบนให้คนอื่นทำแทน</t>
+  </si>
+  <si>
+    <t>หลบหลีก+2, บาป+1</t>
+  </si>
+  <si>
+    <t>ช่วยคุมแรงงานให้เป็นระเบียบ</t>
+  </si>
+  <si>
+    <t>บารมี+1, ความรู้+1</t>
+  </si>
+  <si>
+    <t>หนีเกณฑ์กลางดึก</t>
+  </si>
+  <si>
+    <t>หลบหลีก+4, บาป+1</t>
+  </si>
+  <si>
+    <t>G22</t>
+  </si>
+  <si>
+    <t>บ่อนไก่ชนประจำหมู่บ้าน</t>
+  </si>
+  <si>
+    <t>ไปดูเฉยๆ</t>
+  </si>
+  <si>
+    <t>ไหวพริบ+1</t>
+  </si>
+  <si>
+    <t>เลี้ยงไก่ชนของตัวเอง</t>
+  </si>
+  <si>
+    <t>พละกำลัง+1, ไหวพริบ+1</t>
+  </si>
+  <si>
+    <t>ไม่ยุ่งเกี่ยวกับการพนัน</t>
+  </si>
+  <si>
+    <t>ทุ่มเงินแทงไก่ตัวเต็ง</t>
+  </si>
+  <si>
+    <t>โภคทรัพย์+4, บาป+1</t>
+  </si>
+  <si>
+    <t>โภคทรัพย์-3</t>
+  </si>
+  <si>
+    <t>G23</t>
+  </si>
+  <si>
+    <t>หญิงต่างถิ่นหลงทางมาขอความช่วยเหลือ</t>
+  </si>
+  <si>
+    <t>พาไปส่งถึงบ้าน</t>
+  </si>
+  <si>
+    <t>ส่งต่อให้ผู้ใหญ่บ้านดูแล</t>
+  </si>
+  <si>
+    <t>ระวังตัวว่าเป็นกลลวง</t>
+  </si>
+  <si>
+    <t>G24</t>
+  </si>
+  <si>
+    <t>ได้ตำราพิชัยสงครามเก่ามา</t>
+  </si>
+  <si>
+    <t>อ่านอย่างตั้งใจ</t>
+  </si>
+  <si>
+    <t>ฝึกตามท่าในตำรา</t>
+  </si>
+  <si>
+    <t>คัดลอกออกขาย</t>
+  </si>
+  <si>
+    <t>โภคทรัพย์+1, ความรู้+1</t>
+  </si>
+  <si>
+    <t>ทดลองกลศึกกับกองอาสาท้องถิ่น</t>
+  </si>
+  <si>
+    <t>ต่อสู้+3, บารมี+2</t>
+  </si>
+  <si>
+    <t>G25</t>
+  </si>
+  <si>
+    <t>ช้างป่าบุกไร่</t>
+  </si>
+  <si>
+    <t>ไล่ด้วยคบไฟ</t>
+  </si>
+  <si>
+    <t>ต่อสู้+1, พละกำลัง+1</t>
+  </si>
+  <si>
+    <t>ซ่อนตัวรอให้โขลงผ่านไป</t>
+  </si>
+  <si>
+    <t>ไปตามหมอช้างมาช่วย</t>
+  </si>
+  <si>
+    <t>ลองคล้องช้างด้วยตัวเอง</t>
+  </si>
+  <si>
+    <t>พละกำลัง+3, โภคทรัพย์+3, บารมี+2</t>
+  </si>
+  <si>
+    <t>พละกำลัง-3</t>
+  </si>
+  <si>
+    <t>G26</t>
+  </si>
+  <si>
+    <t>ราหูอมจันทร์</t>
+  </si>
+  <si>
+    <t>ตีเกราะเคาะไม้ไล่ราหู</t>
+  </si>
+  <si>
+    <t>สวดมนต์ภาวนา</t>
+  </si>
+  <si>
+    <t>จดบันทึกปรากฏการณ์</t>
+  </si>
+  <si>
+    <t>G27</t>
+  </si>
+  <si>
+    <t>นายอากรเรียกส่วยเกินพิกัด</t>
+  </si>
+  <si>
+    <t>จ่ายไปตามที่เรียก</t>
+  </si>
+  <si>
+    <t>ต่อรองให้ลดลง</t>
+  </si>
+  <si>
+    <t>ซ่อนทรัพย์ไม่ให้เห็น</t>
+  </si>
+  <si>
+    <t>ร้องเรียนต่อเจ้าเมือง</t>
+  </si>
+  <si>
+    <t>บารมี+3, ความรู้+2</t>
+  </si>
+  <si>
+    <t>G28</t>
+  </si>
+  <si>
+    <t>ทาสหนีนายมาขอหลบซ่อน</t>
+  </si>
+  <si>
+    <t>ให้ที่ซ่อนชั่วคราว</t>
+  </si>
+  <si>
+    <t>บารมี+1, หลบหลีก+1</t>
+  </si>
+  <si>
+    <t>จับส่งคืนนายเพื่อรับรางวัล</t>
+  </si>
+  <si>
+    <t>โภคทรัพย์+2, บาป+1</t>
+  </si>
+  <si>
+    <t>ช่วยหาทางไถ่ตัว</t>
+  </si>
+  <si>
+    <t>พาข้ามเขตแดนกลางคืน</t>
+  </si>
+  <si>
+    <t>หลบหลีก+3, บารมี+2</t>
+  </si>
+  <si>
+    <t>G29</t>
+  </si>
+  <si>
+    <t>เพลงเรือหน้าวัดหน้าน้ำ</t>
+  </si>
+  <si>
+    <t>ร่วมร้องแก้กลอนสด</t>
+  </si>
+  <si>
+    <t>ร่วมพายเรือแข่ง</t>
+  </si>
+  <si>
+    <t>นั่งดูอยู่ริมตลิ่ง</t>
+  </si>
+  <si>
+    <t>G30</t>
+  </si>
+  <si>
+    <t>ได้ยินคนวางแผนลักขโมย</t>
+  </si>
+  <si>
+    <t>ไปแจ้งนายบ้าน</t>
+  </si>
+  <si>
+    <t>แอบสะกดรอยตามดู</t>
+  </si>
+  <si>
+    <t>หลบหลีก+1, ไหวพริบ+1</t>
+  </si>
+  <si>
+    <t>ทำเป็นไม่รู้ไม่เห็น</t>
+  </si>
+  <si>
+    <t>ขอแบ่งส่วนด้วย</t>
+  </si>
+  <si>
+    <t>โภคทรัพย์+4, บาป+3</t>
+  </si>
+  <si>
+    <t>บารมี-3</t>
+  </si>
+  <si>
+    <t>G31</t>
+  </si>
+  <si>
+    <t>ช่างทองหลวงรับลูกมือ</t>
+  </si>
+  <si>
+    <t>ฝากตัวเป็นศิษย์</t>
+  </si>
+  <si>
+    <t>ความรู้+1, โภคทรัพย์+1</t>
+  </si>
+  <si>
+    <t>ขอดูวิธีหล่อพระพุทธรูป</t>
+  </si>
+  <si>
+    <t>ไสยเวทย์+1, ความรู้+1</t>
+  </si>
+  <si>
+    <t>ทำงานเดิมต่อไป</t>
+  </si>
+  <si>
+    <t>ขอทดลองหล่อชิ้นงานเอง</t>
+  </si>
+  <si>
+    <t>โภคทรัพย์+3, ความรู้+2</t>
+  </si>
+  <si>
+    <t>G32</t>
+  </si>
+  <si>
+    <t>ชาวต่างชาติพูดภาษาแปลกหูถามทาง</t>
+  </si>
+  <si>
+    <t>ทักทายและจดจำภาษา</t>
+  </si>
+  <si>
+    <t>พาไปหาล่าม</t>
+  </si>
+  <si>
+    <t>บารมี+1, ไหวพริบ+1</t>
+  </si>
+  <si>
+    <t>ระวังว่าเป็นสายสืบ</t>
+  </si>
+  <si>
+    <t>รับจ้างนำทางลัดเข้าเมือง</t>
+  </si>
+  <si>
+    <t>โภคทรัพย์+3, ไหวพริบ+2</t>
+  </si>
+  <si>
+    <t>G33</t>
+  </si>
+  <si>
+    <t>ชาวบ้านกล่าวหาหญิงชราว่าเป็นแม่มด</t>
+  </si>
+  <si>
+    <t>ออกหน้าปกป้องผู้ถูกกล่าวหา</t>
+  </si>
+  <si>
+    <t>ขอดูหลักฐานก่อนตัดสิน</t>
+  </si>
+  <si>
+    <t>ความรู้+1, ไหวพริบ+1</t>
+  </si>
+  <si>
+    <t>ร่วมขับไล่ออกจากหมู่บ้าน</t>
+  </si>
+  <si>
+    <t>ต่อสู้+1, บาป+2</t>
+  </si>
+  <si>
+    <t>G34</t>
+  </si>
+  <si>
+    <t>พบกรุพระเก่าในโพรงไม้</t>
+  </si>
+  <si>
+    <t>เก็บไว้บูชาเอง</t>
+  </si>
+  <si>
+    <t>ขายให้นักสะสม</t>
+  </si>
+  <si>
+    <t>G35</t>
+  </si>
+  <si>
+    <t>เทศกาลสงกรานต์</t>
+  </si>
+  <si>
+    <t>เล่นสาดน้ำกับเพื่อนบ้าน</t>
+  </si>
+  <si>
+    <t>สรงน้ำพระ รดน้ำผู้ใหญ่</t>
+  </si>
+  <si>
+    <t>ตั้งแผงขายของในงาน</t>
+  </si>
+  <si>
+    <t>G36</t>
+  </si>
+  <si>
+    <t>เพื่อนเก่ากลับมาพร้อมหนี้สิน</t>
+  </si>
+  <si>
+    <t>ช่วยใช้หนี้ให้</t>
+  </si>
+  <si>
+    <t>ให้คำแนะนำหาทางออก</t>
+  </si>
+  <si>
+    <t>ความรู้+1, บารมี+1</t>
+  </si>
+  <si>
+    <t>ตัดความสัมพันธ์</t>
+  </si>
+  <si>
+    <t>ร่วมลงทุนกิจการใหม่กับเพื่อน</t>
+  </si>
+  <si>
+    <t>โภคทรัพย์+4</t>
+  </si>
+  <si>
+    <t>G37</t>
+  </si>
+  <si>
+    <t>ห่าลงเมืองข้างเคียง</t>
+  </si>
+  <si>
+    <t>กักตัวอยู่แต่ในบ้าน</t>
+  </si>
+  <si>
+    <t>ช่วยหมอดูแลคนป่วย</t>
+  </si>
+  <si>
+    <t>ทำพิธีปัดรังควาน</t>
+  </si>
+  <si>
+    <t>เข้าไปส่งยาในเมืองที่โรคระบาด</t>
+  </si>
+  <si>
+    <t>บารมี+4, บุญ+3</t>
+  </si>
+  <si>
+    <t>G38</t>
+  </si>
+  <si>
+    <t>ถูกใส่ความต่อหน้านาย</t>
+  </si>
+  <si>
+    <t>แก้ต่างด้วยหลักฐาน</t>
+  </si>
+  <si>
+    <t>อดทนรอให้ความจริงปรากฏ</t>
+  </si>
+  <si>
+    <t>สืบหาคนปล่อยข่าว</t>
+  </si>
+  <si>
+    <t>ไหวพริบ+1, หลบหลีก+1</t>
+  </si>
+  <si>
+    <t>ท้าสาบานต่อหน้าพระประธาน</t>
+  </si>
+  <si>
+    <t>บารมี+4, ไสยเวทย์+1</t>
+  </si>
+  <si>
+    <t>G39</t>
+  </si>
+  <si>
+    <t>ปีแล้ง ข้าวยากหมากแพง</t>
+  </si>
+  <si>
+    <t>กักตุนข้าวไว้ขายราคาแพง</t>
+  </si>
+  <si>
+    <t>ออกหาของป่ามาเสริม</t>
+  </si>
+  <si>
+    <t>พละกำลัง+1, หลบหลีก+1</t>
+  </si>
+  <si>
+    <t>G40</t>
+  </si>
+  <si>
+    <t>ขบวนราชทูตต่างแดนเดินทางผ่าน</t>
+  </si>
+  <si>
+    <t>ไปเฝ้าดูขบวน</t>
+  </si>
+  <si>
+    <t>ไหวพริบ+1, ความรู้+1</t>
+  </si>
+  <si>
+    <t>รับจ้างแบกเครื่องบรรณาการ</t>
+  </si>
+  <si>
+    <t>ขายเสบียงให้ขบวน</t>
+  </si>
+  <si>
+    <t>ยื่นหนังสือฝากถึงราชสำนัก</t>
+  </si>
+  <si>
+    <t>บารมี-1</t>
   </si>
   <si>
     <t>ประเภท: narrative = บรรยาย · check = เช็คสเตตัส · choice = มีตัวเลือก · เหตุการณ์หลายปีใส่ปีเริ่ม–ปีสิ้นสุดต่างกัน</t>
@@ -8081,7 +8669,7 @@
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:O15"/>
+  <dimension ref="A1:O42"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="2" width="10" style="1" customWidth="1"/>
@@ -8775,6 +9363,1275 @@
       </c>
       <c r="O15" s="1" t="s">
         <v>1010</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A16" s="1" t="s">
+        <v>1011</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>1012</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>1013</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>639</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>1014</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>1015</v>
+      </c>
+      <c r="G16" s="1" t="s">
+        <v>1016</v>
+      </c>
+      <c r="H16" s="1" t="s">
+        <v>677</v>
+      </c>
+      <c r="I16" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="J16" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="K16" s="1" t="s">
+        <v>1017</v>
+      </c>
+      <c r="L16" s="1">
+        <v>0.4</v>
+      </c>
+      <c r="M16" s="1">
+        <v>10</v>
+      </c>
+      <c r="N16" s="1" t="s">
+        <v>1018</v>
+      </c>
+      <c r="O16" s="1" t="s">
+        <v>1019</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A17" s="1" t="s">
+        <v>1020</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>1021</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>1022</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>641</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>1023</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>631</v>
+      </c>
+      <c r="G17" s="1" t="s">
+        <v>1024</v>
+      </c>
+      <c r="H17" s="1" t="s">
+        <v>643</v>
+      </c>
+      <c r="I17" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="J17" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="K17" s="1" t="s">
+        <v>1025</v>
+      </c>
+      <c r="L17" s="1">
+        <v>0.45</v>
+      </c>
+      <c r="M17" s="1">
+        <v>10</v>
+      </c>
+      <c r="N17" s="1" t="s">
+        <v>973</v>
+      </c>
+      <c r="O17" s="1" t="s">
+        <v>950</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A18" s="1" t="s">
+        <v>1026</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>1027</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>1028</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>639</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>1029</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>1030</v>
+      </c>
+      <c r="G18" s="1" t="s">
+        <v>1031</v>
+      </c>
+      <c r="H18" s="1" t="s">
+        <v>1032</v>
+      </c>
+      <c r="I18" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="J18" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="K18" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="L18" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="M18" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="N18" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="O18" s="1" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A19" s="1" t="s">
+        <v>1033</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>1034</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>1035</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>721</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>1036</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>633</v>
+      </c>
+      <c r="G19" s="1" t="s">
+        <v>1037</v>
+      </c>
+      <c r="H19" s="1" t="s">
+        <v>1038</v>
+      </c>
+      <c r="I19" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="J19" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="K19" s="1" t="s">
+        <v>1039</v>
+      </c>
+      <c r="L19" s="1">
+        <v>0.45</v>
+      </c>
+      <c r="M19" s="1">
+        <v>10</v>
+      </c>
+      <c r="N19" s="1" t="s">
+        <v>1040</v>
+      </c>
+      <c r="O19" s="1" t="s">
+        <v>942</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A20" s="1" t="s">
+        <v>1041</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>1042</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>1043</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>1044</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>1045</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>641</v>
+      </c>
+      <c r="G20" s="1" t="s">
+        <v>1046</v>
+      </c>
+      <c r="H20" s="1" t="s">
+        <v>1007</v>
+      </c>
+      <c r="I20" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="J20" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="K20" s="1" t="s">
+        <v>1047</v>
+      </c>
+      <c r="L20" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="M20" s="1">
+        <v>10</v>
+      </c>
+      <c r="N20" s="1" t="s">
+        <v>1048</v>
+      </c>
+      <c r="O20" s="1" t="s">
+        <v>942</v>
+      </c>
+    </row>
+    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A21" s="1" t="s">
+        <v>1049</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>1050</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>1051</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>663</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>1052</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>635</v>
+      </c>
+      <c r="G21" s="1" t="s">
+        <v>1053</v>
+      </c>
+      <c r="H21" s="1" t="s">
+        <v>641</v>
+      </c>
+      <c r="I21" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="J21" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="K21" s="1" t="s">
+        <v>1054</v>
+      </c>
+      <c r="L21" s="1">
+        <v>0.35</v>
+      </c>
+      <c r="M21" s="1">
+        <v>10</v>
+      </c>
+      <c r="N21" s="1" t="s">
+        <v>1055</v>
+      </c>
+      <c r="O21" s="1" t="s">
+        <v>950</v>
+      </c>
+    </row>
+    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A22" s="1" t="s">
+        <v>1056</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>1057</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>1058</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>1044</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>1059</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>639</v>
+      </c>
+      <c r="G22" s="1" t="s">
+        <v>1060</v>
+      </c>
+      <c r="H22" s="1" t="s">
+        <v>1061</v>
+      </c>
+      <c r="I22" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="J22" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="K22" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="L22" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="M22" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="N22" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="O22" s="1" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A23" s="1" t="s">
+        <v>1062</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>1063</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>1064</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>631</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>1065</v>
+      </c>
+      <c r="F23" s="1" t="s">
+        <v>1066</v>
+      </c>
+      <c r="G23" s="1" t="s">
+        <v>1067</v>
+      </c>
+      <c r="H23" s="1" t="s">
+        <v>1068</v>
+      </c>
+      <c r="I23" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="J23" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="K23" s="1" t="s">
+        <v>1069</v>
+      </c>
+      <c r="L23" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="M23" s="1">
+        <v>10</v>
+      </c>
+      <c r="N23" s="1" t="s">
+        <v>1070</v>
+      </c>
+      <c r="O23" s="1" t="s">
+        <v>926</v>
+      </c>
+    </row>
+    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A24" s="1" t="s">
+        <v>1071</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>1072</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>1073</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>1074</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>1075</v>
+      </c>
+      <c r="F24" s="1" t="s">
+        <v>1076</v>
+      </c>
+      <c r="G24" s="1" t="s">
+        <v>1077</v>
+      </c>
+      <c r="H24" s="1" t="s">
+        <v>647</v>
+      </c>
+      <c r="I24" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="J24" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="K24" s="1" t="s">
+        <v>1078</v>
+      </c>
+      <c r="L24" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="M24" s="1">
+        <v>10</v>
+      </c>
+      <c r="N24" s="1" t="s">
+        <v>1079</v>
+      </c>
+      <c r="O24" s="1" t="s">
+        <v>1080</v>
+      </c>
+    </row>
+    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A25" s="1" t="s">
+        <v>1081</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>1082</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>1083</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>639</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>1084</v>
+      </c>
+      <c r="F25" s="1" t="s">
+        <v>691</v>
+      </c>
+      <c r="G25" s="1" t="s">
+        <v>1085</v>
+      </c>
+      <c r="H25" s="1" t="s">
+        <v>641</v>
+      </c>
+      <c r="I25" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="J25" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="K25" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="L25" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="M25" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="N25" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="O25" s="1" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A26" s="1" t="s">
+        <v>1086</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>1087</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>1088</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>635</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>1089</v>
+      </c>
+      <c r="F26" s="1" t="s">
+        <v>721</v>
+      </c>
+      <c r="G26" s="1" t="s">
+        <v>1090</v>
+      </c>
+      <c r="H26" s="1" t="s">
+        <v>1091</v>
+      </c>
+      <c r="I26" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="J26" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="K26" s="1" t="s">
+        <v>1092</v>
+      </c>
+      <c r="L26" s="1">
+        <v>0.45</v>
+      </c>
+      <c r="M26" s="1">
+        <v>10</v>
+      </c>
+      <c r="N26" s="1" t="s">
+        <v>1093</v>
+      </c>
+      <c r="O26" s="1" t="s">
+        <v>966</v>
+      </c>
+    </row>
+    <row r="27" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A27" s="1" t="s">
+        <v>1094</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>1095</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>1096</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>1097</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>1098</v>
+      </c>
+      <c r="F27" s="1" t="s">
+        <v>633</v>
+      </c>
+      <c r="G27" s="1" t="s">
+        <v>1099</v>
+      </c>
+      <c r="H27" s="1" t="s">
+        <v>1068</v>
+      </c>
+      <c r="I27" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="J27" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="K27" s="1" t="s">
+        <v>1100</v>
+      </c>
+      <c r="L27" s="1">
+        <v>0.3</v>
+      </c>
+      <c r="M27" s="1">
+        <v>10</v>
+      </c>
+      <c r="N27" s="1" t="s">
+        <v>1101</v>
+      </c>
+      <c r="O27" s="1" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="28" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A28" s="1" t="s">
+        <v>1103</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>1104</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>1105</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>663</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>1106</v>
+      </c>
+      <c r="F28" s="1" t="s">
+        <v>677</v>
+      </c>
+      <c r="G28" s="1" t="s">
+        <v>1107</v>
+      </c>
+      <c r="H28" s="1" t="s">
+        <v>635</v>
+      </c>
+      <c r="I28" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="J28" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="K28" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="L28" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="M28" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="N28" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="O28" s="1" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A29" s="1" t="s">
+        <v>1108</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>1109</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>1110</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>647</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>1111</v>
+      </c>
+      <c r="F29" s="1" t="s">
+        <v>641</v>
+      </c>
+      <c r="G29" s="1" t="s">
+        <v>1112</v>
+      </c>
+      <c r="H29" s="1" t="s">
+        <v>633</v>
+      </c>
+      <c r="I29" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="J29" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="K29" s="1" t="s">
+        <v>1113</v>
+      </c>
+      <c r="L29" s="1">
+        <v>0.4</v>
+      </c>
+      <c r="M29" s="1">
+        <v>10</v>
+      </c>
+      <c r="N29" s="1" t="s">
+        <v>1114</v>
+      </c>
+      <c r="O29" s="1" t="s">
+        <v>950</v>
+      </c>
+    </row>
+    <row r="30" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A30" s="1" t="s">
+        <v>1115</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>1116</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>1117</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>1118</v>
+      </c>
+      <c r="E30" s="1" t="s">
+        <v>1119</v>
+      </c>
+      <c r="F30" s="1" t="s">
+        <v>1120</v>
+      </c>
+      <c r="G30" s="1" t="s">
+        <v>1121</v>
+      </c>
+      <c r="H30" s="1" t="s">
+        <v>639</v>
+      </c>
+      <c r="I30" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="J30" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="K30" s="1" t="s">
+        <v>1122</v>
+      </c>
+      <c r="L30" s="1">
+        <v>0.45</v>
+      </c>
+      <c r="M30" s="1">
+        <v>10</v>
+      </c>
+      <c r="N30" s="1" t="s">
+        <v>1123</v>
+      </c>
+      <c r="O30" s="1" t="s">
+        <v>926</v>
+      </c>
+    </row>
+    <row r="31" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A31" s="1" t="s">
+        <v>1124</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>1125</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>1126</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>641</v>
+      </c>
+      <c r="E31" s="1" t="s">
+        <v>1127</v>
+      </c>
+      <c r="F31" s="1" t="s">
+        <v>631</v>
+      </c>
+      <c r="G31" s="1" t="s">
+        <v>1128</v>
+      </c>
+      <c r="H31" s="1" t="s">
+        <v>647</v>
+      </c>
+      <c r="I31" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="J31" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="K31" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="L31" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="M31" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="N31" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="O31" s="1" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="32" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A32" s="1" t="s">
+        <v>1129</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>1130</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>1131</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>639</v>
+      </c>
+      <c r="E32" s="1" t="s">
+        <v>1132</v>
+      </c>
+      <c r="F32" s="1" t="s">
+        <v>1133</v>
+      </c>
+      <c r="G32" s="1" t="s">
+        <v>1134</v>
+      </c>
+      <c r="H32" s="1" t="s">
+        <v>656</v>
+      </c>
+      <c r="I32" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="J32" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="K32" s="1" t="s">
+        <v>1135</v>
+      </c>
+      <c r="L32" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="M32" s="1">
+        <v>10</v>
+      </c>
+      <c r="N32" s="1" t="s">
+        <v>1136</v>
+      </c>
+      <c r="O32" s="1" t="s">
+        <v>1137</v>
+      </c>
+    </row>
+    <row r="33" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A33" s="1" t="s">
+        <v>1138</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>1139</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>1140</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>1141</v>
+      </c>
+      <c r="E33" s="1" t="s">
+        <v>1142</v>
+      </c>
+      <c r="F33" s="1" t="s">
+        <v>1143</v>
+      </c>
+      <c r="G33" s="1" t="s">
+        <v>1144</v>
+      </c>
+      <c r="H33" s="1" t="s">
+        <v>663</v>
+      </c>
+      <c r="I33" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="J33" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="K33" s="1" t="s">
+        <v>1145</v>
+      </c>
+      <c r="L33" s="1">
+        <v>0.4</v>
+      </c>
+      <c r="M33" s="1">
+        <v>10</v>
+      </c>
+      <c r="N33" s="1" t="s">
+        <v>1146</v>
+      </c>
+      <c r="O33" s="1" t="s">
+        <v>918</v>
+      </c>
+    </row>
+    <row r="34" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A34" s="1" t="s">
+        <v>1147</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>1148</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>1149</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>635</v>
+      </c>
+      <c r="E34" s="1" t="s">
+        <v>1150</v>
+      </c>
+      <c r="F34" s="1" t="s">
+        <v>1151</v>
+      </c>
+      <c r="G34" s="1" t="s">
+        <v>1152</v>
+      </c>
+      <c r="H34" s="1" t="s">
+        <v>1133</v>
+      </c>
+      <c r="I34" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="J34" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="K34" s="1" t="s">
+        <v>1153</v>
+      </c>
+      <c r="L34" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="M34" s="1">
+        <v>10</v>
+      </c>
+      <c r="N34" s="1" t="s">
+        <v>1154</v>
+      </c>
+      <c r="O34" s="1" t="s">
+        <v>926</v>
+      </c>
+    </row>
+    <row r="35" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A35" s="1" t="s">
+        <v>1155</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>1156</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>1157</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>639</v>
+      </c>
+      <c r="E35" s="1" t="s">
+        <v>1158</v>
+      </c>
+      <c r="F35" s="1" t="s">
+        <v>1159</v>
+      </c>
+      <c r="G35" s="1" t="s">
+        <v>1160</v>
+      </c>
+      <c r="H35" s="1" t="s">
+        <v>1161</v>
+      </c>
+      <c r="I35" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="J35" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="K35" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="L35" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="M35" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="N35" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="O35" s="1" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="36" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A36" s="1" t="s">
+        <v>1162</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>1163</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>1031</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>639</v>
+      </c>
+      <c r="E36" s="1" t="s">
+        <v>1164</v>
+      </c>
+      <c r="F36" s="1" t="s">
+        <v>677</v>
+      </c>
+      <c r="G36" s="1" t="s">
+        <v>1165</v>
+      </c>
+      <c r="H36" s="1" t="s">
+        <v>1120</v>
+      </c>
+      <c r="I36" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="J36" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="K36" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="L36" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="M36" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="N36" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="O36" s="1" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="37" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A37" s="1" t="s">
+        <v>1166</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>1167</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>1168</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>1044</v>
+      </c>
+      <c r="E37" s="1" t="s">
+        <v>1169</v>
+      </c>
+      <c r="F37" s="1" t="s">
+        <v>639</v>
+      </c>
+      <c r="G37" s="1" t="s">
+        <v>1170</v>
+      </c>
+      <c r="H37" s="1" t="s">
+        <v>643</v>
+      </c>
+      <c r="I37" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="J37" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="K37" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="L37" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="M37" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="N37" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="O37" s="1" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="38" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A38" s="1" t="s">
+        <v>1171</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>1172</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>1173</v>
+      </c>
+      <c r="D38" s="1" t="s">
+        <v>670</v>
+      </c>
+      <c r="E38" s="1" t="s">
+        <v>1174</v>
+      </c>
+      <c r="F38" s="1" t="s">
+        <v>1175</v>
+      </c>
+      <c r="G38" s="1" t="s">
+        <v>1176</v>
+      </c>
+      <c r="H38" s="1" t="s">
+        <v>656</v>
+      </c>
+      <c r="I38" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="J38" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="K38" s="1" t="s">
+        <v>1177</v>
+      </c>
+      <c r="L38" s="1">
+        <v>0.45</v>
+      </c>
+      <c r="M38" s="1">
+        <v>10</v>
+      </c>
+      <c r="N38" s="1" t="s">
+        <v>1178</v>
+      </c>
+      <c r="O38" s="1" t="s">
+        <v>1080</v>
+      </c>
+    </row>
+    <row r="39" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A39" s="1" t="s">
+        <v>1179</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>1180</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>1181</v>
+      </c>
+      <c r="D39" s="1" t="s">
+        <v>633</v>
+      </c>
+      <c r="E39" s="1" t="s">
+        <v>1182</v>
+      </c>
+      <c r="F39" s="1" t="s">
+        <v>639</v>
+      </c>
+      <c r="G39" s="1" t="s">
+        <v>1183</v>
+      </c>
+      <c r="H39" s="1" t="s">
+        <v>677</v>
+      </c>
+      <c r="I39" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="J39" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="K39" s="1" t="s">
+        <v>1184</v>
+      </c>
+      <c r="L39" s="1">
+        <v>0.4</v>
+      </c>
+      <c r="M39" s="1">
+        <v>10</v>
+      </c>
+      <c r="N39" s="1" t="s">
+        <v>1185</v>
+      </c>
+      <c r="O39" s="1" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="40" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A40" s="1" t="s">
+        <v>1186</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>1187</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>1188</v>
+      </c>
+      <c r="D40" s="1" t="s">
+        <v>635</v>
+      </c>
+      <c r="E40" s="1" t="s">
+        <v>1189</v>
+      </c>
+      <c r="F40" s="1" t="s">
+        <v>639</v>
+      </c>
+      <c r="G40" s="1" t="s">
+        <v>1190</v>
+      </c>
+      <c r="H40" s="1" t="s">
+        <v>1191</v>
+      </c>
+      <c r="I40" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="J40" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="K40" s="1" t="s">
+        <v>1192</v>
+      </c>
+      <c r="L40" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="M40" s="1">
+        <v>10</v>
+      </c>
+      <c r="N40" s="1" t="s">
+        <v>1193</v>
+      </c>
+      <c r="O40" s="1" t="s">
+        <v>1137</v>
+      </c>
+    </row>
+    <row r="41" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A41" s="1" t="s">
+        <v>1194</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>1195</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>637</v>
+      </c>
+      <c r="D41" s="1" t="s">
+        <v>639</v>
+      </c>
+      <c r="E41" s="1" t="s">
+        <v>1196</v>
+      </c>
+      <c r="F41" s="1" t="s">
+        <v>1030</v>
+      </c>
+      <c r="G41" s="1" t="s">
+        <v>1197</v>
+      </c>
+      <c r="H41" s="1" t="s">
+        <v>1198</v>
+      </c>
+      <c r="I41" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="J41" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="K41" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="L41" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="M41" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="N41" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="O41" s="1" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="42" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A42" s="1" t="s">
+        <v>1199</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>1200</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>1201</v>
+      </c>
+      <c r="D42" s="1" t="s">
+        <v>1202</v>
+      </c>
+      <c r="E42" s="1" t="s">
+        <v>1203</v>
+      </c>
+      <c r="F42" s="1" t="s">
+        <v>631</v>
+      </c>
+      <c r="G42" s="1" t="s">
+        <v>1204</v>
+      </c>
+      <c r="H42" s="1" t="s">
+        <v>643</v>
+      </c>
+      <c r="I42" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="J42" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="K42" s="1" t="s">
+        <v>1205</v>
+      </c>
+      <c r="L42" s="1">
+        <v>0.35</v>
+      </c>
+      <c r="M42" s="1">
+        <v>10</v>
+      </c>
+      <c r="N42" s="1" t="s">
+        <v>1114</v>
+      </c>
+      <c r="O42" s="1" t="s">
+        <v>1206</v>
       </c>
     </row>
   </sheetData>
@@ -8805,7 +10662,7 @@
   <sheetData>
     <row r="1" spans="1:18" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>1011</v>
+        <v>1207</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
@@ -8833,7 +10690,7 @@
         <v>539</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>1012</v>
+        <v>1208</v>
       </c>
       <c r="D2" s="5" t="s">
         <v>298</v>
@@ -8848,13 +10705,13 @@
         <v>541</v>
       </c>
       <c r="H2" s="5" t="s">
-        <v>1013</v>
+        <v>1209</v>
       </c>
       <c r="I2" s="5" t="s">
-        <v>1014</v>
+        <v>1210</v>
       </c>
       <c r="J2" s="5" t="s">
-        <v>1015</v>
+        <v>1211</v>
       </c>
       <c r="K2" s="5" t="s">
         <v>620</v>
@@ -8883,16 +10740,16 @@
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>1016</v>
+        <v>1212</v>
       </c>
       <c r="B3" s="1">
         <v>1</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>1017</v>
+        <v>1213</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>1018</v>
+        <v>1214</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>55</v>
@@ -8939,19 +10796,19 @@
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>1019</v>
+        <v>1215</v>
       </c>
       <c r="B4" s="1">
         <v>1</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>1017</v>
+        <v>1213</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>1020</v>
+        <v>1216</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>1021</v>
+        <v>1217</v>
       </c>
       <c r="F4" s="1">
         <v>1893</v>
@@ -8995,19 +10852,19 @@
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>1022</v>
+        <v>1218</v>
       </c>
       <c r="B5" s="1">
         <v>1</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>1023</v>
+        <v>1219</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>1024</v>
+        <v>1220</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>1025</v>
+        <v>1221</v>
       </c>
       <c r="F5" s="1">
         <v>1894</v>
@@ -9051,16 +10908,16 @@
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>1026</v>
+        <v>1222</v>
       </c>
       <c r="B6" s="1">
         <v>1</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>1023</v>
+        <v>1219</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>1027</v>
+        <v>1223</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>55</v>
@@ -9107,16 +10964,16 @@
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>1028</v>
+        <v>1224</v>
       </c>
       <c r="B7" s="1">
         <v>1</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>1023</v>
+        <v>1219</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>1029</v>
+        <v>1225</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>55</v>
@@ -9163,19 +11020,19 @@
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>1030</v>
+        <v>1226</v>
       </c>
       <c r="B8" s="1">
         <v>1</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>1031</v>
+        <v>1227</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>1032</v>
+        <v>1228</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>1033</v>
+        <v>1229</v>
       </c>
       <c r="F8" s="1">
         <v>1912</v>
@@ -9193,19 +11050,19 @@
         <v>55</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>1034</v>
+        <v>1230</v>
       </c>
       <c r="L8" s="1" t="s">
         <v>656</v>
       </c>
       <c r="M8" s="1" t="s">
-        <v>1035</v>
+        <v>1231</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>1036</v>
+        <v>1232</v>
       </c>
       <c r="O8" s="1" t="s">
-        <v>1037</v>
+        <v>1233</v>
       </c>
       <c r="P8" s="1" t="s">
         <v>647</v>
@@ -9219,19 +11076,19 @@
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>1038</v>
+        <v>1234</v>
       </c>
       <c r="B9" s="1">
         <v>1</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>1023</v>
+        <v>1219</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>1039</v>
+        <v>1235</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>1040</v>
+        <v>1236</v>
       </c>
       <c r="F9" s="1">
         <v>1913</v>
@@ -9275,19 +11132,19 @@
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>1041</v>
+        <v>1237</v>
       </c>
       <c r="B10" s="1">
         <v>1</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>1023</v>
+        <v>1219</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>1042</v>
+        <v>1238</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>1043</v>
+        <v>1239</v>
       </c>
       <c r="F10" s="1">
         <v>1917</v>
@@ -9331,19 +11188,19 @@
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>1044</v>
+        <v>1240</v>
       </c>
       <c r="B11" s="1">
         <v>1</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>1031</v>
+        <v>1227</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>1045</v>
+        <v>1241</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>1046</v>
+        <v>1242</v>
       </c>
       <c r="F11" s="1">
         <v>1931</v>
@@ -9361,19 +11218,19 @@
         <v>55</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>1047</v>
+        <v>1243</v>
       </c>
       <c r="L11" s="1" t="s">
         <v>633</v>
       </c>
       <c r="M11" s="1" t="s">
-        <v>1048</v>
+        <v>1244</v>
       </c>
       <c r="N11" s="1" t="s">
         <v>635</v>
       </c>
       <c r="O11" s="1" t="s">
-        <v>1049</v>
+        <v>1245</v>
       </c>
       <c r="P11" s="1" t="s">
         <v>639</v>
@@ -9387,19 +11244,19 @@
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>1050</v>
+        <v>1246</v>
       </c>
       <c r="B12" s="1">
         <v>1</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>1023</v>
+        <v>1219</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>1051</v>
+        <v>1247</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>1052</v>
+        <v>1248</v>
       </c>
       <c r="F12" s="1">
         <v>1932</v>
@@ -9443,16 +11300,16 @@
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>1053</v>
+        <v>1249</v>
       </c>
       <c r="B13" s="1">
         <v>1</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>1023</v>
+        <v>1219</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>1054</v>
+        <v>1250</v>
       </c>
       <c r="E13" s="1" t="s">
         <v>55</v>
@@ -9499,19 +11356,19 @@
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>1055</v>
+        <v>1251</v>
       </c>
       <c r="B14" s="1">
         <v>1</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>1031</v>
+        <v>1227</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>1056</v>
+        <v>1252</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>1057</v>
+        <v>1253</v>
       </c>
       <c r="F14" s="1">
         <v>1939</v>
@@ -9529,22 +11386,22 @@
         <v>55</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>1058</v>
+        <v>1254</v>
       </c>
       <c r="L14" s="1" t="s">
         <v>633</v>
       </c>
       <c r="M14" s="1" t="s">
-        <v>1059</v>
+        <v>1255</v>
       </c>
       <c r="N14" s="1" t="s">
         <v>639</v>
       </c>
       <c r="O14" s="1" t="s">
-        <v>1060</v>
+        <v>1256</v>
       </c>
       <c r="P14" s="1" t="s">
-        <v>1061</v>
+        <v>1257</v>
       </c>
       <c r="Q14" s="1" t="s">
         <v>55</v>
@@ -9555,16 +11412,16 @@
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>1062</v>
+        <v>1258</v>
       </c>
       <c r="B15" s="1">
         <v>1</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>1017</v>
+        <v>1213</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>1063</v>
+        <v>1259</v>
       </c>
       <c r="E15" s="1" t="s">
         <v>55</v>
@@ -9611,16 +11468,16 @@
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>1064</v>
+        <v>1260</v>
       </c>
       <c r="B16" s="1">
         <v>2</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>1017</v>
+        <v>1213</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>1065</v>
+        <v>1261</v>
       </c>
       <c r="E16" s="1" t="s">
         <v>55</v>
@@ -9667,16 +11524,16 @@
     </row>
     <row r="17" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>1066</v>
+        <v>1262</v>
       </c>
       <c r="B17" s="1">
         <v>2</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>1017</v>
+        <v>1213</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>1067</v>
+        <v>1263</v>
       </c>
       <c r="E17" s="1" t="s">
         <v>55</v>
@@ -9723,16 +11580,16 @@
     </row>
     <row r="18" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>1068</v>
+        <v>1264</v>
       </c>
       <c r="B18" s="1">
         <v>2</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>1031</v>
+        <v>1227</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>1069</v>
+        <v>1265</v>
       </c>
       <c r="E18" s="1" t="s">
         <v>55</v>
@@ -9753,19 +11610,19 @@
         <v>55</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>1070</v>
+        <v>1266</v>
       </c>
       <c r="L18" s="1" t="s">
         <v>643</v>
       </c>
       <c r="M18" s="1" t="s">
-        <v>1071</v>
+        <v>1267</v>
       </c>
       <c r="N18" s="1" t="s">
         <v>635</v>
       </c>
       <c r="O18" s="1" t="s">
-        <v>1072</v>
+        <v>1268</v>
       </c>
       <c r="P18" s="1" t="s">
         <v>631</v>
@@ -9779,19 +11636,19 @@
     </row>
     <row r="19" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>1073</v>
+        <v>1269</v>
       </c>
       <c r="B19" s="1">
         <v>2</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>1031</v>
+        <v>1227</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>1074</v>
+        <v>1270</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>1075</v>
+        <v>1271</v>
       </c>
       <c r="F19" s="1">
         <v>1967</v>
@@ -9809,19 +11666,19 @@
         <v>55</v>
       </c>
       <c r="K19" s="1" t="s">
-        <v>1076</v>
+        <v>1272</v>
       </c>
       <c r="L19" s="1" t="s">
         <v>633</v>
       </c>
       <c r="M19" s="1" t="s">
-        <v>1077</v>
+        <v>1273</v>
       </c>
       <c r="N19" s="1" t="s">
-        <v>1078</v>
+        <v>1274</v>
       </c>
       <c r="O19" s="1" t="s">
-        <v>1079</v>
+        <v>1275</v>
       </c>
       <c r="P19" s="1" t="s">
         <v>639</v>
@@ -9835,19 +11692,19 @@
     </row>
     <row r="20" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>1080</v>
+        <v>1276</v>
       </c>
       <c r="B20" s="1">
         <v>2</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>1023</v>
+        <v>1219</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>1081</v>
+        <v>1277</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>1052</v>
+        <v>1248</v>
       </c>
       <c r="F20" s="1">
         <v>1968</v>
@@ -9891,16 +11748,16 @@
     </row>
     <row r="21" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>1082</v>
+        <v>1278</v>
       </c>
       <c r="B21" s="1">
         <v>2</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>1023</v>
+        <v>1219</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>1083</v>
+        <v>1279</v>
       </c>
       <c r="E21" s="1" t="s">
         <v>55</v>
@@ -9947,16 +11804,16 @@
     </row>
     <row r="22" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>1084</v>
+        <v>1280</v>
       </c>
       <c r="B22" s="1">
         <v>2</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>1017</v>
+        <v>1213</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>1085</v>
+        <v>1281</v>
       </c>
       <c r="E22" s="1" t="s">
         <v>55</v>
@@ -10003,19 +11860,19 @@
     </row>
     <row r="23" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>1086</v>
+        <v>1282</v>
       </c>
       <c r="B23" s="1">
         <v>2</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>1031</v>
+        <v>1227</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>1087</v>
+        <v>1283</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>1088</v>
+        <v>1284</v>
       </c>
       <c r="F23" s="1">
         <v>1991</v>
@@ -10033,19 +11890,19 @@
         <v>55</v>
       </c>
       <c r="K23" s="1" t="s">
-        <v>1089</v>
+        <v>1285</v>
       </c>
       <c r="L23" s="1" t="s">
         <v>639</v>
       </c>
       <c r="M23" s="1" t="s">
-        <v>1090</v>
+        <v>1286</v>
       </c>
       <c r="N23" s="1" t="s">
         <v>635</v>
       </c>
       <c r="O23" s="1" t="s">
-        <v>1091</v>
+        <v>1287</v>
       </c>
       <c r="P23" s="1" t="s">
         <v>641</v>
@@ -10059,16 +11916,16 @@
     </row>
     <row r="24" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>1092</v>
+        <v>1288</v>
       </c>
       <c r="B24" s="1">
         <v>2</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>1031</v>
+        <v>1227</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>1093</v>
+        <v>1289</v>
       </c>
       <c r="E24" s="1" t="s">
         <v>55</v>
@@ -10089,19 +11946,19 @@
         <v>55</v>
       </c>
       <c r="K24" s="1" t="s">
-        <v>1094</v>
+        <v>1290</v>
       </c>
       <c r="L24" s="1" t="s">
-        <v>1095</v>
+        <v>1291</v>
       </c>
       <c r="M24" s="1" t="s">
-        <v>1096</v>
+        <v>1292</v>
       </c>
       <c r="N24" s="1" t="s">
         <v>668</v>
       </c>
       <c r="O24" s="1" t="s">
-        <v>1097</v>
+        <v>1293</v>
       </c>
       <c r="P24" s="1" t="s">
         <v>717</v>
@@ -10115,19 +11972,19 @@
     </row>
     <row r="25" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>1098</v>
+        <v>1294</v>
       </c>
       <c r="B25" s="1">
         <v>2</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>1023</v>
+        <v>1219</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>1099</v>
+        <v>1295</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>1052</v>
+        <v>1248</v>
       </c>
       <c r="F25" s="1">
         <v>2006</v>
@@ -10171,16 +12028,16 @@
     </row>
     <row r="26" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>1100</v>
+        <v>1296</v>
       </c>
       <c r="B26" s="1">
         <v>2</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>1017</v>
+        <v>1213</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>1101</v>
+        <v>1297</v>
       </c>
       <c r="E26" s="1" t="s">
         <v>55</v>
@@ -10227,19 +12084,19 @@
     </row>
     <row r="27" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>1102</v>
+        <v>1298</v>
       </c>
       <c r="B27" s="1">
         <v>3</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>1023</v>
+        <v>1219</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>1103</v>
+        <v>1299</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>1104</v>
+        <v>1300</v>
       </c>
       <c r="F27" s="1">
         <v>2011</v>
@@ -10283,16 +12140,16 @@
     </row>
     <row r="28" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>1105</v>
+        <v>1301</v>
       </c>
       <c r="B28" s="1">
         <v>3</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>1031</v>
+        <v>1227</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>1106</v>
+        <v>1302</v>
       </c>
       <c r="E28" s="1" t="s">
         <v>55</v>
@@ -10313,19 +12170,19 @@
         <v>55</v>
       </c>
       <c r="K28" s="1" t="s">
-        <v>1107</v>
+        <v>1303</v>
       </c>
       <c r="L28" s="1" t="s">
         <v>639</v>
       </c>
       <c r="M28" s="1" t="s">
-        <v>1108</v>
+        <v>1304</v>
       </c>
       <c r="N28" s="1" t="s">
         <v>633</v>
       </c>
       <c r="O28" s="1" t="s">
-        <v>1109</v>
+        <v>1305</v>
       </c>
       <c r="P28" s="1" t="s">
         <v>641</v>
@@ -10339,19 +12196,19 @@
     </row>
     <row r="29" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>1110</v>
+        <v>1306</v>
       </c>
       <c r="B29" s="1">
         <v>3</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>1031</v>
+        <v>1227</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>1111</v>
+        <v>1307</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>1112</v>
+        <v>1308</v>
       </c>
       <c r="F29" s="1">
         <v>2034</v>
@@ -10369,22 +12226,22 @@
         <v>55</v>
       </c>
       <c r="K29" s="1" t="s">
-        <v>1113</v>
+        <v>1309</v>
       </c>
       <c r="L29" s="1" t="s">
-        <v>1114</v>
+        <v>1310</v>
       </c>
       <c r="M29" s="1" t="s">
-        <v>1115</v>
+        <v>1311</v>
       </c>
       <c r="N29" s="1" t="s">
         <v>668</v>
       </c>
       <c r="O29" s="1" t="s">
-        <v>1116</v>
+        <v>1312</v>
       </c>
       <c r="P29" s="1" t="s">
-        <v>1117</v>
+        <v>1313</v>
       </c>
       <c r="Q29" s="1" t="s">
         <v>55</v>
@@ -10395,16 +12252,16 @@
     </row>
     <row r="30" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>1118</v>
+        <v>1314</v>
       </c>
       <c r="B30" s="1">
         <v>3</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>1017</v>
+        <v>1213</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>1119</v>
+        <v>1315</v>
       </c>
       <c r="E30" s="1" t="s">
         <v>55</v>
@@ -10451,16 +12308,16 @@
     </row>
     <row r="31" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>1120</v>
+        <v>1316</v>
       </c>
       <c r="B31" s="1">
         <v>3</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>1023</v>
+        <v>1219</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>1121</v>
+        <v>1317</v>
       </c>
       <c r="E31" s="1" t="s">
         <v>55</v>
@@ -10507,19 +12364,19 @@
     </row>
     <row r="32" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>1122</v>
+        <v>1318</v>
       </c>
       <c r="B32" s="1">
         <v>3</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>1031</v>
+        <v>1227</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>1123</v>
+        <v>1319</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>1124</v>
+        <v>1320</v>
       </c>
       <c r="F32" s="1">
         <v>2054</v>
@@ -10537,19 +12394,19 @@
         <v>55</v>
       </c>
       <c r="K32" s="1" t="s">
-        <v>1125</v>
+        <v>1321</v>
       </c>
       <c r="L32" s="1" t="s">
         <v>660</v>
       </c>
       <c r="M32" s="1" t="s">
-        <v>1126</v>
+        <v>1322</v>
       </c>
       <c r="N32" s="1" t="s">
-        <v>1127</v>
+        <v>1323</v>
       </c>
       <c r="O32" s="1" t="s">
-        <v>1128</v>
+        <v>1324</v>
       </c>
       <c r="P32" s="1" t="s">
         <v>656</v>
@@ -10563,19 +12420,19 @@
     </row>
     <row r="33" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>1129</v>
+        <v>1325</v>
       </c>
       <c r="B33" s="1">
         <v>3</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>1023</v>
+        <v>1219</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>1130</v>
+        <v>1326</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>1052</v>
+        <v>1248</v>
       </c>
       <c r="F33" s="1">
         <v>2055</v>
@@ -10619,16 +12476,16 @@
     </row>
     <row r="34" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>1131</v>
+        <v>1327</v>
       </c>
       <c r="B34" s="1">
         <v>3</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>1017</v>
+        <v>1213</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>1132</v>
+        <v>1328</v>
       </c>
       <c r="E34" s="1" t="s">
         <v>55</v>
@@ -10675,16 +12532,16 @@
     </row>
     <row r="35" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>1133</v>
+        <v>1329</v>
       </c>
       <c r="B35" s="1">
         <v>4</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>1017</v>
+        <v>1213</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>1134</v>
+        <v>1330</v>
       </c>
       <c r="E35" s="1" t="s">
         <v>55</v>
@@ -10731,19 +12588,19 @@
     </row>
     <row r="36" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>1135</v>
+        <v>1331</v>
       </c>
       <c r="B36" s="1">
         <v>4</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>1031</v>
+        <v>1227</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>1136</v>
+        <v>1332</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>1137</v>
+        <v>1333</v>
       </c>
       <c r="F36" s="1">
         <v>2077</v>
@@ -10761,19 +12618,19 @@
         <v>55</v>
       </c>
       <c r="K36" s="1" t="s">
-        <v>1138</v>
+        <v>1334</v>
       </c>
       <c r="L36" s="1" t="s">
         <v>633</v>
       </c>
       <c r="M36" s="1" t="s">
-        <v>1139</v>
+        <v>1335</v>
       </c>
       <c r="N36" s="1" t="s">
         <v>635</v>
       </c>
       <c r="O36" s="1" t="s">
-        <v>1140</v>
+        <v>1336</v>
       </c>
       <c r="P36" s="1" t="s">
         <v>643</v>
@@ -10787,16 +12644,16 @@
     </row>
     <row r="37" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>1141</v>
+        <v>1337</v>
       </c>
       <c r="B37" s="1">
         <v>4</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>1023</v>
+        <v>1219</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>1142</v>
+        <v>1338</v>
       </c>
       <c r="E37" s="1" t="s">
         <v>55</v>
@@ -10843,16 +12700,16 @@
     </row>
     <row r="38" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>1143</v>
+        <v>1339</v>
       </c>
       <c r="B38" s="1">
         <v>4</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>1017</v>
+        <v>1213</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>1144</v>
+        <v>1340</v>
       </c>
       <c r="E38" s="1" t="s">
         <v>55</v>
@@ -10899,19 +12756,19 @@
     </row>
     <row r="39" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
-        <v>1145</v>
+        <v>1341</v>
       </c>
       <c r="B39" s="1">
         <v>4</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>1031</v>
+        <v>1227</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>1146</v>
+        <v>1342</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>1147</v>
+        <v>1343</v>
       </c>
       <c r="F39" s="1">
         <v>2089</v>
@@ -10929,19 +12786,19 @@
         <v>55</v>
       </c>
       <c r="K39" s="1" t="s">
-        <v>1148</v>
+        <v>1344</v>
       </c>
       <c r="L39" s="1" t="s">
         <v>668</v>
       </c>
       <c r="M39" s="1" t="s">
-        <v>1149</v>
+        <v>1345</v>
       </c>
       <c r="N39" s="1" t="s">
         <v>842</v>
       </c>
       <c r="O39" s="1" t="s">
-        <v>1150</v>
+        <v>1346</v>
       </c>
       <c r="P39" s="1" t="s">
         <v>674</v>
@@ -10955,16 +12812,16 @@
     </row>
     <row r="40" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
-        <v>1151</v>
+        <v>1347</v>
       </c>
       <c r="B40" s="1">
         <v>4</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>1023</v>
+        <v>1219</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>1152</v>
+        <v>1348</v>
       </c>
       <c r="E40" s="1" t="s">
         <v>55</v>
@@ -11011,16 +12868,16 @@
     </row>
     <row r="41" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
-        <v>1153</v>
+        <v>1349</v>
       </c>
       <c r="B41" s="1">
         <v>4</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>1017</v>
+        <v>1213</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>1154</v>
+        <v>1350</v>
       </c>
       <c r="E41" s="1" t="s">
         <v>55</v>
@@ -11067,19 +12924,19 @@
     </row>
     <row r="42" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
-        <v>1155</v>
+        <v>1351</v>
       </c>
       <c r="B42" s="1">
         <v>4</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>1031</v>
+        <v>1227</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>1156</v>
+        <v>1352</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>1157</v>
+        <v>1353</v>
       </c>
       <c r="F42" s="1">
         <v>2106</v>
@@ -11097,19 +12954,19 @@
         <v>55</v>
       </c>
       <c r="K42" s="1" t="s">
-        <v>1158</v>
+        <v>1354</v>
       </c>
       <c r="L42" s="1" t="s">
         <v>633</v>
       </c>
       <c r="M42" s="1" t="s">
-        <v>1159</v>
+        <v>1355</v>
       </c>
       <c r="N42" s="1" t="s">
-        <v>1160</v>
+        <v>1356</v>
       </c>
       <c r="O42" s="1" t="s">
-        <v>1161</v>
+        <v>1357</v>
       </c>
       <c r="P42" s="1" t="s">
         <v>663</v>
@@ -11123,19 +12980,19 @@
     </row>
     <row r="43" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
-        <v>1162</v>
+        <v>1358</v>
       </c>
       <c r="B43" s="1">
         <v>4</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>1031</v>
+        <v>1227</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>1163</v>
+        <v>1359</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>1164</v>
+        <v>1360</v>
       </c>
       <c r="F43" s="1">
         <v>2111</v>
@@ -11153,22 +13010,22 @@
         <v>55</v>
       </c>
       <c r="K43" s="1" t="s">
-        <v>1165</v>
+        <v>1361</v>
       </c>
       <c r="L43" s="1" t="s">
         <v>668</v>
       </c>
       <c r="M43" s="1" t="s">
-        <v>1166</v>
+        <v>1362</v>
       </c>
       <c r="N43" s="1" t="s">
-        <v>1167</v>
+        <v>1363</v>
       </c>
       <c r="O43" s="1" t="s">
-        <v>1168</v>
+        <v>1364</v>
       </c>
       <c r="P43" s="1" t="s">
-        <v>1169</v>
+        <v>1365</v>
       </c>
       <c r="Q43" s="1" t="s">
         <v>55</v>
@@ -11179,19 +13036,19 @@
     </row>
     <row r="44" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
-        <v>1170</v>
+        <v>1366</v>
       </c>
       <c r="B44" s="1">
         <v>4</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>1023</v>
+        <v>1219</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>1171</v>
+        <v>1367</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>1052</v>
+        <v>1248</v>
       </c>
       <c r="F44" s="1">
         <v>2113</v>
@@ -11235,19 +13092,19 @@
     </row>
     <row r="45" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
-        <v>1172</v>
+        <v>1368</v>
       </c>
       <c r="B45" s="1">
         <v>4</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>1031</v>
+        <v>1227</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>1173</v>
+        <v>1369</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>1174</v>
+        <v>1370</v>
       </c>
       <c r="F45" s="1">
         <v>2127</v>
@@ -11265,22 +13122,22 @@
         <v>55</v>
       </c>
       <c r="K45" s="1" t="s">
-        <v>1175</v>
+        <v>1371</v>
       </c>
       <c r="L45" s="1" t="s">
         <v>753</v>
       </c>
       <c r="M45" s="1" t="s">
-        <v>1176</v>
+        <v>1372</v>
       </c>
       <c r="N45" s="1" t="s">
         <v>674</v>
       </c>
       <c r="O45" s="1" t="s">
-        <v>1177</v>
+        <v>1373</v>
       </c>
       <c r="P45" s="1" t="s">
-        <v>1178</v>
+        <v>1374</v>
       </c>
       <c r="Q45" s="1" t="s">
         <v>55</v>
@@ -11291,19 +13148,19 @@
     </row>
     <row r="46" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
-        <v>1179</v>
+        <v>1375</v>
       </c>
       <c r="B46" s="1">
         <v>4</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>1023</v>
+        <v>1219</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>1180</v>
+        <v>1376</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>1181</v>
+        <v>1377</v>
       </c>
       <c r="F46" s="1">
         <v>2128</v>
@@ -11347,16 +13204,16 @@
     </row>
     <row r="47" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
-        <v>1182</v>
+        <v>1378</v>
       </c>
       <c r="B47" s="1">
         <v>4</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>1017</v>
+        <v>1213</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>1183</v>
+        <v>1379</v>
       </c>
       <c r="E47" s="1" t="s">
         <v>55</v>
@@ -11403,16 +13260,16 @@
     </row>
     <row r="48" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
-        <v>1184</v>
+        <v>1380</v>
       </c>
       <c r="B48" s="1">
         <v>4</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>1017</v>
+        <v>1213</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>1185</v>
+        <v>1381</v>
       </c>
       <c r="E48" s="1" t="s">
         <v>55</v>
@@ -11459,19 +13316,19 @@
     </row>
     <row r="49" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
-        <v>1186</v>
+        <v>1382</v>
       </c>
       <c r="B49" s="1">
         <v>5</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>1023</v>
+        <v>1219</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>1187</v>
+        <v>1383</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>1188</v>
+        <v>1384</v>
       </c>
       <c r="F49" s="1">
         <v>2136</v>
@@ -11515,19 +13372,19 @@
     </row>
     <row r="50" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
-        <v>1189</v>
+        <v>1385</v>
       </c>
       <c r="B50" s="1">
         <v>5</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>1031</v>
+        <v>1227</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>1190</v>
+        <v>1386</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>1191</v>
+        <v>1387</v>
       </c>
       <c r="F50" s="1">
         <v>2148</v>
@@ -11545,19 +13402,19 @@
         <v>55</v>
       </c>
       <c r="K50" s="1" t="s">
-        <v>1192</v>
+        <v>1388</v>
       </c>
       <c r="L50" s="1" t="s">
         <v>674</v>
       </c>
       <c r="M50" s="1" t="s">
-        <v>1193</v>
+        <v>1389</v>
       </c>
       <c r="N50" s="1" t="s">
         <v>633</v>
       </c>
       <c r="O50" s="1" t="s">
-        <v>1194</v>
+        <v>1390</v>
       </c>
       <c r="P50" s="1" t="s">
         <v>641</v>
@@ -11571,16 +13428,16 @@
     </row>
     <row r="51" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
-        <v>1195</v>
+        <v>1391</v>
       </c>
       <c r="B51" s="1">
         <v>5</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>1017</v>
+        <v>1213</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>1196</v>
+        <v>1392</v>
       </c>
       <c r="E51" s="1" t="s">
         <v>55</v>
@@ -11627,19 +13484,19 @@
     </row>
     <row r="52" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
-        <v>1197</v>
+        <v>1393</v>
       </c>
       <c r="B52" s="1">
         <v>5</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>1031</v>
+        <v>1227</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>1198</v>
+        <v>1394</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>1199</v>
+        <v>1395</v>
       </c>
       <c r="F52" s="1">
         <v>2153</v>
@@ -11657,19 +13514,19 @@
         <v>55</v>
       </c>
       <c r="K52" s="1" t="s">
-        <v>1200</v>
+        <v>1396</v>
       </c>
       <c r="L52" s="1" t="s">
         <v>668</v>
       </c>
       <c r="M52" s="1" t="s">
-        <v>1201</v>
+        <v>1397</v>
       </c>
       <c r="N52" s="1" t="s">
         <v>635</v>
       </c>
       <c r="O52" s="1" t="s">
-        <v>1202</v>
+        <v>1398</v>
       </c>
       <c r="P52" s="1" t="s">
         <v>639</v>
@@ -11683,16 +13540,16 @@
     </row>
     <row r="53" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
-        <v>1203</v>
+        <v>1399</v>
       </c>
       <c r="B53" s="1">
         <v>5</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>1017</v>
+        <v>1213</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>1204</v>
+        <v>1400</v>
       </c>
       <c r="E53" s="1" t="s">
         <v>55</v>
@@ -11739,19 +13596,19 @@
     </row>
     <row r="54" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
-        <v>1205</v>
+        <v>1401</v>
       </c>
       <c r="B54" s="1">
         <v>5</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>1031</v>
+        <v>1227</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>1206</v>
+        <v>1402</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>1207</v>
+        <v>1403</v>
       </c>
       <c r="F54" s="1">
         <v>2156</v>
@@ -11769,22 +13626,22 @@
         <v>55</v>
       </c>
       <c r="K54" s="1" t="s">
-        <v>1208</v>
+        <v>1404</v>
       </c>
       <c r="L54" s="1" t="s">
         <v>674</v>
       </c>
       <c r="M54" s="1" t="s">
-        <v>1209</v>
+        <v>1405</v>
       </c>
       <c r="N54" s="1" t="s">
         <v>660</v>
       </c>
       <c r="O54" s="1" t="s">
-        <v>1210</v>
+        <v>1406</v>
       </c>
       <c r="P54" s="1" t="s">
-        <v>1211</v>
+        <v>1407</v>
       </c>
       <c r="Q54" s="1" t="s">
         <v>55</v>
@@ -11795,16 +13652,16 @@
     </row>
     <row r="55" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
-        <v>1212</v>
+        <v>1408</v>
       </c>
       <c r="B55" s="1">
         <v>5</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>1031</v>
+        <v>1227</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>1213</v>
+        <v>1409</v>
       </c>
       <c r="E55" s="1" t="s">
         <v>55</v>
@@ -11825,19 +13682,19 @@
         <v>55</v>
       </c>
       <c r="K55" s="1" t="s">
-        <v>1214</v>
+        <v>1410</v>
       </c>
       <c r="L55" s="1" t="s">
         <v>668</v>
       </c>
       <c r="M55" s="1" t="s">
-        <v>1215</v>
+        <v>1411</v>
       </c>
       <c r="N55" s="1" t="s">
         <v>842</v>
       </c>
       <c r="O55" s="1" t="s">
-        <v>1037</v>
+        <v>1233</v>
       </c>
       <c r="P55" s="1" t="s">
         <v>647</v>
@@ -11851,16 +13708,16 @@
     </row>
     <row r="56" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
-        <v>1216</v>
+        <v>1412</v>
       </c>
       <c r="B56" s="1">
         <v>5</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>1017</v>
+        <v>1213</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>1217</v>
+        <v>1413</v>
       </c>
       <c r="E56" s="1" t="s">
         <v>55</v>
@@ -11907,16 +13764,16 @@
     </row>
     <row r="57" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
-        <v>1218</v>
+        <v>1414</v>
       </c>
       <c r="B57" s="1">
         <v>5</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>1017</v>
+        <v>1213</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>1219</v>
+        <v>1415</v>
       </c>
       <c r="E57" s="1" t="s">
         <v>55</v>
@@ -11963,16 +13820,16 @@
     </row>
     <row r="58" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
-        <v>1220</v>
+        <v>1416</v>
       </c>
       <c r="B58" s="1">
         <v>5</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>1031</v>
+        <v>1227</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>1221</v>
+        <v>1417</v>
       </c>
       <c r="E58" s="1" t="s">
         <v>55</v>
@@ -11993,19 +13850,19 @@
         <v>55</v>
       </c>
       <c r="K58" s="1" t="s">
-        <v>1222</v>
+        <v>1418</v>
       </c>
       <c r="L58" s="1" t="s">
         <v>668</v>
       </c>
       <c r="M58" s="1" t="s">
-        <v>1223</v>
+        <v>1419</v>
       </c>
       <c r="N58" s="1" t="s">
-        <v>1224</v>
+        <v>1420</v>
       </c>
       <c r="O58" s="1" t="s">
-        <v>1225</v>
+        <v>1421</v>
       </c>
       <c r="P58" s="1" t="s">
         <v>639</v>
@@ -12019,16 +13876,16 @@
     </row>
     <row r="59" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
-        <v>1226</v>
+        <v>1422</v>
       </c>
       <c r="B59" s="1">
         <v>5</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>1023</v>
+        <v>1219</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>1227</v>
+        <v>1423</v>
       </c>
       <c r="E59" s="1" t="s">
         <v>55</v>
@@ -12075,16 +13932,16 @@
     </row>
     <row r="60" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
-        <v>1228</v>
+        <v>1424</v>
       </c>
       <c r="B60" s="1">
         <v>5</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>1017</v>
+        <v>1213</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>1229</v>
+        <v>1425</v>
       </c>
       <c r="E60" s="1" t="s">
         <v>55</v>
@@ -12131,16 +13988,16 @@
     </row>
     <row r="61" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
-        <v>1230</v>
+        <v>1426</v>
       </c>
       <c r="B61" s="1">
         <v>5</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>1017</v>
+        <v>1213</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>1231</v>
+        <v>1427</v>
       </c>
       <c r="E61" s="1" t="s">
         <v>55</v>
@@ -12187,16 +14044,16 @@
     </row>
     <row r="62" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
-        <v>1232</v>
+        <v>1428</v>
       </c>
       <c r="B62" s="1">
         <v>6</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>1017</v>
+        <v>1213</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>1233</v>
+        <v>1429</v>
       </c>
       <c r="E62" s="1" t="s">
         <v>55</v>
@@ -12243,19 +14100,19 @@
     </row>
     <row r="63" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
-        <v>1234</v>
+        <v>1430</v>
       </c>
       <c r="B63" s="1">
         <v>6</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>1031</v>
+        <v>1227</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>1235</v>
+        <v>1431</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>1236</v>
+        <v>1432</v>
       </c>
       <c r="F63" s="1">
         <v>2199</v>
@@ -12273,19 +14130,19 @@
         <v>55</v>
       </c>
       <c r="K63" s="1" t="s">
-        <v>1237</v>
+        <v>1433</v>
       </c>
       <c r="L63" s="1" t="s">
         <v>668</v>
       </c>
       <c r="M63" s="1" t="s">
-        <v>1238</v>
+        <v>1434</v>
       </c>
       <c r="N63" s="1" t="s">
         <v>660</v>
       </c>
       <c r="O63" s="1" t="s">
-        <v>1239</v>
+        <v>1435</v>
       </c>
       <c r="P63" s="1" t="s">
         <v>674</v>
@@ -12299,16 +14156,16 @@
     </row>
     <row r="64" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
-        <v>1240</v>
+        <v>1436</v>
       </c>
       <c r="B64" s="1">
         <v>6</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>1017</v>
+        <v>1213</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>1241</v>
+        <v>1437</v>
       </c>
       <c r="E64" s="1" t="s">
         <v>55</v>
@@ -12355,16 +14212,16 @@
     </row>
     <row r="65" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
-        <v>1242</v>
+        <v>1438</v>
       </c>
       <c r="B65" s="1">
         <v>6</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>1023</v>
+        <v>1219</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>1243</v>
+        <v>1439</v>
       </c>
       <c r="E65" s="1" t="s">
         <v>55</v>
@@ -12411,16 +14268,16 @@
     </row>
     <row r="66" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
-        <v>1244</v>
+        <v>1440</v>
       </c>
       <c r="B66" s="1">
         <v>6</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>1017</v>
+        <v>1213</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>1245</v>
+        <v>1441</v>
       </c>
       <c r="E66" s="1" t="s">
         <v>55</v>
@@ -12467,16 +14324,16 @@
     </row>
     <row r="67" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
-        <v>1246</v>
+        <v>1442</v>
       </c>
       <c r="B67" s="1">
         <v>6</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>1031</v>
+        <v>1227</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>1247</v>
+        <v>1443</v>
       </c>
       <c r="E67" s="1" t="s">
         <v>55</v>
@@ -12497,19 +14354,19 @@
         <v>55</v>
       </c>
       <c r="K67" s="1" t="s">
-        <v>1248</v>
+        <v>1444</v>
       </c>
       <c r="L67" s="1" t="s">
         <v>660</v>
       </c>
       <c r="M67" s="1" t="s">
-        <v>1249</v>
+        <v>1445</v>
       </c>
       <c r="N67" s="1" t="s">
         <v>793</v>
       </c>
       <c r="O67" s="1" t="s">
-        <v>1250</v>
+        <v>1446</v>
       </c>
       <c r="P67" s="1" t="s">
         <v>847</v>
@@ -12523,19 +14380,19 @@
     </row>
     <row r="68" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
-        <v>1251</v>
+        <v>1447</v>
       </c>
       <c r="B68" s="1">
         <v>6</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>1031</v>
+        <v>1227</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>1252</v>
+        <v>1448</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>1253</v>
+        <v>1449</v>
       </c>
       <c r="F68" s="1">
         <v>2228</v>
@@ -12553,19 +14410,19 @@
         <v>55</v>
       </c>
       <c r="K68" s="1" t="s">
-        <v>1254</v>
+        <v>1450</v>
       </c>
       <c r="L68" s="1" t="s">
         <v>674</v>
       </c>
       <c r="M68" s="1" t="s">
-        <v>1255</v>
+        <v>1451</v>
       </c>
       <c r="N68" s="1" t="s">
-        <v>1256</v>
+        <v>1452</v>
       </c>
       <c r="O68" s="1" t="s">
-        <v>1257</v>
+        <v>1453</v>
       </c>
       <c r="P68" s="1" t="s">
         <v>643</v>
@@ -12579,16 +14436,16 @@
     </row>
     <row r="69" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="s">
-        <v>1258</v>
+        <v>1454</v>
       </c>
       <c r="B69" s="1">
         <v>6</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>1017</v>
+        <v>1213</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>1259</v>
+        <v>1455</v>
       </c>
       <c r="E69" s="1" t="s">
         <v>55</v>
@@ -12635,19 +14492,19 @@
     </row>
     <row r="70" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
-        <v>1260</v>
+        <v>1456</v>
       </c>
       <c r="B70" s="1">
         <v>6</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>1031</v>
+        <v>1227</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>1261</v>
+        <v>1457</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>1262</v>
+        <v>1458</v>
       </c>
       <c r="F70" s="1">
         <v>2231</v>
@@ -12665,22 +14522,22 @@
         <v>55</v>
       </c>
       <c r="K70" s="1" t="s">
-        <v>1263</v>
+        <v>1459</v>
       </c>
       <c r="L70" s="1" t="s">
         <v>668</v>
       </c>
       <c r="M70" s="1" t="s">
-        <v>1264</v>
+        <v>1460</v>
       </c>
       <c r="N70" s="1" t="s">
-        <v>1114</v>
+        <v>1310</v>
       </c>
       <c r="O70" s="1" t="s">
-        <v>1265</v>
+        <v>1461</v>
       </c>
       <c r="P70" s="1" t="s">
-        <v>1266</v>
+        <v>1462</v>
       </c>
       <c r="Q70" s="1" t="s">
         <v>55</v>
@@ -12691,19 +14548,19 @@
     </row>
     <row r="71" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
-        <v>1267</v>
+        <v>1463</v>
       </c>
       <c r="B71" s="1">
         <v>6</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>1023</v>
+        <v>1219</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>1268</v>
+        <v>1464</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>1269</v>
+        <v>1465</v>
       </c>
       <c r="F71" s="1">
         <v>2232</v>
@@ -12747,16 +14604,16 @@
     </row>
     <row r="72" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
-        <v>1270</v>
+        <v>1466</v>
       </c>
       <c r="B72" s="1">
         <v>6</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>1017</v>
+        <v>1213</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>1271</v>
+        <v>1467</v>
       </c>
       <c r="E72" s="1" t="s">
         <v>55</v>
@@ -12803,16 +14660,16 @@
     </row>
     <row r="73" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
-        <v>1272</v>
+        <v>1468</v>
       </c>
       <c r="B73" s="1">
         <v>6</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>1017</v>
+        <v>1213</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>1273</v>
+        <v>1469</v>
       </c>
       <c r="E73" s="1" t="s">
         <v>55</v>
@@ -12859,16 +14716,16 @@
     </row>
     <row r="74" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
-        <v>1274</v>
+        <v>1470</v>
       </c>
       <c r="B74" s="1">
         <v>6</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>1031</v>
+        <v>1227</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>1275</v>
+        <v>1471</v>
       </c>
       <c r="E74" s="1" t="s">
         <v>55</v>
@@ -12889,19 +14746,19 @@
         <v>55</v>
       </c>
       <c r="K74" s="1" t="s">
-        <v>1276</v>
+        <v>1472</v>
       </c>
       <c r="L74" s="1" t="s">
         <v>674</v>
       </c>
       <c r="M74" s="1" t="s">
-        <v>1277</v>
+        <v>1473</v>
       </c>
       <c r="N74" s="1" t="s">
-        <v>1278</v>
+        <v>1474</v>
       </c>
       <c r="O74" s="1" t="s">
-        <v>1279</v>
+        <v>1475</v>
       </c>
       <c r="P74" s="1" t="s">
         <v>703</v>
@@ -12915,16 +14772,16 @@
     </row>
     <row r="75" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="s">
-        <v>1280</v>
+        <v>1476</v>
       </c>
       <c r="B75" s="1">
         <v>6</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>1017</v>
+        <v>1213</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>1281</v>
+        <v>1477</v>
       </c>
       <c r="E75" s="1" t="s">
         <v>55</v>
@@ -12971,16 +14828,16 @@
     </row>
     <row r="76" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
-        <v>1282</v>
+        <v>1478</v>
       </c>
       <c r="B76" s="1">
         <v>6</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>1031</v>
+        <v>1227</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>1283</v>
+        <v>1479</v>
       </c>
       <c r="E76" s="1" t="s">
         <v>55</v>
@@ -13001,19 +14858,19 @@
         <v>55</v>
       </c>
       <c r="K76" s="1" t="s">
-        <v>1284</v>
+        <v>1480</v>
       </c>
       <c r="L76" s="1" t="s">
-        <v>1285</v>
+        <v>1481</v>
       </c>
       <c r="M76" s="1" t="s">
-        <v>1286</v>
+        <v>1482</v>
       </c>
       <c r="N76" s="1" t="s">
         <v>631</v>
       </c>
       <c r="O76" s="1" t="s">
-        <v>1287</v>
+        <v>1483</v>
       </c>
       <c r="P76" s="1" t="s">
         <v>641</v>
@@ -13027,16 +14884,16 @@
     </row>
     <row r="77" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A77" s="1" t="s">
-        <v>1288</v>
+        <v>1484</v>
       </c>
       <c r="B77" s="1">
         <v>6</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>1017</v>
+        <v>1213</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>1289</v>
+        <v>1485</v>
       </c>
       <c r="E77" s="1" t="s">
         <v>55</v>
@@ -13083,19 +14940,19 @@
     </row>
     <row r="78" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A78" s="1" t="s">
-        <v>1290</v>
+        <v>1486</v>
       </c>
       <c r="B78" s="1">
         <v>7</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>1023</v>
+        <v>1219</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>1291</v>
+        <v>1487</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>1052</v>
+        <v>1248</v>
       </c>
       <c r="F78" s="1">
         <v>2261</v>
@@ -13139,19 +14996,19 @@
     </row>
     <row r="79" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A79" s="1" t="s">
-        <v>1292</v>
+        <v>1488</v>
       </c>
       <c r="B79" s="1">
         <v>7</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>1031</v>
+        <v>1227</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>1293</v>
+        <v>1489</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>1294</v>
+        <v>1490</v>
       </c>
       <c r="F79" s="1">
         <v>2275</v>
@@ -13169,19 +15026,19 @@
         <v>55</v>
       </c>
       <c r="K79" s="1" t="s">
-        <v>1295</v>
+        <v>1491</v>
       </c>
       <c r="L79" s="1" t="s">
         <v>668</v>
       </c>
       <c r="M79" s="1" t="s">
-        <v>1296</v>
+        <v>1492</v>
       </c>
       <c r="N79" s="1" t="s">
-        <v>1297</v>
+        <v>1493</v>
       </c>
       <c r="O79" s="1" t="s">
-        <v>1298</v>
+        <v>1494</v>
       </c>
       <c r="P79" s="1" t="s">
         <v>674</v>
@@ -13195,16 +15052,16 @@
     </row>
     <row r="80" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A80" s="1" t="s">
-        <v>1299</v>
+        <v>1495</v>
       </c>
       <c r="B80" s="1">
         <v>7</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>1031</v>
+        <v>1227</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>1300</v>
+        <v>1496</v>
       </c>
       <c r="E80" s="1" t="s">
         <v>55</v>
@@ -13225,19 +15082,19 @@
         <v>55</v>
       </c>
       <c r="K80" s="1" t="s">
-        <v>1301</v>
+        <v>1497</v>
       </c>
       <c r="L80" s="1" t="s">
-        <v>1302</v>
+        <v>1498</v>
       </c>
       <c r="M80" s="1" t="s">
-        <v>1303</v>
+        <v>1499</v>
       </c>
       <c r="N80" s="1" t="s">
         <v>674</v>
       </c>
       <c r="O80" s="1" t="s">
-        <v>1304</v>
+        <v>1500</v>
       </c>
       <c r="P80" s="1" t="s">
         <v>847</v>
@@ -13251,16 +15108,16 @@
     </row>
     <row r="81" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="s">
-        <v>1305</v>
+        <v>1501</v>
       </c>
       <c r="B81" s="1">
         <v>7</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>1017</v>
+        <v>1213</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>1306</v>
+        <v>1502</v>
       </c>
       <c r="E81" s="1" t="s">
         <v>55</v>
@@ -13307,16 +15164,16 @@
     </row>
     <row r="82" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A82" s="1" t="s">
-        <v>1307</v>
+        <v>1503</v>
       </c>
       <c r="B82" s="1">
         <v>7</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>1031</v>
+        <v>1227</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>1308</v>
+        <v>1504</v>
       </c>
       <c r="E82" s="1" t="s">
         <v>55</v>
@@ -13337,19 +15194,19 @@
         <v>55</v>
       </c>
       <c r="K82" s="1" t="s">
-        <v>1309</v>
+        <v>1505</v>
       </c>
       <c r="L82" s="1" t="s">
-        <v>1310</v>
+        <v>1506</v>
       </c>
       <c r="M82" s="1" t="s">
-        <v>1311</v>
+        <v>1507</v>
       </c>
       <c r="N82" s="1" t="s">
-        <v>1312</v>
+        <v>1508</v>
       </c>
       <c r="O82" s="1" t="s">
-        <v>1313</v>
+        <v>1509</v>
       </c>
       <c r="P82" s="1" t="s">
         <v>660</v>
@@ -13363,16 +15220,16 @@
     </row>
     <row r="83" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A83" s="1" t="s">
-        <v>1314</v>
+        <v>1510</v>
       </c>
       <c r="B83" s="1">
         <v>7</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>1031</v>
+        <v>1227</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>1315</v>
+        <v>1511</v>
       </c>
       <c r="E83" s="1" t="s">
         <v>55</v>
@@ -13393,22 +15250,22 @@
         <v>55</v>
       </c>
       <c r="K83" s="1" t="s">
-        <v>1316</v>
+        <v>1512</v>
       </c>
       <c r="L83" s="1" t="s">
         <v>674</v>
       </c>
       <c r="M83" s="1" t="s">
-        <v>1317</v>
+        <v>1513</v>
       </c>
       <c r="N83" s="1" t="s">
-        <v>1318</v>
+        <v>1514</v>
       </c>
       <c r="O83" s="1" t="s">
-        <v>1319</v>
+        <v>1515</v>
       </c>
       <c r="P83" s="1" t="s">
-        <v>1320</v>
+        <v>1516</v>
       </c>
       <c r="Q83" s="1" t="s">
         <v>55</v>
@@ -13419,16 +15276,16 @@
     </row>
     <row r="84" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A84" s="1" t="s">
-        <v>1321</v>
+        <v>1517</v>
       </c>
       <c r="B84" s="1">
         <v>7</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>1017</v>
+        <v>1213</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>1322</v>
+        <v>1518</v>
       </c>
       <c r="E84" s="1" t="s">
         <v>55</v>
@@ -13475,16 +15332,16 @@
     </row>
     <row r="85" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A85" s="1" t="s">
-        <v>1323</v>
+        <v>1519</v>
       </c>
       <c r="B85" s="1">
         <v>7</v>
       </c>
       <c r="C85" s="1" t="s">
-        <v>1017</v>
+        <v>1213</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>1324</v>
+        <v>1520</v>
       </c>
       <c r="E85" s="1" t="s">
         <v>55</v>
@@ -13531,16 +15388,16 @@
     </row>
     <row r="86" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A86" s="1" t="s">
-        <v>1325</v>
+        <v>1521</v>
       </c>
       <c r="B86" s="1">
         <v>7</v>
       </c>
       <c r="C86" s="1" t="s">
-        <v>1031</v>
+        <v>1227</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>1326</v>
+        <v>1522</v>
       </c>
       <c r="E86" s="1" t="s">
         <v>55</v>
@@ -13561,22 +15418,22 @@
         <v>55</v>
       </c>
       <c r="K86" s="1" t="s">
-        <v>1327</v>
+        <v>1523</v>
       </c>
       <c r="L86" s="1" t="s">
         <v>633</v>
       </c>
       <c r="M86" s="1" t="s">
-        <v>1328</v>
+        <v>1524</v>
       </c>
       <c r="N86" s="1" t="s">
-        <v>1310</v>
+        <v>1506</v>
       </c>
       <c r="O86" s="1" t="s">
-        <v>1329</v>
+        <v>1525</v>
       </c>
       <c r="P86" s="1" t="s">
-        <v>1330</v>
+        <v>1526</v>
       </c>
       <c r="Q86" s="1" t="s">
         <v>55</v>
@@ -13587,16 +15444,16 @@
     </row>
     <row r="87" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A87" s="1" t="s">
-        <v>1331</v>
+        <v>1527</v>
       </c>
       <c r="B87" s="1">
         <v>7</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>1017</v>
+        <v>1213</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>1332</v>
+        <v>1528</v>
       </c>
       <c r="E87" s="1" t="s">
         <v>55</v>
@@ -13643,16 +15500,16 @@
     </row>
     <row r="88" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A88" s="1" t="s">
-        <v>1333</v>
+        <v>1529</v>
       </c>
       <c r="B88" s="1">
         <v>7</v>
       </c>
       <c r="C88" s="1" t="s">
-        <v>1023</v>
+        <v>1219</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>1334</v>
+        <v>1530</v>
       </c>
       <c r="E88" s="1" t="s">
         <v>55</v>
@@ -13699,19 +15556,19 @@
     </row>
     <row r="89" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A89" s="1" t="s">
-        <v>1335</v>
+        <v>1531</v>
       </c>
       <c r="B89" s="1">
         <v>7</v>
       </c>
       <c r="C89" s="1" t="s">
-        <v>1031</v>
+        <v>1227</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>1336</v>
+        <v>1532</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>1337</v>
+        <v>1533</v>
       </c>
       <c r="F89" s="1">
         <v>2304</v>
@@ -13729,22 +15586,22 @@
         <v>55</v>
       </c>
       <c r="K89" s="1" t="s">
-        <v>1338</v>
+        <v>1534</v>
       </c>
       <c r="L89" s="1" t="s">
-        <v>1339</v>
+        <v>1535</v>
       </c>
       <c r="M89" s="1" t="s">
-        <v>1340</v>
+        <v>1536</v>
       </c>
       <c r="N89" s="1" t="s">
-        <v>1341</v>
+        <v>1537</v>
       </c>
       <c r="O89" s="1" t="s">
-        <v>1342</v>
+        <v>1538</v>
       </c>
       <c r="P89" s="1" t="s">
-        <v>1343</v>
+        <v>1539</v>
       </c>
       <c r="Q89" s="1" t="s">
         <v>55</v>
@@ -13755,19 +15612,19 @@
     </row>
     <row r="90" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A90" s="1" t="s">
-        <v>1344</v>
+        <v>1540</v>
       </c>
       <c r="B90" s="1">
         <v>7</v>
       </c>
       <c r="C90" s="1" t="s">
-        <v>1023</v>
+        <v>1219</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>1345</v>
+        <v>1541</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>1346</v>
+        <v>1542</v>
       </c>
       <c r="F90" s="1">
         <v>2308</v>
@@ -13811,19 +15668,19 @@
     </row>
     <row r="91" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
-        <v>1347</v>
+        <v>1543</v>
       </c>
       <c r="B91" s="1">
         <v>7</v>
       </c>
       <c r="C91" s="1" t="s">
-        <v>1017</v>
+        <v>1213</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>1348</v>
+        <v>1544</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>1349</v>
+        <v>1545</v>
       </c>
       <c r="F91" s="1">
         <v>2310</v>
@@ -13884,7 +15741,7 @@
   <sheetData>
     <row r="1" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>1350</v>
+        <v>1546</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
@@ -13892,10 +15749,10 @@
     </row>
     <row r="2" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
-        <v>1351</v>
+        <v>1547</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>1352</v>
+        <v>1548</v>
       </c>
       <c r="C2" s="5" t="s">
         <v>908</v>
@@ -13909,13 +15766,13 @@
         <v>1</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>1353</v>
+        <v>1549</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>1354</v>
+        <v>1550</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>1355</v>
+        <v>1551</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -13923,13 +15780,13 @@
         <v>2</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>1356</v>
+        <v>1552</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>1357</v>
+        <v>1553</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>1358</v>
+        <v>1554</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -13937,13 +15794,13 @@
         <v>3</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>1359</v>
+        <v>1555</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>1360</v>
+        <v>1556</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>1361</v>
+        <v>1557</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -13951,13 +15808,13 @@
         <v>4</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>1362</v>
+        <v>1558</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>1363</v>
+        <v>1559</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>1364</v>
+        <v>1560</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -13965,13 +15822,13 @@
         <v>5</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>1365</v>
+        <v>1561</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>1366</v>
+        <v>1562</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>1367</v>
+        <v>1563</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -13979,13 +15836,13 @@
         <v>6</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>1368</v>
+        <v>1564</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>1369</v>
+        <v>1565</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>1370</v>
+        <v>1566</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -13993,13 +15850,13 @@
         <v>7</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>1371</v>
+        <v>1567</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>1372</v>
+        <v>1568</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>1373</v>
+        <v>1569</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -14007,13 +15864,13 @@
         <v>8</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>1374</v>
+        <v>1570</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>1375</v>
+        <v>1571</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>1376</v>
+        <v>1572</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -14021,13 +15878,13 @@
         <v>9</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>1377</v>
+        <v>1573</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>1378</v>
+        <v>1574</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>1379</v>
+        <v>1575</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -14035,13 +15892,13 @@
         <v>10</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>1380</v>
+        <v>1576</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>1381</v>
+        <v>1577</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>1382</v>
+        <v>1578</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -14049,13 +15906,13 @@
         <v>11</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>1383</v>
+        <v>1579</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>1384</v>
+        <v>1580</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>1385</v>
+        <v>1581</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -14063,13 +15920,13 @@
         <v>12</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>1386</v>
+        <v>1582</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>1387</v>
+        <v>1583</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>1388</v>
+        <v>1584</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -14077,13 +15934,13 @@
         <v>13</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>1389</v>
+        <v>1585</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>1390</v>
+        <v>1586</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>1391</v>
+        <v>1587</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -14091,13 +15948,13 @@
         <v>14</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>1392</v>
+        <v>1588</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>1393</v>
+        <v>1589</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>1394</v>
+        <v>1590</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
@@ -14105,13 +15962,13 @@
         <v>15</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>1395</v>
+        <v>1591</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>1396</v>
+        <v>1592</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>1397</v>
+        <v>1593</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
@@ -14119,13 +15976,13 @@
         <v>16</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>1398</v>
+        <v>1594</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>1399</v>
+        <v>1595</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>1400</v>
+        <v>1596</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -14133,13 +15990,13 @@
         <v>17</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>1401</v>
+        <v>1597</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>1402</v>
+        <v>1598</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>1403</v>
+        <v>1599</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -14147,13 +16004,13 @@
         <v>18</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>1404</v>
+        <v>1600</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>1405</v>
+        <v>1601</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>1406</v>
+        <v>1602</v>
       </c>
     </row>
   </sheetData>
@@ -14175,7 +16032,7 @@
   <sheetData>
     <row r="1" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>1407</v>
+        <v>1603</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
@@ -14190,10 +16047,10 @@
         <v>298</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>1408</v>
+        <v>1604</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>1409</v>
+        <v>1605</v>
       </c>
       <c r="E2" s="5" t="s">
         <v>301</v>
@@ -14201,33 +16058,33 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>1410</v>
+        <v>1606</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>1411</v>
+        <v>1607</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>1412</v>
+        <v>1608</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>1413</v>
+        <v>1609</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>1414</v>
+        <v>1610</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>1415</v>
+        <v>1611</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>1416</v>
+        <v>1612</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>1417</v>
+        <v>1613</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>1418</v>
+        <v>1614</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>55</v>
@@ -14235,53 +16092,53 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>1419</v>
+        <v>1615</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>1420</v>
+        <v>1616</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>1421</v>
+        <v>1617</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>1422</v>
+        <v>1618</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>1423</v>
+        <v>1619</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>1424</v>
+        <v>1620</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>1425</v>
+        <v>1621</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>1426</v>
+        <v>1622</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>1427</v>
+        <v>1623</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>1428</v>
+        <v>1624</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>1429</v>
+        <v>1625</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>1430</v>
+        <v>1626</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>1431</v>
+        <v>1627</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>1432</v>
+        <v>1628</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>1433</v>
+        <v>1629</v>
       </c>
     </row>
   </sheetData>

--- a/content.xlsx
+++ b/content.xlsx
@@ -337,7 +337,7 @@
     <t>หาบเร่ (ผู้เร่ขายของรายย่อยตามหมู่บ้านและชายป่า)</t>
   </si>
   <si>
-    <t>วานิชตลาดนัด (พ่อค้าที่มีแผงประจำในตลาดชุมชนหรือตลาดหน้าวัดฉ</t>
+    <t>วานิชตลาดนัด (พ่อค้าที่มีแผงประจำในตลาดชุมชนหรือตลาดหน้าวัด)</t>
   </si>
   <si>
     <t>พ่อค้าเรือแพ (ค้าขายตามลำน้ำหลัก)</t>
@@ -391,7 +391,7 @@
     <t>มหาเศรษฐีรัตนราชธานี (ผู้มั่งคั่งที่สุดในพระนคร)</t>
   </si>
   <si>
-    <t>อัครมุขมนตรีศรีมหาโชติเศรษฐี</t>
+    <t>อัครมุขมนตรีศรีมหาโชติเศรษฐี (มหาเศรษฐีผู้ค้ำจุนพระคลังทั้งแผ่นดิน เป็นที่ปรึกษาการค้ากับนานาประเทศ)</t>
   </si>
   <si>
     <t>นายหน้าโรงบ่อน (ผู้ดูแลผลประโยชน์ในที่อโคจร)</t>
@@ -445,7 +445,7 @@
     <t>เจ้าสัวล่มอาณาจักร (มหาเศรษฐีที่รวยจนคุกคามเสถียรภาพรัฐ)</t>
   </si>
   <si>
-    <t>อัครสมุหเศรษฐีทุจริตวิบัติ</t>
+    <t>อัครสมุหเศรษฐีทุจริตวิบัติ (เจ้าพ่อการค้าที่ผูกขาดทุกเส้นทางด้วยการโกงและติดสินบน จนพระคลังสั่นคลอน)</t>
   </si>
   <si>
     <t>ไพร่กสิกรรม ผู้ใช้แรงงานในไร่นาพื้นฐานตามระบบกอร์เว</t>
@@ -505,7 +505,7 @@
     <t>อัครเกษตราธิการศรีอโยธยา (ที่สุดแห่งสายงานกสิกรรม)</t>
   </si>
   <si>
-    <t>อัครสมุหเกษตราธิบดีวิสุทธิกร</t>
+    <t>อัครสมุหเกษตราธิบดีวิสุทธิกร (ผู้ดูแลยุ้งฉางและที่นาหลวงทั่วราชอาณาจักร ให้ไพร่ฟ้าอิ่มท้องทุกฤดู)</t>
   </si>
   <si>
     <t>คนบุกรุกป่าสงวน (ถางพงขยายที่นาโดยพละการ)</t>
@@ -559,13 +559,13 @@
     <t>จอมอาสัจอธรรมเกษตร (ผู้กุมความลับการทำลายอาหารอาณาจักร)</t>
   </si>
   <si>
-    <t>จอมอวตารอสุรกสิกรรมล่มธาตรี</t>
+    <t>จอมอวตารอสุรกสิกรรมล่มธาตรี (ผู้กุมเสบียงทั้งแผ่นดินไว้ในมือ ปล่อยให้ข้าวยากหมากแพงเพื่ออำนาจของตน)</t>
   </si>
   <si>
     <t>มหาดเล็กรายงาน (ผู้รับใช้เริ่มเรียนรู้งานในพระราชวัง)</t>
   </si>
   <si>
-    <t>ทนายหน้าหอ (ผู้คุมเอกสารและรับส่งคำสั่งเบ่วงต้นให้ขุนนาง</t>
+    <t>ทนายหน้าหอ (ผู้คุมเอกสารและรับส่งคำสั่งเบื้องต้นให้ขุนนาง)</t>
   </si>
   <si>
     <t>พนักงานอาลักษณ์ (ผู้คัดลอกราชสาส์น/กฎหมาย)</t>
@@ -577,7 +577,7 @@
     <t>ข้าหลวงตรวจการบัญชี (ตรวจสอบไพร่พล)</t>
   </si>
   <si>
-    <t>พนักงานสถาบันกระบวนการยุติธรรม</t>
+    <t>พนักงานสถาบันกระบวนการยุติธรรม (เจ้าพนักงานในศาล ช่วยไต่สวนความและจดคำให้การ)</t>
   </si>
   <si>
     <t>เจ้ากรมมหาดไทยฝ่ายเหนือ (คุมพลเรือนหัวเมืองเหนือ)</t>
@@ -589,7 +589,7 @@
     <t>ราชทูตเจริญสัมพันธไมตรี (ผู้แทนทางการทูต)</t>
   </si>
   <si>
-    <t>ข้าหลวงผู้รักษากฎมณเฑียรบาล</t>
+    <t>ข้าหลวงผู้รักษากฎมณเฑียรบาล (ขุนนางผู้กำกับให้ราชสำนักเป็นไปตามกฎมณเฑียรบาล)</t>
   </si>
   <si>
     <t>โกษาธิบดี (พระคลัง) (คุมการคลัง/ต่างประเทศ)</t>
@@ -604,22 +604,22 @@
     <t>ราชปุโรหิตพฤฒาจารย์ (ที่ปรึกษาสูงสุดฝั่งพลเรือน)</t>
   </si>
   <si>
-    <t>ผู้ตรวจการแผ่นดินสิบทิศ</t>
-  </si>
-  <si>
-    <t>อัครมนตรีศรีอโยธยา</t>
-  </si>
-  <si>
-    <t>ผู้สำเร็จราชการแผ่นดินฝ่ายพลเรือน</t>
-  </si>
-  <si>
-    <t>มหาอำมาตย์รัตนราชธานี</t>
-  </si>
-  <si>
-    <t>อัครมุขมนตรีศรีสวัสดิพิจิตร</t>
-  </si>
-  <si>
-    <t>อัครสมุหอมาตย์ศรีวิสุทธิบรมนาถ</t>
+    <t>ผู้ตรวจการแผ่นดินสิบทิศ (ผู้ออกตรวจราชการหัวเมืองทุกทิศ สอบความทุกข์ร้อนของราษฎร)</t>
+  </si>
+  <si>
+    <t>อัครมนตรีศรีอโยธยา (เสนาบดีผู้ใหญ่ที่ทรงไว้วางพระทัยให้ว่าราชการสำคัญของกรุง)</t>
+  </si>
+  <si>
+    <t>ผู้สำเร็จราชการแผ่นดินฝ่ายพลเรือน (ผู้ว่าราชการแผ่นดินฝ่ายพลเรือนแทนพระองค์ยามเสด็จไม่อยู่)</t>
+  </si>
+  <si>
+    <t>มหาอำมาตย์รัตนราชธานี (มหาอำมาตย์ผู้บังคับบัญชาจตุสดมภ์ทั้งสี่กรม)</t>
+  </si>
+  <si>
+    <t>อัครมุขมนตรีศรีสวัสดิพิจิตร (อัครเสนาบดีผู้ถวายคำปรึกษาราชการแผ่นดินโดยตรง)</t>
+  </si>
+  <si>
+    <t>อัครสมุหอมาตย์ศรีวิสุทธิบรมนาถ (ยอดขุนนางฝ่ายพลเรือน ผู้วางรากฐานการปกครองให้บ้านเมืองสงบร่มเย็น)</t>
   </si>
   <si>
     <t>พนักงานส่วยนอกบัญชี (ผู้แอบเก็บส่วยเข้าตัว)</t>
@@ -667,13 +667,13 @@
     <t>จอมบงการวิบัติเศรษฐกิจ (ทำลายระบบการคลังเพื่อบีบรัฐ)</t>
   </si>
   <si>
-    <t>เจ้าสำนักทรราชเงาอโยธยา</t>
-  </si>
-  <si>
-    <t>พญามารหัตถ์อธรรมล่มพิภพ</t>
-  </si>
-  <si>
-    <t>อัครสมุหอธรรมจอมบงการล่มธาตรี</t>
+    <t>เจ้าสำนักทรราชเงาอโยธยา (ผู้นำกลุ่มขุนนางกังฉินที่ชักใยราชสำนักอยู่เบื้องหลัง)</t>
+  </si>
+  <si>
+    <t>พญามารหัตถ์อธรรมล่มพิภพ (ขุนนางผู้กุมอำนาจด้วยความกลัว ใครขัดขวางย่อมหายไปอย่างไร้ร่องรอย)</t>
+  </si>
+  <si>
+    <t>อัครสมุหอธรรมจอมบงการล่มธาตรี (ผู้บงการแผ่นดินจากเงามืด แม้กษัตริย์ก็ต้องเกรงใจ)</t>
   </si>
   <si>
     <t>เด็กวัด ผู้เริ่มต้นเรียนรู้อักขระขอมและพื้นฐานพระธรรมบท</t>
@@ -733,7 +733,7 @@
     <t>อัครสมุหปุโรหิตวิสุทธิรักษ์ (ผู้พิทักษ์ดวงเมือง)</t>
   </si>
   <si>
-    <t>อัครมุนีศรีสัจญาณบรมครู</t>
+    <t>อัครมุนีศรีสัจญาณบรมครู (พระราชครูผู้รอบรู้ไตรเพทและโหราศาสตร์ เป็นที่เคารพของทั้งราชสำนัก)</t>
   </si>
   <si>
     <t>หมอทำเสน่ห์ (ผู้ใช้เวทย์มนต์ในทางตัณหา)</t>
@@ -787,7 +787,7 @@
     <t>เจ้าสำนักไสยเวทย์เงามรณะ (ผู้บงการความตาย)</t>
   </si>
   <si>
-    <t>จอมขมังเวทย์วิบัติจักรวาล</t>
+    <t>จอมขมังเวทย์วิบัติจักรวาล (หมอผีผู้ใช้อาคมมืดหลอกหลอนบ้านเมือง จนผู้คนหวาดกลัวทั่วแผ่นดิน)</t>
   </si>
   <si>
     <t>ไพร่หลวง พลเมืองที่ต้องเข้าเวรรับราชการทหารตามระบบกอร์เว</t>
@@ -805,7 +805,7 @@
     <t>ทนายเลือก (องครักษ์ผู้ชำนาญอาวุธ)</t>
   </si>
   <si>
-    <t>พนักงานองครักษ์จักรนารายณ์</t>
+    <t>พนักงานองครักษ์จักรนารายณ์ (ทหารองครักษ์ผู้ถวายอารักขาใกล้ชิดเบื้องพระยุคลบาท)</t>
   </si>
   <si>
     <t>ขุนศึกกองหน้า (ผู้นำทัพทลายค่าย)</t>
@@ -814,40 +814,40 @@
     <t>หลวงพิชัยยุทธ (ผู้เจนจบตำราสงคราม)</t>
   </si>
   <si>
-    <t>พระมหามนตรีองครักษ์</t>
-  </si>
-  <si>
-    <t>เจ้าพระยาปราบปัจจามิตร</t>
+    <t>พระมหามนตรีองครักษ์ (นายกององครักษ์ผู้คุมกำลังรักษาพระองค์)</t>
+  </si>
+  <si>
+    <t>เจ้าพระยาปราบปัจจามิตร (แม่ทัพผู้ปราบศัตรูที่รุกล้ำชายแดน)</t>
   </si>
   <si>
     <t>จอมทัพพิทักษ์ปฐพี (ผู้กอบกู้เอกราช)</t>
   </si>
   <si>
-    <t>อัครมุขมนตรีมหาโยธา</t>
-  </si>
-  <si>
-    <t>อัครมหาเสนาบดีสมุหพระกลาโหม</t>
-  </si>
-  <si>
-    <t>พญาสีหราชเดโชชัยอภัยพิริยพาหุ</t>
-  </si>
-  <si>
-    <t>อัครขัตติยโยธาพิทักษ์ไอยรา</t>
+    <t>อัครมุขมนตรีมหาโยธา (เสนาบดีผู้ใหญ่ฝ่ายทหาร ถวายคำปรึกษาเรื่องการศึก)</t>
+  </si>
+  <si>
+    <t>อัครมหาเสนาบดีสมุหพระกลาโหม (สมุหพระกลาโหม ผู้บังคับบัญชาหัวเมืองฝ่ายทหารทั้งหมด)</t>
+  </si>
+  <si>
+    <t>พญาสีหราชเดโชชัยอภัยพิริยพาหุ (แม่ทัพใหญ่ผู้เก่งกล้า นำทัพหน้าออกรบด้วยตนเอง)</t>
+  </si>
+  <si>
+    <t>อัครขัตติยโยธาพิทักษ์ไอยรา (แม่ทัพช้าง ผู้บัญชาการกองช้างศึกของหลวง)</t>
   </si>
   <si>
     <t>จอมทัพพินาศทศทิศ (ผู้ปราบทุกอาณาจักร)</t>
   </si>
   <si>
-    <t>อัครสมุหมหาพิชัยสงคราม</t>
-  </si>
-  <si>
-    <t>ผู้พิทักษ์สกลพิภพสยามาธิราช</t>
-  </si>
-  <si>
-    <t>อัครมหาเสนาบดีศรีสวัสดิ์อาญาสิทธิ์</t>
-  </si>
-  <si>
-    <t>อัครสมุหมหาราชเดโชชัยวิสุทธิศักดิ์</t>
+    <t>อัครสมุหมหาพิชัยสงคราม (ผู้วางแผนพิชัยสงครามของทั้งราชอาณาจักร)</t>
+  </si>
+  <si>
+    <t>ผู้พิทักษ์สกลพิภพสยามาธิราช (จอมทัพผู้ปกป้องราชอาณาจักรจากข้าศึกทุกทิศ)</t>
+  </si>
+  <si>
+    <t>อัครมหาเสนาบดีศรีสวัสดิ์อาญาสิทธิ์ (อัครเสนาบดีฝ่ายทหาร ถือพระแสงอาญาสิทธิ์สั่งการแทนพระองค์ในยามศึก)</t>
+  </si>
+  <si>
+    <t>อัครสมุหมหาราชเดโชชัยวิสุทธิศักดิ์ (ยอดขุนศึกแห่งกรุงศรีอยุธยา ชื่อเสียงเลื่องลือไปทั่วสารทิศ)</t>
   </si>
   <si>
     <t>ทหารหนีราชการ (พลซุ่มในป่า)</t>
@@ -901,7 +901,7 @@
     <t>เจ้าสำนักขุนศึกทรราชอโยธยา (ที่สุดแห่งด้านมืด)</t>
   </si>
   <si>
-    <t>อัครสมุหอธรรมโยธาธิบดีวิบัติพิภพ</t>
+    <t>อัครสมุหอธรรมโยธาธิบดีวิบัติพิภพ (จอมทัพทรราชผู้ใช้กองทัพข่มขู่ราษฎรและราชบัลลังก์)</t>
   </si>
   <si>
     <t>ผู้เตรียมออกบวช</t>

--- a/content.xlsx
+++ b/content.xlsx
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3862" uniqueCount="1863">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3928" uniqueCount="1867">
   <si>
     <t>เนื้อหาเกมอโยธยา Idle — แก้ในไฟล์นี้แล้วรัน npm run xlsx:import เพื่อเขียนกลับเป็น data/*.json</t>
   </si>
@@ -2803,7 +2803,7 @@
     <t>ไหวพริบ+2, หลบหลีก+1</t>
   </si>
   <si>
-    <t>เสี่ยงดวง: โอกาส 0–1, ผลใส่ "บุญ+2" หรือ "ความชอบ+0.05" ได้</t>
+    <t>เสี่ยงดวง: โอกาส 0–1, ผลใส่ "บุญ+2" หรือ "ความชอบ+0.05" ได้ · หมวด: fun สันทนาการ / health สุขภาพ / vice อบายมุข / ว่าง = ทั่วไป (fun/health ขึ้นได้ตั้งแต่วัยรุ่น และขึ้นบ่อยขึ้นเมื่อความสำราญ/สุขภาพต่ำ)</t>
   </si>
   <si>
     <t>เสี่ยงดวง</t>
@@ -2821,6 +2821,9 @@
     <t>ผลล้มเหลว</t>
   </si>
   <si>
+    <t>หมวด</t>
+  </si>
+  <si>
     <t>G01</t>
   </si>
   <si>
@@ -3793,6 +3796,9 @@
     <t>บารมี-1, สำราญ-1</t>
   </si>
   <si>
+    <t>fun</t>
+  </si>
+  <si>
     <t>G42</t>
   </si>
   <si>
@@ -4042,6 +4048,9 @@
     <t>บารมี+1, ไสยเวทย์+1, สำราญ-1</t>
   </si>
   <si>
+    <t>vice</t>
+  </si>
+  <si>
     <t>G52</t>
   </si>
   <si>
@@ -4154,6 +4163,9 @@
   </si>
   <si>
     <t>โภคทรัพย์+1, สุขภาพ-1</t>
+  </si>
+  <si>
+    <t>health</t>
   </si>
   <si>
     <t>G57</t>
@@ -9368,7 +9380,7 @@
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:O67"/>
+  <dimension ref="A1:P67"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="2" width="10" style="1" customWidth="1"/>
@@ -9385,9 +9397,10 @@
     <col min="13" max="13" width="18" style="1" customWidth="1"/>
     <col min="14" max="14" width="12" style="1" customWidth="1"/>
     <col min="15" max="15" width="13" style="1" customWidth="1"/>
+    <col min="16" max="16" width="10" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>925</v>
       </c>
@@ -9405,8 +9418,9 @@
       <c r="M1" s="3"/>
       <c r="N1" s="3"/>
       <c r="O1" s="3"/>
-    </row>
-    <row r="2" spans="1:15" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="P1" s="3"/>
+    </row>
+    <row r="2" spans="1:16" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
         <v>617</v>
       </c>
@@ -9452,31 +9466,34 @@
       <c r="O2" s="5" t="s">
         <v>930</v>
       </c>
-    </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P2" s="5" t="s">
+        <v>931</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>931</v>
+        <v>932</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>933</v>
+        <v>934</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>934</v>
+        <v>935</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>935</v>
+        <v>936</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>631</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>936</v>
+        <v>937</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>937</v>
+        <v>938</v>
       </c>
       <c r="I3" s="1" t="s">
         <v>55</v>
@@ -9485,7 +9502,7 @@
         <v>55</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="L3" s="1">
         <v>0.5</v>
@@ -9494,33 +9511,36 @@
         <v>15</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>939</v>
+        <v>940</v>
       </c>
       <c r="O3" s="1" t="s">
-        <v>940</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
+        <v>941</v>
+      </c>
+      <c r="P3" s="1" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>942</v>
+        <v>943</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>943</v>
+        <v>944</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>654</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>944</v>
+        <v>945</v>
       </c>
       <c r="F4" s="1" t="s">
         <v>721</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="H4" s="1" t="s">
         <v>647</v>
@@ -9532,7 +9552,7 @@
         <v>55</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>946</v>
+        <v>947</v>
       </c>
       <c r="L4" s="1">
         <v>0.45</v>
@@ -9541,36 +9561,39 @@
         <v>10</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>947</v>
+        <v>948</v>
       </c>
       <c r="O4" s="1" t="s">
-        <v>948</v>
-      </c>
-    </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
+        <v>949</v>
+      </c>
+      <c r="P4" s="1" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>949</v>
+        <v>950</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>950</v>
+        <v>951</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>951</v>
+        <v>952</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>639</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>952</v>
+        <v>953</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>953</v>
+        <v>954</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>954</v>
+        <v>955</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>955</v>
+        <v>956</v>
       </c>
       <c r="I5" s="1" t="s">
         <v>55</v>
@@ -9579,7 +9602,7 @@
         <v>55</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>956</v>
+        <v>957</v>
       </c>
       <c r="L5" s="1">
         <v>0.5</v>
@@ -9588,33 +9611,36 @@
         <v>10</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>957</v>
+        <v>958</v>
       </c>
       <c r="O5" s="1" t="s">
-        <v>940</v>
-      </c>
-    </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+        <v>941</v>
+      </c>
+      <c r="P5" s="1" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>958</v>
+        <v>959</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>959</v>
+        <v>960</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>960</v>
+        <v>961</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>961</v>
+        <v>962</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>962</v>
+        <v>963</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>963</v>
+        <v>964</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>964</v>
+        <v>965</v>
       </c>
       <c r="H6" s="1" t="s">
         <v>680</v>
@@ -9626,7 +9652,7 @@
         <v>55</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>965</v>
+        <v>966</v>
       </c>
       <c r="L6" s="1">
         <v>0.5</v>
@@ -9635,33 +9661,36 @@
         <v>20</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>966</v>
+        <v>967</v>
       </c>
       <c r="O6" s="1" t="s">
-        <v>967</v>
-      </c>
-    </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
+        <v>968</v>
+      </c>
+      <c r="P6" s="1" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>968</v>
+        <v>969</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>969</v>
+        <v>970</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>970</v>
+        <v>971</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>696</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>971</v>
+        <v>972</v>
       </c>
       <c r="F7" s="1" t="s">
         <v>654</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
       <c r="H7" s="1" t="s">
         <v>633</v>
@@ -9673,7 +9702,7 @@
         <v>55</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="L7" s="1">
         <v>0.45</v>
@@ -9682,33 +9711,36 @@
         <v>10</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="O7" s="1" t="s">
-        <v>975</v>
-      </c>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
+        <v>976</v>
+      </c>
+      <c r="P7" s="1" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="D8" s="1" t="s">
         <v>656</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="F8" s="1" t="s">
         <v>654</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="H8" s="1" t="s">
         <v>721</v>
@@ -9720,7 +9752,7 @@
         <v>55</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>981</v>
+        <v>982</v>
       </c>
       <c r="L8" s="1">
         <v>0.5</v>
@@ -9729,33 +9761,36 @@
         <v>15</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>982</v>
+        <v>983</v>
       </c>
       <c r="O8" s="1" t="s">
-        <v>983</v>
-      </c>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
+        <v>984</v>
+      </c>
+      <c r="P8" s="1" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>984</v>
+        <v>985</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>985</v>
+        <v>986</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>986</v>
+        <v>987</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>988</v>
+        <v>989</v>
       </c>
       <c r="F9" s="1" t="s">
         <v>680</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>989</v>
+        <v>990</v>
       </c>
       <c r="H9" s="1" t="s">
         <v>696</v>
@@ -9767,7 +9802,7 @@
         <v>55</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>990</v>
+        <v>991</v>
       </c>
       <c r="L9" s="1">
         <v>0.4</v>
@@ -9776,36 +9811,39 @@
         <v>15</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>991</v>
+        <v>992</v>
       </c>
       <c r="O9" s="1" t="s">
-        <v>992</v>
-      </c>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
+        <v>993</v>
+      </c>
+      <c r="P9" s="1" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>995</v>
+        <v>996</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>643</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="F10" s="1" t="s">
         <v>639</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>998</v>
+        <v>999</v>
       </c>
       <c r="I10" s="1" t="s">
         <v>55</v>
@@ -9814,7 +9852,7 @@
         <v>55</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>999</v>
+        <v>1000</v>
       </c>
       <c r="L10" s="1">
         <v>0.5</v>
@@ -9823,36 +9861,39 @@
         <v>10</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>1000</v>
+        <v>1001</v>
       </c>
       <c r="O10" s="1" t="s">
-        <v>975</v>
-      </c>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
+        <v>976</v>
+      </c>
+      <c r="P10" s="1" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>1002</v>
+        <v>1003</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>1003</v>
+        <v>1004</v>
       </c>
       <c r="D11" s="1" t="s">
         <v>654</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>1004</v>
+        <v>1005</v>
       </c>
       <c r="F11" s="1" t="s">
         <v>680</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>1006</v>
+        <v>1007</v>
       </c>
       <c r="I11" s="1" t="s">
         <v>55</v>
@@ -9861,7 +9902,7 @@
         <v>55</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>1007</v>
+        <v>1008</v>
       </c>
       <c r="L11" s="1">
         <v>0.45</v>
@@ -9870,33 +9911,36 @@
         <v>20</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>1008</v>
+        <v>1009</v>
       </c>
       <c r="O11" s="1" t="s">
-        <v>967</v>
-      </c>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
+        <v>968</v>
+      </c>
+      <c r="P11" s="1" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>1009</v>
+        <v>1010</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>1010</v>
+        <v>1011</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>1011</v>
+        <v>1012</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>1012</v>
+        <v>1013</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>1013</v>
+        <v>1014</v>
       </c>
       <c r="F12" s="1" t="s">
         <v>696</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="H12" s="1" t="s">
         <v>721</v>
@@ -9908,7 +9952,7 @@
         <v>55</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>1015</v>
+        <v>1016</v>
       </c>
       <c r="L12" s="1">
         <v>0.5</v>
@@ -9917,36 +9961,39 @@
         <v>15</v>
       </c>
       <c r="N12" s="1" t="s">
-        <v>1016</v>
+        <v>1017</v>
       </c>
       <c r="O12" s="1" t="s">
-        <v>948</v>
-      </c>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
+        <v>949</v>
+      </c>
+      <c r="P12" s="1" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>1017</v>
+        <v>1018</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="D13" s="1" t="s">
         <v>745</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>1020</v>
+        <v>1021</v>
       </c>
       <c r="F13" s="1" t="s">
         <v>680</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>1021</v>
+        <v>1022</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>961</v>
+        <v>962</v>
       </c>
       <c r="I13" s="1" t="s">
         <v>55</v>
@@ -9955,7 +10002,7 @@
         <v>55</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>1022</v>
+        <v>1023</v>
       </c>
       <c r="L13" s="1">
         <v>0.45</v>
@@ -9964,33 +10011,36 @@
         <v>20</v>
       </c>
       <c r="N13" s="1" t="s">
-        <v>1023</v>
+        <v>1024</v>
       </c>
       <c r="O13" s="1" t="s">
-        <v>967</v>
-      </c>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
+        <v>968</v>
+      </c>
+      <c r="P13" s="1" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>1024</v>
+        <v>1025</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>1025</v>
+        <v>1026</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>1026</v>
+        <v>1027</v>
       </c>
       <c r="D14" s="1" t="s">
         <v>654</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>1027</v>
+        <v>1028</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>1028</v>
+        <v>1029</v>
       </c>
       <c r="H14" s="1" t="s">
         <v>696</v>
@@ -10002,7 +10052,7 @@
         <v>55</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>1029</v>
+        <v>1030</v>
       </c>
       <c r="L14" s="1">
         <v>0.5</v>
@@ -10011,36 +10061,39 @@
         <v>10</v>
       </c>
       <c r="N14" s="1" t="s">
-        <v>1030</v>
+        <v>1031</v>
       </c>
       <c r="O14" s="1" t="s">
-        <v>940</v>
-      </c>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
+        <v>941</v>
+      </c>
+      <c r="P14" s="1" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>1031</v>
+        <v>1032</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>1032</v>
+        <v>1033</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>1033</v>
+        <v>1034</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>1034</v>
+        <v>1035</v>
       </c>
       <c r="F15" s="1" t="s">
         <v>633</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>1035</v>
+        <v>1036</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>1036</v>
+        <v>1037</v>
       </c>
       <c r="I15" s="1" t="s">
         <v>55</v>
@@ -10049,7 +10102,7 @@
         <v>55</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>1037</v>
+        <v>1038</v>
       </c>
       <c r="L15" s="1">
         <v>0.45</v>
@@ -10058,33 +10111,36 @@
         <v>20</v>
       </c>
       <c r="N15" s="1" t="s">
-        <v>1038</v>
+        <v>1039</v>
       </c>
       <c r="O15" s="1" t="s">
-        <v>1039</v>
-      </c>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
+        <v>1040</v>
+      </c>
+      <c r="P15" s="1" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>1040</v>
+        <v>1041</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>1041</v>
+        <v>1042</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>1042</v>
+        <v>1043</v>
       </c>
       <c r="D16" s="1" t="s">
         <v>639</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>1043</v>
+        <v>1044</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>1044</v>
+        <v>1045</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
       <c r="H16" s="1" t="s">
         <v>680</v>
@@ -10096,7 +10152,7 @@
         <v>55</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>1046</v>
+        <v>1047</v>
       </c>
       <c r="L16" s="1">
         <v>0.4</v>
@@ -10105,33 +10161,36 @@
         <v>10</v>
       </c>
       <c r="N16" s="1" t="s">
-        <v>1047</v>
+        <v>1048</v>
       </c>
       <c r="O16" s="1" t="s">
-        <v>1048</v>
-      </c>
-    </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
+        <v>1049</v>
+      </c>
+      <c r="P16" s="1" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>1049</v>
+        <v>1050</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>1050</v>
+        <v>1051</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>1051</v>
+        <v>1052</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>1052</v>
+        <v>1053</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>1053</v>
+        <v>1054</v>
       </c>
       <c r="F17" s="1" t="s">
         <v>631</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>1054</v>
+        <v>1055</v>
       </c>
       <c r="H17" s="1" t="s">
         <v>735</v>
@@ -10143,7 +10202,7 @@
         <v>55</v>
       </c>
       <c r="K17" s="1" t="s">
-        <v>1055</v>
+        <v>1056</v>
       </c>
       <c r="L17" s="1">
         <v>0.45</v>
@@ -10152,36 +10211,39 @@
         <v>10</v>
       </c>
       <c r="N17" s="1" t="s">
-        <v>1000</v>
+        <v>1001</v>
       </c>
       <c r="O17" s="1" t="s">
-        <v>975</v>
-      </c>
-    </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
+        <v>976</v>
+      </c>
+      <c r="P17" s="1" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="18" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>1056</v>
+        <v>1057</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>1057</v>
+        <v>1058</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>1058</v>
+        <v>1059</v>
       </c>
       <c r="D18" s="1" t="s">
         <v>656</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>1059</v>
+        <v>1060</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>1060</v>
+        <v>1061</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>1062</v>
+        <v>1063</v>
       </c>
       <c r="I18" s="1" t="s">
         <v>55</v>
@@ -10204,31 +10266,34 @@
       <c r="O18" s="1" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P18" s="1" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="19" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>1063</v>
+        <v>1064</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>1064</v>
+        <v>1065</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>1065</v>
+        <v>1066</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>1066</v>
+        <v>1067</v>
       </c>
       <c r="F19" s="1" t="s">
         <v>721</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>1067</v>
+        <v>1068</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>1068</v>
+        <v>1069</v>
       </c>
       <c r="I19" s="1" t="s">
         <v>55</v>
@@ -10237,7 +10302,7 @@
         <v>55</v>
       </c>
       <c r="K19" s="1" t="s">
-        <v>1069</v>
+        <v>1070</v>
       </c>
       <c r="L19" s="1">
         <v>0.45</v>
@@ -10246,36 +10311,39 @@
         <v>10</v>
       </c>
       <c r="N19" s="1" t="s">
-        <v>1070</v>
+        <v>1071</v>
       </c>
       <c r="O19" s="1" t="s">
-        <v>967</v>
-      </c>
-    </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
+        <v>968</v>
+      </c>
+      <c r="P19" s="1" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="20" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>1071</v>
+        <v>1072</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>1072</v>
+        <v>1073</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>1073</v>
+        <v>1074</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>1074</v>
+        <v>1075</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="F20" s="1" t="s">
         <v>696</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>1076</v>
+        <v>1077</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>1077</v>
+        <v>1078</v>
       </c>
       <c r="I20" s="1" t="s">
         <v>55</v>
@@ -10284,7 +10352,7 @@
         <v>55</v>
       </c>
       <c r="K20" s="1" t="s">
-        <v>1078</v>
+        <v>1079</v>
       </c>
       <c r="L20" s="1">
         <v>0.5</v>
@@ -10293,33 +10361,36 @@
         <v>10</v>
       </c>
       <c r="N20" s="1" t="s">
-        <v>1079</v>
+        <v>1080</v>
       </c>
       <c r="O20" s="1" t="s">
-        <v>967</v>
-      </c>
-    </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
+        <v>968</v>
+      </c>
+      <c r="P20" s="1" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="21" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>1080</v>
+        <v>1081</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>1081</v>
+        <v>1082</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>1082</v>
+        <v>1083</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>1083</v>
+        <v>1084</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>1084</v>
+        <v>1085</v>
       </c>
       <c r="F21" s="1" t="s">
         <v>654</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>1085</v>
+        <v>1086</v>
       </c>
       <c r="H21" s="1" t="s">
         <v>696</v>
@@ -10331,7 +10402,7 @@
         <v>55</v>
       </c>
       <c r="K21" s="1" t="s">
-        <v>1086</v>
+        <v>1087</v>
       </c>
       <c r="L21" s="1">
         <v>0.35</v>
@@ -10340,36 +10411,39 @@
         <v>10</v>
       </c>
       <c r="N21" s="1" t="s">
-        <v>1087</v>
+        <v>1088</v>
       </c>
       <c r="O21" s="1" t="s">
-        <v>975</v>
-      </c>
-    </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
+        <v>976</v>
+      </c>
+      <c r="P21" s="1" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="22" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>1088</v>
+        <v>1089</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>1089</v>
+        <v>1090</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>1090</v>
+        <v>1091</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>1091</v>
+        <v>1092</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>1092</v>
+        <v>1093</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>1093</v>
+        <v>1094</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>1094</v>
+        <v>1095</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>1095</v>
+        <v>1096</v>
       </c>
       <c r="I22" s="1" t="s">
         <v>55</v>
@@ -10392,31 +10466,34 @@
       <c r="O22" s="1" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P22" s="1" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="23" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>1096</v>
+        <v>1097</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>1097</v>
+        <v>1098</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>1098</v>
+        <v>1099</v>
       </c>
       <c r="D23" s="1" t="s">
         <v>631</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>1099</v>
+        <v>1100</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>1100</v>
+        <v>1101</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>1101</v>
+        <v>1102</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>1102</v>
+        <v>1103</v>
       </c>
       <c r="I23" s="1" t="s">
         <v>55</v>
@@ -10425,7 +10502,7 @@
         <v>55</v>
       </c>
       <c r="K23" s="1" t="s">
-        <v>1103</v>
+        <v>1104</v>
       </c>
       <c r="L23" s="1">
         <v>0.5</v>
@@ -10434,33 +10511,36 @@
         <v>10</v>
       </c>
       <c r="N23" s="1" t="s">
-        <v>1104</v>
+        <v>1105</v>
       </c>
       <c r="O23" s="1" t="s">
-        <v>948</v>
-      </c>
-    </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
+        <v>949</v>
+      </c>
+      <c r="P23" s="1" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="24" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>1105</v>
+        <v>1106</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>1106</v>
+        <v>1107</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>1107</v>
+        <v>1108</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>1108</v>
+        <v>1109</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>1110</v>
+        <v>1111</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>1111</v>
+        <v>1112</v>
       </c>
       <c r="H24" s="1" t="s">
         <v>647</v>
@@ -10472,7 +10552,7 @@
         <v>55</v>
       </c>
       <c r="K24" s="1" t="s">
-        <v>1112</v>
+        <v>1113</v>
       </c>
       <c r="L24" s="1">
         <v>0.5</v>
@@ -10481,33 +10561,36 @@
         <v>10</v>
       </c>
       <c r="N24" s="1" t="s">
-        <v>1113</v>
+        <v>1114</v>
       </c>
       <c r="O24" s="1" t="s">
-        <v>1114</v>
-      </c>
-    </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
+        <v>1115</v>
+      </c>
+      <c r="P24" s="1" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="25" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
       <c r="D25" s="1" t="s">
         <v>656</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>1118</v>
+        <v>1119</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>1119</v>
+        <v>1120</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>1120</v>
+        <v>1121</v>
       </c>
       <c r="H25" s="1" t="s">
         <v>696</v>
@@ -10533,31 +10616,34 @@
       <c r="O25" s="1" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P25" s="1" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="26" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>1122</v>
+        <v>1123</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>1123</v>
+        <v>1124</v>
       </c>
       <c r="D26" s="1" t="s">
         <v>654</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>1124</v>
+        <v>1125</v>
       </c>
       <c r="F26" s="1" t="s">
         <v>742</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>1125</v>
+        <v>1126</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>1126</v>
+        <v>1127</v>
       </c>
       <c r="I26" s="1" t="s">
         <v>55</v>
@@ -10566,7 +10652,7 @@
         <v>55</v>
       </c>
       <c r="K26" s="1" t="s">
-        <v>1127</v>
+        <v>1128</v>
       </c>
       <c r="L26" s="1">
         <v>0.45</v>
@@ -10575,36 +10661,39 @@
         <v>10</v>
       </c>
       <c r="N26" s="1" t="s">
-        <v>1128</v>
+        <v>1129</v>
       </c>
       <c r="O26" s="1" t="s">
-        <v>992</v>
-      </c>
-    </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.25">
+        <v>993</v>
+      </c>
+      <c r="P26" s="1" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="27" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>1129</v>
+        <v>1130</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>1130</v>
+        <v>1131</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>1131</v>
+        <v>1132</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>1132</v>
+        <v>1133</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>1133</v>
+        <v>1134</v>
       </c>
       <c r="F27" s="1" t="s">
         <v>721</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>1134</v>
+        <v>1135</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>1135</v>
+        <v>1136</v>
       </c>
       <c r="I27" s="1" t="s">
         <v>55</v>
@@ -10613,7 +10702,7 @@
         <v>55</v>
       </c>
       <c r="K27" s="1" t="s">
-        <v>1136</v>
+        <v>1137</v>
       </c>
       <c r="L27" s="1">
         <v>0.3</v>
@@ -10622,33 +10711,36 @@
         <v>10</v>
       </c>
       <c r="N27" s="1" t="s">
-        <v>1137</v>
+        <v>1138</v>
       </c>
       <c r="O27" s="1" t="s">
-        <v>1138</v>
-      </c>
-    </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.25">
+        <v>1139</v>
+      </c>
+      <c r="P27" s="1" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="28" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>1139</v>
+        <v>1140</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>1140</v>
+        <v>1141</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>1141</v>
+        <v>1142</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>1142</v>
+        <v>1143</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>1143</v>
+        <v>1144</v>
       </c>
       <c r="F28" s="1" t="s">
         <v>680</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>1144</v>
+        <v>1145</v>
       </c>
       <c r="H28" s="1" t="s">
         <v>654</v>
@@ -10674,28 +10766,31 @@
       <c r="O28" s="1" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P28" s="1" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="29" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>1145</v>
+        <v>1146</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>1146</v>
+        <v>1147</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>1147</v>
+        <v>1148</v>
       </c>
       <c r="D29" s="1" t="s">
         <v>647</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>1148</v>
+        <v>1149</v>
       </c>
       <c r="F29" s="1" t="s">
         <v>696</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>1149</v>
+        <v>1150</v>
       </c>
       <c r="H29" s="1" t="s">
         <v>721</v>
@@ -10707,7 +10802,7 @@
         <v>55</v>
       </c>
       <c r="K29" s="1" t="s">
-        <v>1150</v>
+        <v>1151</v>
       </c>
       <c r="L29" s="1">
         <v>0.4</v>
@@ -10716,33 +10811,36 @@
         <v>10</v>
       </c>
       <c r="N29" s="1" t="s">
-        <v>1151</v>
+        <v>1152</v>
       </c>
       <c r="O29" s="1" t="s">
-        <v>975</v>
-      </c>
-    </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.25">
+        <v>976</v>
+      </c>
+      <c r="P29" s="1" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="30" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>1152</v>
+        <v>1153</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>1153</v>
+        <v>1154</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>1154</v>
+        <v>1155</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>1155</v>
+        <v>1156</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>1156</v>
+        <v>1157</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>1157</v>
+        <v>1158</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>1158</v>
+        <v>1159</v>
       </c>
       <c r="H30" s="1" t="s">
         <v>639</v>
@@ -10754,7 +10852,7 @@
         <v>55</v>
       </c>
       <c r="K30" s="1" t="s">
-        <v>1159</v>
+        <v>1160</v>
       </c>
       <c r="L30" s="1">
         <v>0.45</v>
@@ -10763,33 +10861,36 @@
         <v>10</v>
       </c>
       <c r="N30" s="1" t="s">
-        <v>1160</v>
+        <v>1161</v>
       </c>
       <c r="O30" s="1" t="s">
-        <v>948</v>
-      </c>
-    </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.25">
+        <v>949</v>
+      </c>
+      <c r="P30" s="1" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="31" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>1161</v>
+        <v>1162</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>1162</v>
+        <v>1163</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>1163</v>
+        <v>1164</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>1052</v>
+        <v>1053</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>1164</v>
+        <v>1165</v>
       </c>
       <c r="F31" s="1" t="s">
         <v>730</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>1165</v>
+        <v>1166</v>
       </c>
       <c r="H31" s="1" t="s">
         <v>647</v>
@@ -10815,28 +10916,31 @@
       <c r="O31" s="1" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P31" s="1" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="32" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>1166</v>
+        <v>1167</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>1167</v>
+        <v>1168</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>1168</v>
+        <v>1169</v>
       </c>
       <c r="D32" s="1" t="s">
         <v>656</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>1169</v>
+        <v>1170</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>1170</v>
+        <v>1171</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>1171</v>
+        <v>1172</v>
       </c>
       <c r="H32" s="1" t="s">
         <v>658</v>
@@ -10848,7 +10952,7 @@
         <v>55</v>
       </c>
       <c r="K32" s="1" t="s">
-        <v>1172</v>
+        <v>1173</v>
       </c>
       <c r="L32" s="1">
         <v>0.5</v>
@@ -10857,33 +10961,36 @@
         <v>10</v>
       </c>
       <c r="N32" s="1" t="s">
-        <v>1173</v>
+        <v>1174</v>
       </c>
       <c r="O32" s="1" t="s">
-        <v>1174</v>
-      </c>
-    </row>
-    <row r="33" spans="1:15" x14ac:dyDescent="0.25">
+        <v>1175</v>
+      </c>
+      <c r="P32" s="1" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="33" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>1175</v>
+        <v>1176</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>1176</v>
+        <v>1177</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>1178</v>
+        <v>1179</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>1179</v>
+        <v>1180</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>1180</v>
+        <v>1181</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>1181</v>
+        <v>1182</v>
       </c>
       <c r="H33" s="1" t="s">
         <v>665</v>
@@ -10895,7 +11002,7 @@
         <v>55</v>
       </c>
       <c r="K33" s="1" t="s">
-        <v>1182</v>
+        <v>1183</v>
       </c>
       <c r="L33" s="1">
         <v>0.4</v>
@@ -10904,36 +11011,39 @@
         <v>10</v>
       </c>
       <c r="N33" s="1" t="s">
-        <v>1183</v>
+        <v>1184</v>
       </c>
       <c r="O33" s="1" t="s">
-        <v>940</v>
-      </c>
-    </row>
-    <row r="34" spans="1:15" x14ac:dyDescent="0.25">
+        <v>941</v>
+      </c>
+      <c r="P33" s="1" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="34" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>1185</v>
+        <v>1186</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>1186</v>
+        <v>1187</v>
       </c>
       <c r="D34" s="1" t="s">
         <v>654</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>1187</v>
+        <v>1188</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>1188</v>
+        <v>1189</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>1189</v>
+        <v>1190</v>
       </c>
       <c r="H34" s="1" t="s">
-        <v>1170</v>
+        <v>1171</v>
       </c>
       <c r="I34" s="1" t="s">
         <v>55</v>
@@ -10942,7 +11052,7 @@
         <v>55</v>
       </c>
       <c r="K34" s="1" t="s">
-        <v>1190</v>
+        <v>1191</v>
       </c>
       <c r="L34" s="1">
         <v>0.5</v>
@@ -10951,36 +11061,39 @@
         <v>10</v>
       </c>
       <c r="N34" s="1" t="s">
-        <v>1191</v>
+        <v>1192</v>
       </c>
       <c r="O34" s="1" t="s">
-        <v>948</v>
-      </c>
-    </row>
-    <row r="35" spans="1:15" x14ac:dyDescent="0.25">
+        <v>949</v>
+      </c>
+      <c r="P34" s="1" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="35" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>1192</v>
+        <v>1193</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>1193</v>
+        <v>1194</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>1194</v>
+        <v>1195</v>
       </c>
       <c r="D35" s="1" t="s">
         <v>656</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>1195</v>
+        <v>1196</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>1196</v>
+        <v>1197</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>1197</v>
+        <v>1198</v>
       </c>
       <c r="H35" s="1" t="s">
-        <v>1198</v>
+        <v>1199</v>
       </c>
       <c r="I35" s="1" t="s">
         <v>55</v>
@@ -11003,31 +11116,34 @@
       <c r="O35" s="1" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="36" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P35" s="1" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="36" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>1199</v>
+        <v>1200</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>1200</v>
+        <v>1201</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="D36" s="1" t="s">
         <v>639</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>1201</v>
+        <v>1202</v>
       </c>
       <c r="F36" s="1" t="s">
         <v>680</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>1202</v>
+        <v>1203</v>
       </c>
       <c r="H36" s="1" t="s">
-        <v>1203</v>
+        <v>1204</v>
       </c>
       <c r="I36" s="1" t="s">
         <v>55</v>
@@ -11050,28 +11166,31 @@
       <c r="O36" s="1" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="37" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P36" s="1" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="37" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>1204</v>
+        <v>1205</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>1205</v>
+        <v>1206</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>1206</v>
+        <v>1207</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>1091</v>
+        <v>1092</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>1207</v>
+        <v>1208</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>934</v>
+        <v>935</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>1208</v>
+        <v>1209</v>
       </c>
       <c r="H37" s="1" t="s">
         <v>745</v>
@@ -11097,28 +11216,31 @@
       <c r="O37" s="1" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="38" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P37" s="1" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="38" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>1209</v>
+        <v>1210</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>1210</v>
+        <v>1211</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>1211</v>
+        <v>1212</v>
       </c>
       <c r="D38" s="1" t="s">
         <v>673</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>1212</v>
+        <v>1213</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>1213</v>
+        <v>1214</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>1214</v>
+        <v>1215</v>
       </c>
       <c r="H38" s="1" t="s">
         <v>658</v>
@@ -11130,7 +11252,7 @@
         <v>55</v>
       </c>
       <c r="K38" s="1" t="s">
-        <v>1215</v>
+        <v>1216</v>
       </c>
       <c r="L38" s="1">
         <v>0.45</v>
@@ -11139,33 +11261,36 @@
         <v>10</v>
       </c>
       <c r="N38" s="1" t="s">
-        <v>1216</v>
+        <v>1217</v>
       </c>
       <c r="O38" s="1" t="s">
-        <v>1114</v>
-      </c>
-    </row>
-    <row r="39" spans="1:15" x14ac:dyDescent="0.25">
+        <v>1115</v>
+      </c>
+      <c r="P38" s="1" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="39" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
-        <v>1217</v>
+        <v>1218</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>1218</v>
+        <v>1219</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>1219</v>
+        <v>1220</v>
       </c>
       <c r="D39" s="1" t="s">
         <v>633</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>1220</v>
+        <v>1221</v>
       </c>
       <c r="F39" s="1" t="s">
         <v>656</v>
       </c>
       <c r="G39" s="1" t="s">
-        <v>1221</v>
+        <v>1222</v>
       </c>
       <c r="H39" s="1" t="s">
         <v>680</v>
@@ -11177,7 +11302,7 @@
         <v>55</v>
       </c>
       <c r="K39" s="1" t="s">
-        <v>1222</v>
+        <v>1223</v>
       </c>
       <c r="L39" s="1">
         <v>0.4</v>
@@ -11186,36 +11311,39 @@
         <v>10</v>
       </c>
       <c r="N39" s="1" t="s">
-        <v>1223</v>
+        <v>1224</v>
       </c>
       <c r="O39" s="1" t="s">
-        <v>1138</v>
-      </c>
-    </row>
-    <row r="40" spans="1:15" x14ac:dyDescent="0.25">
+        <v>1139</v>
+      </c>
+      <c r="P39" s="1" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="40" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
-        <v>1224</v>
+        <v>1225</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>1225</v>
+        <v>1226</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>1226</v>
+        <v>1227</v>
       </c>
       <c r="D40" s="1" t="s">
         <v>654</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>1227</v>
+        <v>1228</v>
       </c>
       <c r="F40" s="1" t="s">
         <v>656</v>
       </c>
       <c r="G40" s="1" t="s">
-        <v>1228</v>
+        <v>1229</v>
       </c>
       <c r="H40" s="1" t="s">
-        <v>1229</v>
+        <v>1230</v>
       </c>
       <c r="I40" s="1" t="s">
         <v>55</v>
@@ -11224,7 +11352,7 @@
         <v>55</v>
       </c>
       <c r="K40" s="1" t="s">
-        <v>1230</v>
+        <v>1231</v>
       </c>
       <c r="L40" s="1">
         <v>0.5</v>
@@ -11233,18 +11361,21 @@
         <v>10</v>
       </c>
       <c r="N40" s="1" t="s">
-        <v>1231</v>
+        <v>1232</v>
       </c>
       <c r="O40" s="1" t="s">
-        <v>1174</v>
-      </c>
-    </row>
-    <row r="41" spans="1:15" x14ac:dyDescent="0.25">
+        <v>1175</v>
+      </c>
+      <c r="P40" s="1" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="41" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
-        <v>1232</v>
+        <v>1233</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>1233</v>
+        <v>1234</v>
       </c>
       <c r="C41" s="1" t="s">
         <v>637</v>
@@ -11253,16 +11384,16 @@
         <v>639</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>1234</v>
+        <v>1235</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>1060</v>
+        <v>1061</v>
       </c>
       <c r="G41" s="1" t="s">
-        <v>1235</v>
+        <v>1236</v>
       </c>
       <c r="H41" s="1" t="s">
-        <v>1236</v>
+        <v>1237</v>
       </c>
       <c r="I41" s="1" t="s">
         <v>55</v>
@@ -11285,28 +11416,31 @@
       <c r="O41" s="1" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="42" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P41" s="1" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="42" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
-        <v>1237</v>
+        <v>1238</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>1238</v>
+        <v>1239</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>1239</v>
+        <v>1240</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>1240</v>
+        <v>1241</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>1241</v>
+        <v>1242</v>
       </c>
       <c r="F42" s="1" t="s">
         <v>631</v>
       </c>
       <c r="G42" s="1" t="s">
-        <v>1242</v>
+        <v>1243</v>
       </c>
       <c r="H42" s="1" t="s">
         <v>745</v>
@@ -11318,7 +11452,7 @@
         <v>55</v>
       </c>
       <c r="K42" s="1" t="s">
-        <v>1243</v>
+        <v>1244</v>
       </c>
       <c r="L42" s="1">
         <v>0.35</v>
@@ -11327,33 +11461,36 @@
         <v>10</v>
       </c>
       <c r="N42" s="1" t="s">
-        <v>1151</v>
+        <v>1152</v>
       </c>
       <c r="O42" s="1" t="s">
-        <v>1244</v>
-      </c>
-    </row>
-    <row r="43" spans="1:15" x14ac:dyDescent="0.25">
+        <v>1245</v>
+      </c>
+      <c r="P42" s="1" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="43" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
-        <v>1245</v>
+        <v>1246</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>1246</v>
+        <v>1247</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>1247</v>
+        <v>1248</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>1248</v>
+        <v>1249</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>1249</v>
+        <v>1250</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>1250</v>
+        <v>1251</v>
       </c>
       <c r="G43" s="1" t="s">
-        <v>1251</v>
+        <v>1252</v>
       </c>
       <c r="H43" s="1" t="s">
         <v>710</v>
@@ -11365,7 +11502,7 @@
         <v>55</v>
       </c>
       <c r="K43" s="1" t="s">
-        <v>1252</v>
+        <v>1253</v>
       </c>
       <c r="L43" s="1">
         <v>0.5</v>
@@ -11374,33 +11511,36 @@
         <v>10</v>
       </c>
       <c r="N43" s="1" t="s">
-        <v>1253</v>
+        <v>1254</v>
       </c>
       <c r="O43" s="1" t="s">
-        <v>1254</v>
-      </c>
-    </row>
-    <row r="44" spans="1:15" x14ac:dyDescent="0.25">
+        <v>1255</v>
+      </c>
+      <c r="P43" s="1" t="s">
+        <v>1256</v>
+      </c>
+    </row>
+    <row r="44" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
-        <v>1255</v>
+        <v>1257</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>1256</v>
+        <v>1258</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>1257</v>
+        <v>1259</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>1258</v>
+        <v>1260</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>1259</v>
+        <v>1261</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>1260</v>
+        <v>1262</v>
       </c>
       <c r="G44" s="1" t="s">
-        <v>1261</v>
+        <v>1263</v>
       </c>
       <c r="H44" s="1" t="s">
         <v>710</v>
@@ -11412,7 +11552,7 @@
         <v>55</v>
       </c>
       <c r="K44" s="1" t="s">
-        <v>1262</v>
+        <v>1264</v>
       </c>
       <c r="L44" s="1">
         <v>0.4</v>
@@ -11421,36 +11561,39 @@
         <v>10</v>
       </c>
       <c r="N44" s="1" t="s">
-        <v>1263</v>
+        <v>1265</v>
       </c>
       <c r="O44" s="1" t="s">
-        <v>1264</v>
-      </c>
-    </row>
-    <row r="45" spans="1:15" x14ac:dyDescent="0.25">
+        <v>1266</v>
+      </c>
+      <c r="P44" s="1" t="s">
+        <v>1256</v>
+      </c>
+    </row>
+    <row r="45" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
-        <v>1265</v>
+        <v>1267</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>1266</v>
+        <v>1268</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>1267</v>
+        <v>1269</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>1268</v>
+        <v>1270</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>1107</v>
+        <v>1108</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>1250</v>
+        <v>1251</v>
       </c>
       <c r="G45" s="1" t="s">
-        <v>1269</v>
+        <v>1271</v>
       </c>
       <c r="H45" s="1" t="s">
-        <v>1270</v>
+        <v>1272</v>
       </c>
       <c r="I45" s="1" t="s">
         <v>55</v>
@@ -11459,7 +11602,7 @@
         <v>55</v>
       </c>
       <c r="K45" s="1" t="s">
-        <v>1271</v>
+        <v>1273</v>
       </c>
       <c r="L45" s="1">
         <v>0.5</v>
@@ -11468,36 +11611,39 @@
         <v>10</v>
       </c>
       <c r="N45" s="1" t="s">
-        <v>1272</v>
+        <v>1274</v>
       </c>
       <c r="O45" s="1" t="s">
-        <v>1273</v>
-      </c>
-    </row>
-    <row r="46" spans="1:15" x14ac:dyDescent="0.25">
+        <v>1275</v>
+      </c>
+      <c r="P45" s="1" t="s">
+        <v>1256</v>
+      </c>
+    </row>
+    <row r="46" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
-        <v>1274</v>
+        <v>1276</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>1275</v>
+        <v>1277</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>1276</v>
+        <v>1278</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>1277</v>
+        <v>1279</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>1278</v>
+        <v>1280</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>1279</v>
+        <v>1281</v>
       </c>
       <c r="G46" s="1" t="s">
-        <v>1280</v>
+        <v>1282</v>
       </c>
       <c r="H46" s="1" t="s">
-        <v>1281</v>
+        <v>1283</v>
       </c>
       <c r="I46" s="1" t="s">
         <v>55</v>
@@ -11520,31 +11666,34 @@
       <c r="O46" s="1" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="47" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P46" s="1" t="s">
+        <v>1256</v>
+      </c>
+    </row>
+    <row r="47" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
-        <v>1282</v>
+        <v>1284</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>1283</v>
+        <v>1285</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>1284</v>
+        <v>1286</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>1285</v>
+        <v>1287</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>1286</v>
+        <v>1288</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>1250</v>
+        <v>1251</v>
       </c>
       <c r="G47" s="1" t="s">
-        <v>1287</v>
+        <v>1289</v>
       </c>
       <c r="H47" s="1" t="s">
-        <v>1288</v>
+        <v>1290</v>
       </c>
       <c r="I47" s="1" t="s">
         <v>55</v>
@@ -11567,31 +11716,34 @@
       <c r="O47" s="1" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="48" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P47" s="1" t="s">
+        <v>1256</v>
+      </c>
+    </row>
+    <row r="48" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
-        <v>1289</v>
+        <v>1291</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>1290</v>
+        <v>1292</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>1291</v>
+        <v>1293</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>1292</v>
+        <v>1294</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>1293</v>
+        <v>1295</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>1260</v>
+        <v>1262</v>
       </c>
       <c r="G48" s="1" t="s">
-        <v>1294</v>
+        <v>1296</v>
       </c>
       <c r="H48" s="1" t="s">
-        <v>1250</v>
+        <v>1251</v>
       </c>
       <c r="I48" s="1" t="s">
         <v>55</v>
@@ -11600,7 +11752,7 @@
         <v>55</v>
       </c>
       <c r="K48" s="1" t="s">
-        <v>1295</v>
+        <v>1297</v>
       </c>
       <c r="L48" s="1">
         <v>0.45</v>
@@ -11609,36 +11761,39 @@
         <v>10</v>
       </c>
       <c r="N48" s="1" t="s">
-        <v>1296</v>
+        <v>1298</v>
       </c>
       <c r="O48" s="1" t="s">
-        <v>1297</v>
-      </c>
-    </row>
-    <row r="49" spans="1:15" x14ac:dyDescent="0.25">
+        <v>1299</v>
+      </c>
+      <c r="P48" s="1" t="s">
+        <v>1256</v>
+      </c>
+    </row>
+    <row r="49" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
-        <v>1298</v>
+        <v>1300</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>1299</v>
+        <v>1301</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>1300</v>
+        <v>1302</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>1301</v>
+        <v>1303</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>1302</v>
+        <v>1304</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>1108</v>
+        <v>1109</v>
       </c>
       <c r="G49" s="1" t="s">
-        <v>1303</v>
+        <v>1305</v>
       </c>
       <c r="H49" s="1" t="s">
-        <v>1304</v>
+        <v>1306</v>
       </c>
       <c r="I49" s="1" t="s">
         <v>55</v>
@@ -11661,31 +11816,34 @@
       <c r="O49" s="1" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="50" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P49" s="1" t="s">
+        <v>1256</v>
+      </c>
+    </row>
+    <row r="50" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
-        <v>1305</v>
+        <v>1307</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>1306</v>
+        <v>1308</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>1307</v>
+        <v>1309</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>1308</v>
+        <v>1310</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>1309</v>
+        <v>1311</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>1310</v>
+        <v>1312</v>
       </c>
       <c r="G50" s="1" t="s">
-        <v>1311</v>
+        <v>1313</v>
       </c>
       <c r="H50" s="1" t="s">
-        <v>1312</v>
+        <v>1314</v>
       </c>
       <c r="I50" s="1" t="s">
         <v>55</v>
@@ -11694,7 +11852,7 @@
         <v>55</v>
       </c>
       <c r="K50" s="1" t="s">
-        <v>1313</v>
+        <v>1315</v>
       </c>
       <c r="L50" s="1">
         <v>0.35</v>
@@ -11703,36 +11861,39 @@
         <v>10</v>
       </c>
       <c r="N50" s="1" t="s">
-        <v>1314</v>
+        <v>1316</v>
       </c>
       <c r="O50" s="1" t="s">
-        <v>1315</v>
-      </c>
-    </row>
-    <row r="51" spans="1:15" x14ac:dyDescent="0.25">
+        <v>1317</v>
+      </c>
+      <c r="P50" s="1" t="s">
+        <v>1256</v>
+      </c>
+    </row>
+    <row r="51" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
-        <v>1316</v>
+        <v>1318</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>1317</v>
+        <v>1319</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>1318</v>
+        <v>1320</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>1258</v>
+        <v>1260</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>1319</v>
+        <v>1321</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>1320</v>
+        <v>1322</v>
       </c>
       <c r="G51" s="1" t="s">
-        <v>1321</v>
+        <v>1323</v>
       </c>
       <c r="H51" s="1" t="s">
-        <v>1322</v>
+        <v>1324</v>
       </c>
       <c r="I51" s="1" t="s">
         <v>55</v>
@@ -11755,31 +11916,34 @@
       <c r="O51" s="1" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="52" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P51" s="1" t="s">
+        <v>1256</v>
+      </c>
+    </row>
+    <row r="52" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
-        <v>1323</v>
+        <v>1325</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>1324</v>
+        <v>1326</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>1325</v>
+        <v>1327</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>1326</v>
+        <v>1328</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>1327</v>
+        <v>1329</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>1328</v>
+        <v>1330</v>
       </c>
       <c r="G52" s="1" t="s">
-        <v>1329</v>
+        <v>1331</v>
       </c>
       <c r="H52" s="1" t="s">
-        <v>1250</v>
+        <v>1251</v>
       </c>
       <c r="I52" s="1" t="s">
         <v>55</v>
@@ -11802,78 +11966,84 @@
       <c r="O52" s="1" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="53" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P52" s="1" t="s">
+        <v>1256</v>
+      </c>
+    </row>
+    <row r="53" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
+        <v>1332</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>1333</v>
+      </c>
+      <c r="C53" s="1" t="s">
+        <v>1334</v>
+      </c>
+      <c r="D53" s="1" t="s">
+        <v>1335</v>
+      </c>
+      <c r="E53" s="1" t="s">
+        <v>1336</v>
+      </c>
+      <c r="F53" s="1" t="s">
+        <v>1337</v>
+      </c>
+      <c r="G53" s="1" t="s">
+        <v>1338</v>
+      </c>
+      <c r="H53" s="1" t="s">
+        <v>1339</v>
+      </c>
+      <c r="I53" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="J53" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="K53" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="L53" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="M53" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="N53" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="O53" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="P53" s="1" t="s">
+        <v>1340</v>
+      </c>
+    </row>
+    <row r="54" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A54" s="1" t="s">
+        <v>1341</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>1342</v>
+      </c>
+      <c r="C54" s="1" t="s">
+        <v>1343</v>
+      </c>
+      <c r="D54" s="1" t="s">
         <v>1330</v>
       </c>
-      <c r="B53" s="1" t="s">
-        <v>1331</v>
-      </c>
-      <c r="C53" s="1" t="s">
-        <v>1332</v>
-      </c>
-      <c r="D53" s="1" t="s">
-        <v>1333</v>
-      </c>
-      <c r="E53" s="1" t="s">
-        <v>1334</v>
-      </c>
-      <c r="F53" s="1" t="s">
-        <v>1335</v>
-      </c>
-      <c r="G53" s="1" t="s">
-        <v>1336</v>
-      </c>
-      <c r="H53" s="1" t="s">
-        <v>1337</v>
-      </c>
-      <c r="I53" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="J53" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="K53" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="L53" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="M53" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="N53" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="O53" s="1" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="54" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A54" s="1" t="s">
-        <v>1338</v>
-      </c>
-      <c r="B54" s="1" t="s">
-        <v>1339</v>
-      </c>
-      <c r="C54" s="1" t="s">
-        <v>1340</v>
-      </c>
-      <c r="D54" s="1" t="s">
-        <v>1328</v>
-      </c>
       <c r="E54" s="1" t="s">
-        <v>1341</v>
+        <v>1344</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>1342</v>
+        <v>1345</v>
       </c>
       <c r="G54" s="1" t="s">
-        <v>1343</v>
+        <v>1346</v>
       </c>
       <c r="H54" s="1" t="s">
-        <v>1344</v>
+        <v>1347</v>
       </c>
       <c r="I54" s="1" t="s">
         <v>55</v>
@@ -11882,7 +12052,7 @@
         <v>55</v>
       </c>
       <c r="K54" s="1" t="s">
-        <v>1345</v>
+        <v>1348</v>
       </c>
       <c r="L54" s="1">
         <v>0.4</v>
@@ -11891,36 +12061,39 @@
         <v>10</v>
       </c>
       <c r="N54" s="1" t="s">
-        <v>1346</v>
+        <v>1349</v>
       </c>
       <c r="O54" s="1" t="s">
-        <v>1347</v>
-      </c>
-    </row>
-    <row r="55" spans="1:15" x14ac:dyDescent="0.25">
+        <v>1350</v>
+      </c>
+      <c r="P54" s="1" t="s">
+        <v>1256</v>
+      </c>
+    </row>
+    <row r="55" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
-        <v>1348</v>
+        <v>1351</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>1349</v>
+        <v>1352</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>1350</v>
+        <v>1353</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>1268</v>
+        <v>1270</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>1351</v>
+        <v>1354</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>1352</v>
+        <v>1355</v>
       </c>
       <c r="G55" s="1" t="s">
-        <v>1353</v>
+        <v>1356</v>
       </c>
       <c r="H55" s="1" t="s">
-        <v>1354</v>
+        <v>1357</v>
       </c>
       <c r="I55" s="1" t="s">
         <v>55</v>
@@ -11943,28 +12116,31 @@
       <c r="O55" s="1" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="56" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P55" s="1" t="s">
+        <v>1256</v>
+      </c>
+    </row>
+    <row r="56" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
-        <v>1355</v>
+        <v>1358</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>1356</v>
+        <v>1359</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>1357</v>
+        <v>1360</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>1358</v>
+        <v>1361</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>1359</v>
+        <v>1362</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>1250</v>
+        <v>1251</v>
       </c>
       <c r="G56" s="1" t="s">
-        <v>1360</v>
+        <v>1363</v>
       </c>
       <c r="H56" s="1" t="s">
         <v>710</v>
@@ -11990,31 +12166,34 @@
       <c r="O56" s="1" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="57" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P56" s="1" t="s">
+        <v>1256</v>
+      </c>
+    </row>
+    <row r="57" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
-        <v>1361</v>
+        <v>1364</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>1362</v>
+        <v>1365</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>1363</v>
+        <v>1366</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>1364</v>
+        <v>1367</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>1365</v>
+        <v>1368</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>1366</v>
+        <v>1369</v>
       </c>
       <c r="G57" s="1" t="s">
-        <v>1367</v>
+        <v>1370</v>
       </c>
       <c r="H57" s="1" t="s">
-        <v>1250</v>
+        <v>1251</v>
       </c>
       <c r="I57" s="1" t="s">
         <v>55</v>
@@ -12037,31 +12216,34 @@
       <c r="O57" s="1" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="58" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P57" s="1" t="s">
+        <v>1256</v>
+      </c>
+    </row>
+    <row r="58" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
-        <v>1368</v>
+        <v>1371</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>1369</v>
+        <v>1372</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>1370</v>
+        <v>1373</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>1371</v>
+        <v>1374</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>1372</v>
+        <v>1375</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>1373</v>
+        <v>1376</v>
       </c>
       <c r="G58" s="1" t="s">
-        <v>1374</v>
+        <v>1377</v>
       </c>
       <c r="H58" s="1" t="s">
-        <v>1375</v>
+        <v>1378</v>
       </c>
       <c r="I58" s="1" t="s">
         <v>55</v>
@@ -12084,125 +12266,134 @@
       <c r="O58" s="1" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="59" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P58" s="1" t="s">
+        <v>1379</v>
+      </c>
+    </row>
+    <row r="59" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
-        <v>1376</v>
+        <v>1380</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>1377</v>
+        <v>1381</v>
       </c>
       <c r="C59" s="1" t="s">
+        <v>1382</v>
+      </c>
+      <c r="D59" s="1" t="s">
+        <v>1383</v>
+      </c>
+      <c r="E59" s="1" t="s">
+        <v>1384</v>
+      </c>
+      <c r="F59" s="1" t="s">
+        <v>1385</v>
+      </c>
+      <c r="G59" s="1" t="s">
+        <v>1386</v>
+      </c>
+      <c r="H59" s="1" t="s">
         <v>1378</v>
       </c>
-      <c r="D59" s="1" t="s">
+      <c r="I59" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="J59" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="K59" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="L59" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="M59" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="N59" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="O59" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="P59" s="1" t="s">
         <v>1379</v>
       </c>
-      <c r="E59" s="1" t="s">
-        <v>1380</v>
-      </c>
-      <c r="F59" s="1" t="s">
-        <v>1381</v>
-      </c>
-      <c r="G59" s="1" t="s">
-        <v>1382</v>
-      </c>
-      <c r="H59" s="1" t="s">
-        <v>1375</v>
-      </c>
-      <c r="I59" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="J59" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="K59" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="L59" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="M59" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="N59" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="O59" s="1" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="60" spans="1:15" x14ac:dyDescent="0.25">
+    </row>
+    <row r="60" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
+        <v>1387</v>
+      </c>
+      <c r="B60" s="1" t="s">
+        <v>1388</v>
+      </c>
+      <c r="C60" s="1" t="s">
+        <v>1389</v>
+      </c>
+      <c r="D60" s="1" t="s">
+        <v>1390</v>
+      </c>
+      <c r="E60" s="1" t="s">
+        <v>1391</v>
+      </c>
+      <c r="F60" s="1" t="s">
+        <v>1392</v>
+      </c>
+      <c r="G60" s="1" t="s">
+        <v>1393</v>
+      </c>
+      <c r="H60" s="1" t="s">
+        <v>1394</v>
+      </c>
+      <c r="I60" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="J60" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="K60" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="L60" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="M60" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="N60" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="O60" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="P60" s="1" t="s">
+        <v>1379</v>
+      </c>
+    </row>
+    <row r="61" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A61" s="1" t="s">
+        <v>1395</v>
+      </c>
+      <c r="B61" s="1" t="s">
+        <v>1396</v>
+      </c>
+      <c r="C61" s="1" t="s">
+        <v>1397</v>
+      </c>
+      <c r="D61" s="1" t="s">
         <v>1383</v>
       </c>
-      <c r="B60" s="1" t="s">
-        <v>1384</v>
-      </c>
-      <c r="C60" s="1" t="s">
-        <v>1385</v>
-      </c>
-      <c r="D60" s="1" t="s">
-        <v>1386</v>
-      </c>
-      <c r="E60" s="1" t="s">
-        <v>1387</v>
-      </c>
-      <c r="F60" s="1" t="s">
-        <v>1388</v>
-      </c>
-      <c r="G60" s="1" t="s">
-        <v>1389</v>
-      </c>
-      <c r="H60" s="1" t="s">
-        <v>1390</v>
-      </c>
-      <c r="I60" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="J60" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="K60" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="L60" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="M60" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="N60" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="O60" s="1" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="61" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A61" s="1" t="s">
-        <v>1391</v>
-      </c>
-      <c r="B61" s="1" t="s">
-        <v>1392</v>
-      </c>
-      <c r="C61" s="1" t="s">
-        <v>1393</v>
-      </c>
-      <c r="D61" s="1" t="s">
-        <v>1379</v>
-      </c>
       <c r="E61" s="1" t="s">
-        <v>1394</v>
+        <v>1398</v>
       </c>
       <c r="F61" s="1" t="s">
         <v>749</v>
       </c>
       <c r="G61" s="1" t="s">
-        <v>1395</v>
+        <v>1399</v>
       </c>
       <c r="H61" s="1" t="s">
-        <v>1250</v>
+        <v>1251</v>
       </c>
       <c r="I61" s="1" t="s">
         <v>55</v>
@@ -12225,31 +12416,34 @@
       <c r="O61" s="1" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="62" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P61" s="1" t="s">
+        <v>1379</v>
+      </c>
+    </row>
+    <row r="62" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
-        <v>1396</v>
+        <v>1400</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>1397</v>
+        <v>1401</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>1398</v>
+        <v>1402</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>1399</v>
+        <v>1403</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>1400</v>
+        <v>1404</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>1401</v>
+        <v>1405</v>
       </c>
       <c r="G62" s="1" t="s">
-        <v>1402</v>
+        <v>1406</v>
       </c>
       <c r="H62" s="1" t="s">
-        <v>1403</v>
+        <v>1407</v>
       </c>
       <c r="I62" s="1" t="s">
         <v>55</v>
@@ -12272,31 +12466,34 @@
       <c r="O62" s="1" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="63" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P62" s="1" t="s">
+        <v>1379</v>
+      </c>
+    </row>
+    <row r="63" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
-        <v>1404</v>
+        <v>1408</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>1405</v>
+        <v>1409</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>1406</v>
+        <v>1410</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>1407</v>
+        <v>1411</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>1408</v>
+        <v>1412</v>
       </c>
       <c r="F63" s="1" t="s">
-        <v>1352</v>
+        <v>1355</v>
       </c>
       <c r="G63" s="1" t="s">
-        <v>1409</v>
+        <v>1413</v>
       </c>
       <c r="H63" s="1" t="s">
-        <v>1410</v>
+        <v>1414</v>
       </c>
       <c r="I63" s="1" t="s">
         <v>55</v>
@@ -12319,31 +12516,34 @@
       <c r="O63" s="1" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="64" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P63" s="1" t="s">
+        <v>1379</v>
+      </c>
+    </row>
+    <row r="64" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
-        <v>1411</v>
+        <v>1415</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>1412</v>
+        <v>1416</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>1413</v>
+        <v>1417</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>1320</v>
+        <v>1322</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>1414</v>
+        <v>1418</v>
       </c>
       <c r="F64" s="1" t="s">
-        <v>1415</v>
+        <v>1419</v>
       </c>
       <c r="G64" s="1" t="s">
-        <v>1416</v>
+        <v>1420</v>
       </c>
       <c r="H64" s="1" t="s">
-        <v>1417</v>
+        <v>1421</v>
       </c>
       <c r="I64" s="1" t="s">
         <v>55</v>
@@ -12366,31 +12566,34 @@
       <c r="O64" s="1" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="65" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P64" s="1" t="s">
+        <v>1379</v>
+      </c>
+    </row>
+    <row r="65" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
-        <v>1418</v>
+        <v>1422</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>1419</v>
+        <v>1423</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>1420</v>
+        <v>1424</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>1421</v>
+        <v>1425</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>1422</v>
+        <v>1426</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>1373</v>
+        <v>1376</v>
       </c>
       <c r="G65" s="1" t="s">
-        <v>1423</v>
+        <v>1427</v>
       </c>
       <c r="H65" s="1" t="s">
-        <v>1424</v>
+        <v>1428</v>
       </c>
       <c r="I65" s="1" t="s">
         <v>55</v>
@@ -12413,31 +12616,34 @@
       <c r="O65" s="1" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="66" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P65" s="1" t="s">
+        <v>1379</v>
+      </c>
+    </row>
+    <row r="66" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
-        <v>1425</v>
+        <v>1429</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>1426</v>
+        <v>1430</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>1427</v>
+        <v>1431</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>1428</v>
+        <v>1432</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>1429</v>
+        <v>1433</v>
       </c>
       <c r="F66" s="1" t="s">
-        <v>1352</v>
+        <v>1355</v>
       </c>
       <c r="G66" s="1" t="s">
-        <v>1430</v>
+        <v>1434</v>
       </c>
       <c r="H66" s="1" t="s">
-        <v>1310</v>
+        <v>1312</v>
       </c>
       <c r="I66" s="1" t="s">
         <v>55</v>
@@ -12460,31 +12666,34 @@
       <c r="O66" s="1" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="67" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P66" s="1" t="s">
+        <v>1379</v>
+      </c>
+    </row>
+    <row r="67" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
-        <v>1431</v>
+        <v>1435</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>1432</v>
+        <v>1436</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>1433</v>
+        <v>1437</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>1434</v>
+        <v>1438</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>1435</v>
+        <v>1439</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>1074</v>
+        <v>1075</v>
       </c>
       <c r="G67" s="1" t="s">
-        <v>1436</v>
+        <v>1440</v>
       </c>
       <c r="H67" s="1" t="s">
-        <v>1347</v>
+        <v>1350</v>
       </c>
       <c r="I67" s="1" t="s">
         <v>55</v>
@@ -12506,6 +12715,9 @@
       </c>
       <c r="O67" s="1" t="s">
         <v>55</v>
+      </c>
+      <c r="P67" s="1" t="s">
+        <v>1379</v>
       </c>
     </row>
   </sheetData>
@@ -12536,7 +12748,7 @@
   <sheetData>
     <row r="1" spans="1:18" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>1437</v>
+        <v>1441</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
@@ -12564,7 +12776,7 @@
         <v>539</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>1438</v>
+        <v>1442</v>
       </c>
       <c r="D2" s="5" t="s">
         <v>298</v>
@@ -12579,13 +12791,13 @@
         <v>541</v>
       </c>
       <c r="H2" s="5" t="s">
-        <v>1439</v>
+        <v>1443</v>
       </c>
       <c r="I2" s="5" t="s">
-        <v>1440</v>
+        <v>1444</v>
       </c>
       <c r="J2" s="5" t="s">
-        <v>1441</v>
+        <v>1445</v>
       </c>
       <c r="K2" s="5" t="s">
         <v>620</v>
@@ -12614,16 +12826,16 @@
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>1442</v>
+        <v>1446</v>
       </c>
       <c r="B3" s="1">
         <v>1</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>1443</v>
+        <v>1447</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>1444</v>
+        <v>1448</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>55</v>
@@ -12670,19 +12882,19 @@
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>1445</v>
+        <v>1449</v>
       </c>
       <c r="B4" s="1">
         <v>1</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>1443</v>
+        <v>1447</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>1446</v>
+        <v>1450</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>1447</v>
+        <v>1451</v>
       </c>
       <c r="F4" s="1">
         <v>1893</v>
@@ -12726,19 +12938,19 @@
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>1448</v>
+        <v>1452</v>
       </c>
       <c r="B5" s="1">
         <v>1</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>1449</v>
+        <v>1453</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>1450</v>
+        <v>1454</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>1451</v>
+        <v>1455</v>
       </c>
       <c r="F5" s="1">
         <v>1894</v>
@@ -12782,16 +12994,16 @@
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>1452</v>
+        <v>1456</v>
       </c>
       <c r="B6" s="1">
         <v>1</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>1449</v>
+        <v>1453</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>1453</v>
+        <v>1457</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>55</v>
@@ -12838,16 +13050,16 @@
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>1454</v>
+        <v>1458</v>
       </c>
       <c r="B7" s="1">
         <v>1</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>1449</v>
+        <v>1453</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>1455</v>
+        <v>1459</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>55</v>
@@ -12894,19 +13106,19 @@
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>1456</v>
+        <v>1460</v>
       </c>
       <c r="B8" s="1">
         <v>1</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>1457</v>
+        <v>1461</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>1458</v>
+        <v>1462</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>1459</v>
+        <v>1463</v>
       </c>
       <c r="F8" s="1">
         <v>1912</v>
@@ -12924,22 +13136,22 @@
         <v>55</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>1460</v>
+        <v>1464</v>
       </c>
       <c r="L8" s="1" t="s">
-        <v>1461</v>
+        <v>1465</v>
       </c>
       <c r="M8" s="1" t="s">
-        <v>1462</v>
+        <v>1466</v>
       </c>
       <c r="N8" s="1" t="s">
         <v>768</v>
       </c>
       <c r="O8" s="1" t="s">
-        <v>1463</v>
+        <v>1467</v>
       </c>
       <c r="P8" s="1" t="s">
-        <v>1410</v>
+        <v>1414</v>
       </c>
       <c r="Q8" s="1" t="s">
         <v>55</v>
@@ -12950,19 +13162,19 @@
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>1464</v>
+        <v>1468</v>
       </c>
       <c r="B9" s="1">
         <v>1</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>1449</v>
+        <v>1453</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>1465</v>
+        <v>1469</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>1466</v>
+        <v>1470</v>
       </c>
       <c r="F9" s="1">
         <v>1913</v>
@@ -13006,19 +13218,19 @@
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>1467</v>
+        <v>1471</v>
       </c>
       <c r="B10" s="1">
         <v>1</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>1449</v>
+        <v>1453</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>1468</v>
+        <v>1472</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>1469</v>
+        <v>1473</v>
       </c>
       <c r="F10" s="1">
         <v>1917</v>
@@ -13062,19 +13274,19 @@
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>1470</v>
+        <v>1474</v>
       </c>
       <c r="B11" s="1">
         <v>1</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>1457</v>
+        <v>1461</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>1471</v>
+        <v>1475</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>1472</v>
+        <v>1476</v>
       </c>
       <c r="F11" s="1">
         <v>1931</v>
@@ -13092,19 +13304,19 @@
         <v>55</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>1473</v>
+        <v>1477</v>
       </c>
       <c r="L11" s="1" t="s">
         <v>721</v>
       </c>
       <c r="M11" s="1" t="s">
-        <v>1474</v>
+        <v>1478</v>
       </c>
       <c r="N11" s="1" t="s">
         <v>654</v>
       </c>
       <c r="O11" s="1" t="s">
-        <v>1475</v>
+        <v>1479</v>
       </c>
       <c r="P11" s="1" t="s">
         <v>639</v>
@@ -13118,19 +13330,19 @@
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>1476</v>
+        <v>1480</v>
       </c>
       <c r="B12" s="1">
         <v>1</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>1449</v>
+        <v>1453</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>1477</v>
+        <v>1481</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>1478</v>
+        <v>1482</v>
       </c>
       <c r="F12" s="1">
         <v>1932</v>
@@ -13174,16 +13386,16 @@
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>1479</v>
+        <v>1483</v>
       </c>
       <c r="B13" s="1">
         <v>1</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>1449</v>
+        <v>1453</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>1480</v>
+        <v>1484</v>
       </c>
       <c r="E13" s="1" t="s">
         <v>55</v>
@@ -13230,19 +13442,19 @@
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>1481</v>
+        <v>1485</v>
       </c>
       <c r="B14" s="1">
         <v>1</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>1457</v>
+        <v>1461</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>1482</v>
+        <v>1486</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>1483</v>
+        <v>1487</v>
       </c>
       <c r="F14" s="1">
         <v>1939</v>
@@ -13260,22 +13472,22 @@
         <v>55</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>1484</v>
+        <v>1488</v>
       </c>
       <c r="L14" s="1" t="s">
         <v>721</v>
       </c>
       <c r="M14" s="1" t="s">
-        <v>1485</v>
+        <v>1489</v>
       </c>
       <c r="N14" s="1" t="s">
         <v>656</v>
       </c>
       <c r="O14" s="1" t="s">
-        <v>1486</v>
+        <v>1490</v>
       </c>
       <c r="P14" s="1" t="s">
-        <v>1487</v>
+        <v>1491</v>
       </c>
       <c r="Q14" s="1" t="s">
         <v>55</v>
@@ -13286,16 +13498,16 @@
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>1488</v>
+        <v>1492</v>
       </c>
       <c r="B15" s="1">
         <v>1</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>1443</v>
+        <v>1447</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>1489</v>
+        <v>1493</v>
       </c>
       <c r="E15" s="1" t="s">
         <v>55</v>
@@ -13342,16 +13554,16 @@
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>1490</v>
+        <v>1494</v>
       </c>
       <c r="B16" s="1">
         <v>2</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>1443</v>
+        <v>1447</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>1491</v>
+        <v>1495</v>
       </c>
       <c r="E16" s="1" t="s">
         <v>55</v>
@@ -13398,16 +13610,16 @@
     </row>
     <row r="17" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>1492</v>
+        <v>1496</v>
       </c>
       <c r="B17" s="1">
         <v>2</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>1443</v>
+        <v>1447</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>1493</v>
+        <v>1497</v>
       </c>
       <c r="E17" s="1" t="s">
         <v>55</v>
@@ -13454,16 +13666,16 @@
     </row>
     <row r="18" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>1494</v>
+        <v>1498</v>
       </c>
       <c r="B18" s="1">
         <v>2</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>1457</v>
+        <v>1461</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>1495</v>
+        <v>1499</v>
       </c>
       <c r="E18" s="1" t="s">
         <v>55</v>
@@ -13484,19 +13696,19 @@
         <v>55</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>1496</v>
+        <v>1500</v>
       </c>
       <c r="L18" s="1" t="s">
         <v>745</v>
       </c>
       <c r="M18" s="1" t="s">
-        <v>1497</v>
+        <v>1501</v>
       </c>
       <c r="N18" s="1" t="s">
         <v>654</v>
       </c>
       <c r="O18" s="1" t="s">
-        <v>1498</v>
+        <v>1502</v>
       </c>
       <c r="P18" s="1" t="s">
         <v>730</v>
@@ -13510,19 +13722,19 @@
     </row>
     <row r="19" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>1499</v>
+        <v>1503</v>
       </c>
       <c r="B19" s="1">
         <v>2</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>1457</v>
+        <v>1461</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>1500</v>
+        <v>1504</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>1501</v>
+        <v>1505</v>
       </c>
       <c r="F19" s="1">
         <v>1967</v>
@@ -13540,19 +13752,19 @@
         <v>55</v>
       </c>
       <c r="K19" s="1" t="s">
-        <v>1502</v>
+        <v>1506</v>
       </c>
       <c r="L19" s="1" t="s">
         <v>633</v>
       </c>
       <c r="M19" s="1" t="s">
-        <v>1503</v>
+        <v>1507</v>
       </c>
       <c r="N19" s="1" t="s">
-        <v>1504</v>
+        <v>1508</v>
       </c>
       <c r="O19" s="1" t="s">
-        <v>1505</v>
+        <v>1509</v>
       </c>
       <c r="P19" s="1" t="s">
         <v>656</v>
@@ -13566,19 +13778,19 @@
     </row>
     <row r="20" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>1506</v>
+        <v>1510</v>
       </c>
       <c r="B20" s="1">
         <v>2</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>1449</v>
+        <v>1453</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>1507</v>
+        <v>1511</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>1478</v>
+        <v>1482</v>
       </c>
       <c r="F20" s="1">
         <v>1968</v>
@@ -13622,16 +13834,16 @@
     </row>
     <row r="21" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>1508</v>
+        <v>1512</v>
       </c>
       <c r="B21" s="1">
         <v>2</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>1449</v>
+        <v>1453</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>1509</v>
+        <v>1513</v>
       </c>
       <c r="E21" s="1" t="s">
         <v>55</v>
@@ -13678,16 +13890,16 @@
     </row>
     <row r="22" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>1510</v>
+        <v>1514</v>
       </c>
       <c r="B22" s="1">
         <v>2</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>1443</v>
+        <v>1447</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>1511</v>
+        <v>1515</v>
       </c>
       <c r="E22" s="1" t="s">
         <v>55</v>
@@ -13734,19 +13946,19 @@
     </row>
     <row r="23" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>1512</v>
+        <v>1516</v>
       </c>
       <c r="B23" s="1">
         <v>2</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>1457</v>
+        <v>1461</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>1513</v>
+        <v>1517</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>1514</v>
+        <v>1518</v>
       </c>
       <c r="F23" s="1">
         <v>1991</v>
@@ -13764,19 +13976,19 @@
         <v>55</v>
       </c>
       <c r="K23" s="1" t="s">
-        <v>1515</v>
+        <v>1519</v>
       </c>
       <c r="L23" s="1" t="s">
         <v>656</v>
       </c>
       <c r="M23" s="1" t="s">
-        <v>1516</v>
+        <v>1520</v>
       </c>
       <c r="N23" s="1" t="s">
-        <v>1517</v>
+        <v>1521</v>
       </c>
       <c r="O23" s="1" t="s">
-        <v>1518</v>
+        <v>1522</v>
       </c>
       <c r="P23" s="1" t="s">
         <v>696</v>
@@ -13790,16 +14002,16 @@
     </row>
     <row r="24" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>1519</v>
+        <v>1523</v>
       </c>
       <c r="B24" s="1">
         <v>2</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>1457</v>
+        <v>1461</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>1520</v>
+        <v>1524</v>
       </c>
       <c r="E24" s="1" t="s">
         <v>55</v>
@@ -13820,19 +14032,19 @@
         <v>55</v>
       </c>
       <c r="K24" s="1" t="s">
-        <v>1521</v>
+        <v>1525</v>
       </c>
       <c r="L24" s="1" t="s">
-        <v>1522</v>
+        <v>1526</v>
       </c>
       <c r="M24" s="1" t="s">
-        <v>1523</v>
+        <v>1527</v>
       </c>
       <c r="N24" s="1" t="s">
-        <v>1524</v>
+        <v>1528</v>
       </c>
       <c r="O24" s="1" t="s">
-        <v>1525</v>
+        <v>1529</v>
       </c>
       <c r="P24" s="1" t="s">
         <v>724</v>
@@ -13846,19 +14058,19 @@
     </row>
     <row r="25" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>1526</v>
+        <v>1530</v>
       </c>
       <c r="B25" s="1">
         <v>2</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>1449</v>
+        <v>1453</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>1527</v>
+        <v>1531</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>1478</v>
+        <v>1482</v>
       </c>
       <c r="F25" s="1">
         <v>2006</v>
@@ -13902,16 +14114,16 @@
     </row>
     <row r="26" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>1528</v>
+        <v>1532</v>
       </c>
       <c r="B26" s="1">
         <v>2</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>1443</v>
+        <v>1447</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>1529</v>
+        <v>1533</v>
       </c>
       <c r="E26" s="1" t="s">
         <v>55</v>
@@ -13958,19 +14170,19 @@
     </row>
     <row r="27" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>1530</v>
+        <v>1534</v>
       </c>
       <c r="B27" s="1">
         <v>3</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>1449</v>
+        <v>1453</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>1531</v>
+        <v>1535</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>1532</v>
+        <v>1536</v>
       </c>
       <c r="F27" s="1">
         <v>2011</v>
@@ -14014,16 +14226,16 @@
     </row>
     <row r="28" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>1533</v>
+        <v>1537</v>
       </c>
       <c r="B28" s="1">
         <v>3</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>1457</v>
+        <v>1461</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>1534</v>
+        <v>1538</v>
       </c>
       <c r="E28" s="1" t="s">
         <v>55</v>
@@ -14044,19 +14256,19 @@
         <v>55</v>
       </c>
       <c r="K28" s="1" t="s">
-        <v>1535</v>
+        <v>1539</v>
       </c>
       <c r="L28" s="1" t="s">
         <v>656</v>
       </c>
       <c r="M28" s="1" t="s">
-        <v>1536</v>
+        <v>1540</v>
       </c>
       <c r="N28" s="1" t="s">
         <v>633</v>
       </c>
       <c r="O28" s="1" t="s">
-        <v>1537</v>
+        <v>1541</v>
       </c>
       <c r="P28" s="1" t="s">
         <v>696</v>
@@ -14070,19 +14282,19 @@
     </row>
     <row r="29" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>1538</v>
+        <v>1542</v>
       </c>
       <c r="B29" s="1">
         <v>3</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>1457</v>
+        <v>1461</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>1539</v>
+        <v>1543</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>1540</v>
+        <v>1544</v>
       </c>
       <c r="F29" s="1">
         <v>2034</v>
@@ -14100,19 +14312,19 @@
         <v>55</v>
       </c>
       <c r="K29" s="1" t="s">
-        <v>1541</v>
+        <v>1545</v>
       </c>
       <c r="L29" s="1" t="s">
-        <v>1542</v>
+        <v>1546</v>
       </c>
       <c r="M29" s="1" t="s">
-        <v>1543</v>
+        <v>1547</v>
       </c>
       <c r="N29" s="1" t="s">
         <v>859</v>
       </c>
       <c r="O29" s="1" t="s">
-        <v>1544</v>
+        <v>1548</v>
       </c>
       <c r="P29" s="1" t="s">
         <v>721</v>
@@ -14126,16 +14338,16 @@
     </row>
     <row r="30" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>1545</v>
+        <v>1549</v>
       </c>
       <c r="B30" s="1">
         <v>3</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>1443</v>
+        <v>1447</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>1546</v>
+        <v>1550</v>
       </c>
       <c r="E30" s="1" t="s">
         <v>55</v>
@@ -14182,16 +14394,16 @@
     </row>
     <row r="31" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>1547</v>
+        <v>1551</v>
       </c>
       <c r="B31" s="1">
         <v>3</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>1449</v>
+        <v>1453</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>1548</v>
+        <v>1552</v>
       </c>
       <c r="E31" s="1" t="s">
         <v>55</v>
@@ -14238,19 +14450,19 @@
     </row>
     <row r="32" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>1549</v>
+        <v>1553</v>
       </c>
       <c r="B32" s="1">
         <v>3</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>1457</v>
+        <v>1461</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>1550</v>
+        <v>1554</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>1551</v>
+        <v>1555</v>
       </c>
       <c r="F32" s="1">
         <v>2054</v>
@@ -14268,19 +14480,19 @@
         <v>55</v>
       </c>
       <c r="K32" s="1" t="s">
-        <v>1552</v>
+        <v>1556</v>
       </c>
       <c r="L32" s="1" t="s">
         <v>662</v>
       </c>
       <c r="M32" s="1" t="s">
-        <v>1553</v>
+        <v>1557</v>
       </c>
       <c r="N32" s="1" t="s">
-        <v>1554</v>
+        <v>1558</v>
       </c>
       <c r="O32" s="1" t="s">
-        <v>1555</v>
+        <v>1559</v>
       </c>
       <c r="P32" s="1" t="s">
         <v>658</v>
@@ -14294,19 +14506,19 @@
     </row>
     <row r="33" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>1556</v>
+        <v>1560</v>
       </c>
       <c r="B33" s="1">
         <v>3</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>1449</v>
+        <v>1453</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>1557</v>
+        <v>1561</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>1478</v>
+        <v>1482</v>
       </c>
       <c r="F33" s="1">
         <v>2055</v>
@@ -14350,16 +14562,16 @@
     </row>
     <row r="34" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>1558</v>
+        <v>1562</v>
       </c>
       <c r="B34" s="1">
         <v>3</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>1443</v>
+        <v>1447</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>1559</v>
+        <v>1563</v>
       </c>
       <c r="E34" s="1" t="s">
         <v>55</v>
@@ -14406,16 +14618,16 @@
     </row>
     <row r="35" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>1560</v>
+        <v>1564</v>
       </c>
       <c r="B35" s="1">
         <v>4</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>1443</v>
+        <v>1447</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>1561</v>
+        <v>1565</v>
       </c>
       <c r="E35" s="1" t="s">
         <v>55</v>
@@ -14462,19 +14674,19 @@
     </row>
     <row r="36" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>1562</v>
+        <v>1566</v>
       </c>
       <c r="B36" s="1">
         <v>4</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>1457</v>
+        <v>1461</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>1563</v>
+        <v>1567</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>1564</v>
+        <v>1568</v>
       </c>
       <c r="F36" s="1">
         <v>2077</v>
@@ -14492,19 +14704,19 @@
         <v>55</v>
       </c>
       <c r="K36" s="1" t="s">
-        <v>1565</v>
+        <v>1569</v>
       </c>
       <c r="L36" s="1" t="s">
         <v>633</v>
       </c>
       <c r="M36" s="1" t="s">
-        <v>1566</v>
+        <v>1570</v>
       </c>
       <c r="N36" s="1" t="s">
         <v>654</v>
       </c>
       <c r="O36" s="1" t="s">
-        <v>1567</v>
+        <v>1571</v>
       </c>
       <c r="P36" s="1" t="s">
         <v>745</v>
@@ -14518,16 +14730,16 @@
     </row>
     <row r="37" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>1568</v>
+        <v>1572</v>
       </c>
       <c r="B37" s="1">
         <v>4</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>1449</v>
+        <v>1453</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>1569</v>
+        <v>1573</v>
       </c>
       <c r="E37" s="1" t="s">
         <v>55</v>
@@ -14574,16 +14786,16 @@
     </row>
     <row r="38" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>1570</v>
+        <v>1574</v>
       </c>
       <c r="B38" s="1">
         <v>4</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>1443</v>
+        <v>1447</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>1571</v>
+        <v>1575</v>
       </c>
       <c r="E38" s="1" t="s">
         <v>55</v>
@@ -14630,19 +14842,19 @@
     </row>
     <row r="39" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
-        <v>1572</v>
+        <v>1576</v>
       </c>
       <c r="B39" s="1">
         <v>4</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>1457</v>
+        <v>1461</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>1573</v>
+        <v>1577</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>1574</v>
+        <v>1578</v>
       </c>
       <c r="F39" s="1">
         <v>2089</v>
@@ -14660,19 +14872,19 @@
         <v>55</v>
       </c>
       <c r="K39" s="1" t="s">
-        <v>1575</v>
+        <v>1579</v>
       </c>
       <c r="L39" s="1" t="s">
         <v>671</v>
       </c>
       <c r="M39" s="1" t="s">
-        <v>1576</v>
+        <v>1580</v>
       </c>
       <c r="N39" s="1" t="s">
         <v>861</v>
       </c>
       <c r="O39" s="1" t="s">
-        <v>1577</v>
+        <v>1581</v>
       </c>
       <c r="P39" s="1" t="s">
         <v>901</v>
@@ -14686,16 +14898,16 @@
     </row>
     <row r="40" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
-        <v>1578</v>
+        <v>1582</v>
       </c>
       <c r="B40" s="1">
         <v>4</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>1449</v>
+        <v>1453</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>1579</v>
+        <v>1583</v>
       </c>
       <c r="E40" s="1" t="s">
         <v>55</v>
@@ -14742,16 +14954,16 @@
     </row>
     <row r="41" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
-        <v>1580</v>
+        <v>1584</v>
       </c>
       <c r="B41" s="1">
         <v>4</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>1443</v>
+        <v>1447</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>1581</v>
+        <v>1585</v>
       </c>
       <c r="E41" s="1" t="s">
         <v>55</v>
@@ -14798,19 +15010,19 @@
     </row>
     <row r="42" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
-        <v>1582</v>
+        <v>1586</v>
       </c>
       <c r="B42" s="1">
         <v>4</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>1457</v>
+        <v>1461</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>1583</v>
+        <v>1587</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>1584</v>
+        <v>1588</v>
       </c>
       <c r="F42" s="1">
         <v>2106</v>
@@ -14828,22 +15040,22 @@
         <v>55</v>
       </c>
       <c r="K42" s="1" t="s">
-        <v>1585</v>
+        <v>1589</v>
       </c>
       <c r="L42" s="1" t="s">
         <v>633</v>
       </c>
       <c r="M42" s="1" t="s">
-        <v>1586</v>
+        <v>1590</v>
       </c>
       <c r="N42" s="1" t="s">
-        <v>1587</v>
+        <v>1591</v>
       </c>
       <c r="O42" s="1" t="s">
-        <v>1588</v>
+        <v>1592</v>
       </c>
       <c r="P42" s="1" t="s">
-        <v>1142</v>
+        <v>1143</v>
       </c>
       <c r="Q42" s="1" t="s">
         <v>55</v>
@@ -14854,19 +15066,19 @@
     </row>
     <row r="43" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
-        <v>1589</v>
+        <v>1593</v>
       </c>
       <c r="B43" s="1">
         <v>4</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>1457</v>
+        <v>1461</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>1590</v>
+        <v>1594</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>1591</v>
+        <v>1595</v>
       </c>
       <c r="F43" s="1">
         <v>2111</v>
@@ -14884,22 +15096,22 @@
         <v>55</v>
       </c>
       <c r="K43" s="1" t="s">
-        <v>1592</v>
+        <v>1596</v>
       </c>
       <c r="L43" s="1" t="s">
         <v>671</v>
       </c>
       <c r="M43" s="1" t="s">
-        <v>1593</v>
+        <v>1597</v>
       </c>
       <c r="N43" s="1" t="s">
-        <v>1594</v>
+        <v>1598</v>
       </c>
       <c r="O43" s="1" t="s">
-        <v>1595</v>
+        <v>1599</v>
       </c>
       <c r="P43" s="1" t="s">
-        <v>1596</v>
+        <v>1600</v>
       </c>
       <c r="Q43" s="1" t="s">
         <v>55</v>
@@ -14910,19 +15122,19 @@
     </row>
     <row r="44" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
-        <v>1597</v>
+        <v>1601</v>
       </c>
       <c r="B44" s="1">
         <v>4</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>1449</v>
+        <v>1453</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>1598</v>
+        <v>1602</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>1478</v>
+        <v>1482</v>
       </c>
       <c r="F44" s="1">
         <v>2113</v>
@@ -14966,19 +15178,19 @@
     </row>
     <row r="45" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
-        <v>1599</v>
+        <v>1603</v>
       </c>
       <c r="B45" s="1">
         <v>4</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>1457</v>
+        <v>1461</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>1600</v>
+        <v>1604</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>1601</v>
+        <v>1605</v>
       </c>
       <c r="F45" s="1">
         <v>2127</v>
@@ -14996,22 +15208,22 @@
         <v>55</v>
       </c>
       <c r="K45" s="1" t="s">
-        <v>1602</v>
+        <v>1606</v>
       </c>
       <c r="L45" s="1" t="s">
         <v>766</v>
       </c>
       <c r="M45" s="1" t="s">
-        <v>1603</v>
+        <v>1607</v>
       </c>
       <c r="N45" s="1" t="s">
         <v>760</v>
       </c>
       <c r="O45" s="1" t="s">
-        <v>1604</v>
+        <v>1608</v>
       </c>
       <c r="P45" s="1" t="s">
-        <v>1605</v>
+        <v>1609</v>
       </c>
       <c r="Q45" s="1" t="s">
         <v>55</v>
@@ -15022,19 +15234,19 @@
     </row>
     <row r="46" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
-        <v>1606</v>
+        <v>1610</v>
       </c>
       <c r="B46" s="1">
         <v>4</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>1449</v>
+        <v>1453</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>1607</v>
+        <v>1611</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>1608</v>
+        <v>1612</v>
       </c>
       <c r="F46" s="1">
         <v>2128</v>
@@ -15078,16 +15290,16 @@
     </row>
     <row r="47" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
-        <v>1609</v>
+        <v>1613</v>
       </c>
       <c r="B47" s="1">
         <v>4</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>1443</v>
+        <v>1447</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>1610</v>
+        <v>1614</v>
       </c>
       <c r="E47" s="1" t="s">
         <v>55</v>
@@ -15134,16 +15346,16 @@
     </row>
     <row r="48" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
-        <v>1611</v>
+        <v>1615</v>
       </c>
       <c r="B48" s="1">
         <v>4</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>1443</v>
+        <v>1447</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>1612</v>
+        <v>1616</v>
       </c>
       <c r="E48" s="1" t="s">
         <v>55</v>
@@ -15190,19 +15402,19 @@
     </row>
     <row r="49" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
-        <v>1613</v>
+        <v>1617</v>
       </c>
       <c r="B49" s="1">
         <v>5</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>1449</v>
+        <v>1453</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>1614</v>
+        <v>1618</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>1615</v>
+        <v>1619</v>
       </c>
       <c r="F49" s="1">
         <v>2136</v>
@@ -15246,19 +15458,19 @@
     </row>
     <row r="50" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
-        <v>1616</v>
+        <v>1620</v>
       </c>
       <c r="B50" s="1">
         <v>5</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>1457</v>
+        <v>1461</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>1617</v>
+        <v>1621</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>1618</v>
+        <v>1622</v>
       </c>
       <c r="F50" s="1">
         <v>2148</v>
@@ -15276,19 +15488,19 @@
         <v>55</v>
       </c>
       <c r="K50" s="1" t="s">
-        <v>1619</v>
+        <v>1623</v>
       </c>
       <c r="L50" s="1" t="s">
         <v>677</v>
       </c>
       <c r="M50" s="1" t="s">
-        <v>1620</v>
+        <v>1624</v>
       </c>
       <c r="N50" s="1" t="s">
         <v>633</v>
       </c>
       <c r="O50" s="1" t="s">
-        <v>1621</v>
+        <v>1625</v>
       </c>
       <c r="P50" s="1" t="s">
         <v>696</v>
@@ -15302,16 +15514,16 @@
     </row>
     <row r="51" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
-        <v>1622</v>
+        <v>1626</v>
       </c>
       <c r="B51" s="1">
         <v>5</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>1443</v>
+        <v>1447</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>1623</v>
+        <v>1627</v>
       </c>
       <c r="E51" s="1" t="s">
         <v>55</v>
@@ -15358,19 +15570,19 @@
     </row>
     <row r="52" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
-        <v>1624</v>
+        <v>1628</v>
       </c>
       <c r="B52" s="1">
         <v>5</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>1457</v>
+        <v>1461</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>1625</v>
+        <v>1629</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>1626</v>
+        <v>1630</v>
       </c>
       <c r="F52" s="1">
         <v>2153</v>
@@ -15388,19 +15600,19 @@
         <v>55</v>
       </c>
       <c r="K52" s="1" t="s">
-        <v>1627</v>
+        <v>1631</v>
       </c>
       <c r="L52" s="1" t="s">
         <v>859</v>
       </c>
       <c r="M52" s="1" t="s">
-        <v>1628</v>
+        <v>1632</v>
       </c>
       <c r="N52" s="1" t="s">
         <v>654</v>
       </c>
       <c r="O52" s="1" t="s">
-        <v>1629</v>
+        <v>1633</v>
       </c>
       <c r="P52" s="1" t="s">
         <v>656</v>
@@ -15414,16 +15626,16 @@
     </row>
     <row r="53" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
-        <v>1630</v>
+        <v>1634</v>
       </c>
       <c r="B53" s="1">
         <v>5</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>1443</v>
+        <v>1447</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>1631</v>
+        <v>1635</v>
       </c>
       <c r="E53" s="1" t="s">
         <v>55</v>
@@ -15470,19 +15682,19 @@
     </row>
     <row r="54" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
-        <v>1632</v>
+        <v>1636</v>
       </c>
       <c r="B54" s="1">
         <v>5</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>1457</v>
+        <v>1461</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>1633</v>
+        <v>1637</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>1634</v>
+        <v>1638</v>
       </c>
       <c r="F54" s="1">
         <v>2156</v>
@@ -15500,22 +15712,22 @@
         <v>55</v>
       </c>
       <c r="K54" s="1" t="s">
-        <v>1635</v>
+        <v>1639</v>
       </c>
       <c r="L54" s="1" t="s">
         <v>760</v>
       </c>
       <c r="M54" s="1" t="s">
-        <v>1636</v>
+        <v>1640</v>
       </c>
       <c r="N54" s="1" t="s">
         <v>662</v>
       </c>
       <c r="O54" s="1" t="s">
-        <v>1637</v>
+        <v>1641</v>
       </c>
       <c r="P54" s="1" t="s">
-        <v>1638</v>
+        <v>1642</v>
       </c>
       <c r="Q54" s="1" t="s">
         <v>55</v>
@@ -15526,16 +15738,16 @@
     </row>
     <row r="55" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
-        <v>1639</v>
+        <v>1643</v>
       </c>
       <c r="B55" s="1">
         <v>5</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>1457</v>
+        <v>1461</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>1640</v>
+        <v>1644</v>
       </c>
       <c r="E55" s="1" t="s">
         <v>55</v>
@@ -15556,22 +15768,22 @@
         <v>55</v>
       </c>
       <c r="K55" s="1" t="s">
-        <v>1641</v>
+        <v>1645</v>
       </c>
       <c r="L55" s="1" t="s">
         <v>859</v>
       </c>
       <c r="M55" s="1" t="s">
-        <v>1642</v>
+        <v>1646</v>
       </c>
       <c r="N55" s="1" t="s">
         <v>861</v>
       </c>
       <c r="O55" s="1" t="s">
-        <v>1463</v>
+        <v>1467</v>
       </c>
       <c r="P55" s="1" t="s">
-        <v>1410</v>
+        <v>1414</v>
       </c>
       <c r="Q55" s="1" t="s">
         <v>55</v>
@@ -15582,16 +15794,16 @@
     </row>
     <row r="56" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
-        <v>1643</v>
+        <v>1647</v>
       </c>
       <c r="B56" s="1">
         <v>5</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>1443</v>
+        <v>1447</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>1644</v>
+        <v>1648</v>
       </c>
       <c r="E56" s="1" t="s">
         <v>55</v>
@@ -15638,16 +15850,16 @@
     </row>
     <row r="57" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
-        <v>1645</v>
+        <v>1649</v>
       </c>
       <c r="B57" s="1">
         <v>5</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>1443</v>
+        <v>1447</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>1646</v>
+        <v>1650</v>
       </c>
       <c r="E57" s="1" t="s">
         <v>55</v>
@@ -15694,16 +15906,16 @@
     </row>
     <row r="58" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
-        <v>1647</v>
+        <v>1651</v>
       </c>
       <c r="B58" s="1">
         <v>5</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>1457</v>
+        <v>1461</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>1648</v>
+        <v>1652</v>
       </c>
       <c r="E58" s="1" t="s">
         <v>55</v>
@@ -15724,19 +15936,19 @@
         <v>55</v>
       </c>
       <c r="K58" s="1" t="s">
-        <v>1649</v>
+        <v>1653</v>
       </c>
       <c r="L58" s="1" t="s">
         <v>859</v>
       </c>
       <c r="M58" s="1" t="s">
-        <v>1650</v>
+        <v>1654</v>
       </c>
       <c r="N58" s="1" t="s">
-        <v>1651</v>
+        <v>1655</v>
       </c>
       <c r="O58" s="1" t="s">
-        <v>1652</v>
+        <v>1656</v>
       </c>
       <c r="P58" s="1" t="s">
         <v>639</v>
@@ -15750,16 +15962,16 @@
     </row>
     <row r="59" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
-        <v>1653</v>
+        <v>1657</v>
       </c>
       <c r="B59" s="1">
         <v>5</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>1449</v>
+        <v>1453</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>1654</v>
+        <v>1658</v>
       </c>
       <c r="E59" s="1" t="s">
         <v>55</v>
@@ -15806,16 +16018,16 @@
     </row>
     <row r="60" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
-        <v>1655</v>
+        <v>1659</v>
       </c>
       <c r="B60" s="1">
         <v>5</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>1443</v>
+        <v>1447</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>1656</v>
+        <v>1660</v>
       </c>
       <c r="E60" s="1" t="s">
         <v>55</v>
@@ -15862,16 +16074,16 @@
     </row>
     <row r="61" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
-        <v>1657</v>
+        <v>1661</v>
       </c>
       <c r="B61" s="1">
         <v>5</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>1443</v>
+        <v>1447</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>1658</v>
+        <v>1662</v>
       </c>
       <c r="E61" s="1" t="s">
         <v>55</v>
@@ -15918,16 +16130,16 @@
     </row>
     <row r="62" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
-        <v>1659</v>
+        <v>1663</v>
       </c>
       <c r="B62" s="1">
         <v>6</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>1443</v>
+        <v>1447</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>1660</v>
+        <v>1664</v>
       </c>
       <c r="E62" s="1" t="s">
         <v>55</v>
@@ -15974,19 +16186,19 @@
     </row>
     <row r="63" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
-        <v>1661</v>
+        <v>1665</v>
       </c>
       <c r="B63" s="1">
         <v>6</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>1457</v>
+        <v>1461</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>1662</v>
+        <v>1666</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>1663</v>
+        <v>1667</v>
       </c>
       <c r="F63" s="1">
         <v>2199</v>
@@ -16004,19 +16216,19 @@
         <v>55</v>
       </c>
       <c r="K63" s="1" t="s">
-        <v>1664</v>
+        <v>1668</v>
       </c>
       <c r="L63" s="1" t="s">
         <v>859</v>
       </c>
       <c r="M63" s="1" t="s">
-        <v>1665</v>
+        <v>1669</v>
       </c>
       <c r="N63" s="1" t="s">
         <v>662</v>
       </c>
       <c r="O63" s="1" t="s">
-        <v>1666</v>
+        <v>1670</v>
       </c>
       <c r="P63" s="1" t="s">
         <v>901</v>
@@ -16030,16 +16242,16 @@
     </row>
     <row r="64" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
-        <v>1667</v>
+        <v>1671</v>
       </c>
       <c r="B64" s="1">
         <v>6</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>1443</v>
+        <v>1447</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>1668</v>
+        <v>1672</v>
       </c>
       <c r="E64" s="1" t="s">
         <v>55</v>
@@ -16086,16 +16298,16 @@
     </row>
     <row r="65" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
-        <v>1669</v>
+        <v>1673</v>
       </c>
       <c r="B65" s="1">
         <v>6</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>1449</v>
+        <v>1453</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>1670</v>
+        <v>1674</v>
       </c>
       <c r="E65" s="1" t="s">
         <v>55</v>
@@ -16142,16 +16354,16 @@
     </row>
     <row r="66" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
-        <v>1671</v>
+        <v>1675</v>
       </c>
       <c r="B66" s="1">
         <v>6</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>1443</v>
+        <v>1447</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>1672</v>
+        <v>1676</v>
       </c>
       <c r="E66" s="1" t="s">
         <v>55</v>
@@ -16198,16 +16410,16 @@
     </row>
     <row r="67" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
-        <v>1673</v>
+        <v>1677</v>
       </c>
       <c r="B67" s="1">
         <v>6</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>1457</v>
+        <v>1461</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>1674</v>
+        <v>1678</v>
       </c>
       <c r="E67" s="1" t="s">
         <v>55</v>
@@ -16228,19 +16440,19 @@
         <v>55</v>
       </c>
       <c r="K67" s="1" t="s">
-        <v>1675</v>
+        <v>1679</v>
       </c>
       <c r="L67" s="1" t="s">
         <v>795</v>
       </c>
       <c r="M67" s="1" t="s">
-        <v>1676</v>
+        <v>1680</v>
       </c>
       <c r="N67" s="1" t="s">
         <v>810</v>
       </c>
       <c r="O67" s="1" t="s">
-        <v>1677</v>
+        <v>1681</v>
       </c>
       <c r="P67" s="1" t="s">
         <v>916</v>
@@ -16254,19 +16466,19 @@
     </row>
     <row r="68" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
-        <v>1678</v>
+        <v>1682</v>
       </c>
       <c r="B68" s="1">
         <v>6</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>1457</v>
+        <v>1461</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>1679</v>
+        <v>1683</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>1680</v>
+        <v>1684</v>
       </c>
       <c r="F68" s="1">
         <v>2228</v>
@@ -16284,19 +16496,19 @@
         <v>55</v>
       </c>
       <c r="K68" s="1" t="s">
-        <v>1681</v>
+        <v>1685</v>
       </c>
       <c r="L68" s="1" t="s">
         <v>760</v>
       </c>
       <c r="M68" s="1" t="s">
-        <v>1682</v>
+        <v>1686</v>
       </c>
       <c r="N68" s="1" t="s">
-        <v>1683</v>
+        <v>1687</v>
       </c>
       <c r="O68" s="1" t="s">
-        <v>1684</v>
+        <v>1688</v>
       </c>
       <c r="P68" s="1" t="s">
         <v>745</v>
@@ -16310,16 +16522,16 @@
     </row>
     <row r="69" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="s">
-        <v>1685</v>
+        <v>1689</v>
       </c>
       <c r="B69" s="1">
         <v>6</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>1443</v>
+        <v>1447</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>1686</v>
+        <v>1690</v>
       </c>
       <c r="E69" s="1" t="s">
         <v>55</v>
@@ -16366,19 +16578,19 @@
     </row>
     <row r="70" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
-        <v>1687</v>
+        <v>1691</v>
       </c>
       <c r="B70" s="1">
         <v>6</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>1457</v>
+        <v>1461</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>1688</v>
+        <v>1692</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>1689</v>
+        <v>1693</v>
       </c>
       <c r="F70" s="1">
         <v>2231</v>
@@ -16396,22 +16608,22 @@
         <v>55</v>
       </c>
       <c r="K70" s="1" t="s">
-        <v>1690</v>
+        <v>1694</v>
       </c>
       <c r="L70" s="1" t="s">
         <v>671</v>
       </c>
       <c r="M70" s="1" t="s">
-        <v>1691</v>
+        <v>1695</v>
       </c>
       <c r="N70" s="1" t="s">
-        <v>1692</v>
+        <v>1696</v>
       </c>
       <c r="O70" s="1" t="s">
-        <v>1693</v>
+        <v>1697</v>
       </c>
       <c r="P70" s="1" t="s">
-        <v>1694</v>
+        <v>1698</v>
       </c>
       <c r="Q70" s="1" t="s">
         <v>55</v>
@@ -16422,19 +16634,19 @@
     </row>
     <row r="71" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
-        <v>1695</v>
+        <v>1699</v>
       </c>
       <c r="B71" s="1">
         <v>6</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>1449</v>
+        <v>1453</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>1696</v>
+        <v>1700</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>1697</v>
+        <v>1701</v>
       </c>
       <c r="F71" s="1">
         <v>2232</v>
@@ -16478,16 +16690,16 @@
     </row>
     <row r="72" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
-        <v>1698</v>
+        <v>1702</v>
       </c>
       <c r="B72" s="1">
         <v>6</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>1443</v>
+        <v>1447</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>1699</v>
+        <v>1703</v>
       </c>
       <c r="E72" s="1" t="s">
         <v>55</v>
@@ -16534,16 +16746,16 @@
     </row>
     <row r="73" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
-        <v>1700</v>
+        <v>1704</v>
       </c>
       <c r="B73" s="1">
         <v>6</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>1443</v>
+        <v>1447</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>1701</v>
+        <v>1705</v>
       </c>
       <c r="E73" s="1" t="s">
         <v>55</v>
@@ -16590,16 +16802,16 @@
     </row>
     <row r="74" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
-        <v>1702</v>
+        <v>1706</v>
       </c>
       <c r="B74" s="1">
         <v>6</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>1457</v>
+        <v>1461</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>1703</v>
+        <v>1707</v>
       </c>
       <c r="E74" s="1" t="s">
         <v>55</v>
@@ -16620,22 +16832,22 @@
         <v>55</v>
       </c>
       <c r="K74" s="1" t="s">
-        <v>1704</v>
+        <v>1708</v>
       </c>
       <c r="L74" s="1" t="s">
         <v>760</v>
       </c>
       <c r="M74" s="1" t="s">
-        <v>1705</v>
+        <v>1709</v>
       </c>
       <c r="N74" s="1" t="s">
-        <v>1706</v>
+        <v>1710</v>
       </c>
       <c r="O74" s="1" t="s">
-        <v>1707</v>
+        <v>1711</v>
       </c>
       <c r="P74" s="1" t="s">
-        <v>1708</v>
+        <v>1712</v>
       </c>
       <c r="Q74" s="1" t="s">
         <v>55</v>
@@ -16646,16 +16858,16 @@
     </row>
     <row r="75" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="s">
-        <v>1709</v>
+        <v>1713</v>
       </c>
       <c r="B75" s="1">
         <v>6</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>1443</v>
+        <v>1447</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>1710</v>
+        <v>1714</v>
       </c>
       <c r="E75" s="1" t="s">
         <v>55</v>
@@ -16702,16 +16914,16 @@
     </row>
     <row r="76" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
-        <v>1711</v>
+        <v>1715</v>
       </c>
       <c r="B76" s="1">
         <v>6</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>1457</v>
+        <v>1461</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>1712</v>
+        <v>1716</v>
       </c>
       <c r="E76" s="1" t="s">
         <v>55</v>
@@ -16732,19 +16944,19 @@
         <v>55</v>
       </c>
       <c r="K76" s="1" t="s">
-        <v>1713</v>
+        <v>1717</v>
       </c>
       <c r="L76" s="1" t="s">
-        <v>1714</v>
+        <v>1718</v>
       </c>
       <c r="M76" s="1" t="s">
-        <v>1715</v>
+        <v>1719</v>
       </c>
       <c r="N76" s="1" t="s">
         <v>631</v>
       </c>
       <c r="O76" s="1" t="s">
-        <v>1716</v>
+        <v>1720</v>
       </c>
       <c r="P76" s="1" t="s">
         <v>696</v>
@@ -16758,16 +16970,16 @@
     </row>
     <row r="77" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A77" s="1" t="s">
-        <v>1717</v>
+        <v>1721</v>
       </c>
       <c r="B77" s="1">
         <v>6</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>1443</v>
+        <v>1447</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>1718</v>
+        <v>1722</v>
       </c>
       <c r="E77" s="1" t="s">
         <v>55</v>
@@ -16814,19 +17026,19 @@
     </row>
     <row r="78" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A78" s="1" t="s">
-        <v>1719</v>
+        <v>1723</v>
       </c>
       <c r="B78" s="1">
         <v>7</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>1449</v>
+        <v>1453</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>1720</v>
+        <v>1724</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>1478</v>
+        <v>1482</v>
       </c>
       <c r="F78" s="1">
         <v>2261</v>
@@ -16870,19 +17082,19 @@
     </row>
     <row r="79" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A79" s="1" t="s">
-        <v>1721</v>
+        <v>1725</v>
       </c>
       <c r="B79" s="1">
         <v>7</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>1457</v>
+        <v>1461</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>1722</v>
+        <v>1726</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>1723</v>
+        <v>1727</v>
       </c>
       <c r="F79" s="1">
         <v>2275</v>
@@ -16900,19 +17112,19 @@
         <v>55</v>
       </c>
       <c r="K79" s="1" t="s">
-        <v>1724</v>
+        <v>1728</v>
       </c>
       <c r="L79" s="1" t="s">
         <v>671</v>
       </c>
       <c r="M79" s="1" t="s">
-        <v>1725</v>
+        <v>1729</v>
       </c>
       <c r="N79" s="1" t="s">
-        <v>1726</v>
+        <v>1730</v>
       </c>
       <c r="O79" s="1" t="s">
-        <v>1727</v>
+        <v>1731</v>
       </c>
       <c r="P79" s="1" t="s">
         <v>901</v>
@@ -16926,16 +17138,16 @@
     </row>
     <row r="80" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A80" s="1" t="s">
-        <v>1728</v>
+        <v>1732</v>
       </c>
       <c r="B80" s="1">
         <v>7</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>1457</v>
+        <v>1461</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>1729</v>
+        <v>1733</v>
       </c>
       <c r="E80" s="1" t="s">
         <v>55</v>
@@ -16956,19 +17168,19 @@
         <v>55</v>
       </c>
       <c r="K80" s="1" t="s">
-        <v>1730</v>
+        <v>1734</v>
       </c>
       <c r="L80" s="1" t="s">
-        <v>1731</v>
+        <v>1735</v>
       </c>
       <c r="M80" s="1" t="s">
-        <v>1732</v>
+        <v>1736</v>
       </c>
       <c r="N80" s="1" t="s">
         <v>760</v>
       </c>
       <c r="O80" s="1" t="s">
-        <v>1733</v>
+        <v>1737</v>
       </c>
       <c r="P80" s="1" t="s">
         <v>916</v>
@@ -16982,16 +17194,16 @@
     </row>
     <row r="81" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="s">
-        <v>1734</v>
+        <v>1738</v>
       </c>
       <c r="B81" s="1">
         <v>7</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>1443</v>
+        <v>1447</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>1735</v>
+        <v>1739</v>
       </c>
       <c r="E81" s="1" t="s">
         <v>55</v>
@@ -17038,16 +17250,16 @@
     </row>
     <row r="82" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A82" s="1" t="s">
-        <v>1736</v>
+        <v>1740</v>
       </c>
       <c r="B82" s="1">
         <v>7</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>1457</v>
+        <v>1461</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>1737</v>
+        <v>1741</v>
       </c>
       <c r="E82" s="1" t="s">
         <v>55</v>
@@ -17068,19 +17280,19 @@
         <v>55</v>
       </c>
       <c r="K82" s="1" t="s">
-        <v>1738</v>
+        <v>1742</v>
       </c>
       <c r="L82" s="1" t="s">
-        <v>1739</v>
+        <v>1743</v>
       </c>
       <c r="M82" s="1" t="s">
-        <v>1740</v>
+        <v>1744</v>
       </c>
       <c r="N82" s="1" t="s">
-        <v>1741</v>
+        <v>1745</v>
       </c>
       <c r="O82" s="1" t="s">
-        <v>1742</v>
+        <v>1746</v>
       </c>
       <c r="P82" s="1" t="s">
         <v>662</v>
@@ -17094,16 +17306,16 @@
     </row>
     <row r="83" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A83" s="1" t="s">
-        <v>1743</v>
+        <v>1747</v>
       </c>
       <c r="B83" s="1">
         <v>7</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>1457</v>
+        <v>1461</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>1744</v>
+        <v>1748</v>
       </c>
       <c r="E83" s="1" t="s">
         <v>55</v>
@@ -17124,22 +17336,22 @@
         <v>55</v>
       </c>
       <c r="K83" s="1" t="s">
-        <v>1745</v>
+        <v>1749</v>
       </c>
       <c r="L83" s="1" t="s">
         <v>760</v>
       </c>
       <c r="M83" s="1" t="s">
-        <v>1746</v>
+        <v>1750</v>
       </c>
       <c r="N83" s="1" t="s">
         <v>643</v>
       </c>
       <c r="O83" s="1" t="s">
-        <v>1747</v>
+        <v>1751</v>
       </c>
       <c r="P83" s="1" t="s">
-        <v>1748</v>
+        <v>1752</v>
       </c>
       <c r="Q83" s="1" t="s">
         <v>55</v>
@@ -17150,16 +17362,16 @@
     </row>
     <row r="84" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A84" s="1" t="s">
-        <v>1749</v>
+        <v>1753</v>
       </c>
       <c r="B84" s="1">
         <v>7</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>1443</v>
+        <v>1447</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>1750</v>
+        <v>1754</v>
       </c>
       <c r="E84" s="1" t="s">
         <v>55</v>
@@ -17206,16 +17418,16 @@
     </row>
     <row r="85" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A85" s="1" t="s">
-        <v>1751</v>
+        <v>1755</v>
       </c>
       <c r="B85" s="1">
         <v>7</v>
       </c>
       <c r="C85" s="1" t="s">
-        <v>1443</v>
+        <v>1447</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>1752</v>
+        <v>1756</v>
       </c>
       <c r="E85" s="1" t="s">
         <v>55</v>
@@ -17262,16 +17474,16 @@
     </row>
     <row r="86" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A86" s="1" t="s">
-        <v>1753</v>
+        <v>1757</v>
       </c>
       <c r="B86" s="1">
         <v>7</v>
       </c>
       <c r="C86" s="1" t="s">
-        <v>1457</v>
+        <v>1461</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>1754</v>
+        <v>1758</v>
       </c>
       <c r="E86" s="1" t="s">
         <v>55</v>
@@ -17292,22 +17504,22 @@
         <v>55</v>
       </c>
       <c r="K86" s="1" t="s">
-        <v>1755</v>
+        <v>1759</v>
       </c>
       <c r="L86" s="1" t="s">
         <v>633</v>
       </c>
       <c r="M86" s="1" t="s">
-        <v>1756</v>
+        <v>1760</v>
       </c>
       <c r="N86" s="1" t="s">
-        <v>1757</v>
+        <v>1761</v>
       </c>
       <c r="O86" s="1" t="s">
-        <v>1758</v>
+        <v>1762</v>
       </c>
       <c r="P86" s="1" t="s">
-        <v>1759</v>
+        <v>1763</v>
       </c>
       <c r="Q86" s="1" t="s">
         <v>55</v>
@@ -17318,16 +17530,16 @@
     </row>
     <row r="87" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A87" s="1" t="s">
-        <v>1760</v>
+        <v>1764</v>
       </c>
       <c r="B87" s="1">
         <v>7</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>1443</v>
+        <v>1447</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>1761</v>
+        <v>1765</v>
       </c>
       <c r="E87" s="1" t="s">
         <v>55</v>
@@ -17374,16 +17586,16 @@
     </row>
     <row r="88" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A88" s="1" t="s">
-        <v>1762</v>
+        <v>1766</v>
       </c>
       <c r="B88" s="1">
         <v>7</v>
       </c>
       <c r="C88" s="1" t="s">
-        <v>1449</v>
+        <v>1453</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>1763</v>
+        <v>1767</v>
       </c>
       <c r="E88" s="1" t="s">
         <v>55</v>
@@ -17430,19 +17642,19 @@
     </row>
     <row r="89" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A89" s="1" t="s">
-        <v>1764</v>
+        <v>1768</v>
       </c>
       <c r="B89" s="1">
         <v>7</v>
       </c>
       <c r="C89" s="1" t="s">
-        <v>1457</v>
+        <v>1461</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>1765</v>
+        <v>1769</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>1766</v>
+        <v>1770</v>
       </c>
       <c r="F89" s="1">
         <v>2304</v>
@@ -17460,22 +17672,22 @@
         <v>55</v>
       </c>
       <c r="K89" s="1" t="s">
-        <v>1767</v>
+        <v>1771</v>
       </c>
       <c r="L89" s="1" t="s">
-        <v>1768</v>
+        <v>1772</v>
       </c>
       <c r="M89" s="1" t="s">
-        <v>1769</v>
+        <v>1773</v>
       </c>
       <c r="N89" s="1" t="s">
-        <v>1770</v>
+        <v>1774</v>
       </c>
       <c r="O89" s="1" t="s">
-        <v>1771</v>
+        <v>1775</v>
       </c>
       <c r="P89" s="1" t="s">
-        <v>1772</v>
+        <v>1776</v>
       </c>
       <c r="Q89" s="1" t="s">
         <v>55</v>
@@ -17486,19 +17698,19 @@
     </row>
     <row r="90" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A90" s="1" t="s">
-        <v>1773</v>
+        <v>1777</v>
       </c>
       <c r="B90" s="1">
         <v>7</v>
       </c>
       <c r="C90" s="1" t="s">
-        <v>1449</v>
+        <v>1453</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>1774</v>
+        <v>1778</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>1775</v>
+        <v>1779</v>
       </c>
       <c r="F90" s="1">
         <v>2308</v>
@@ -17542,19 +17754,19 @@
     </row>
     <row r="91" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
-        <v>1776</v>
+        <v>1780</v>
       </c>
       <c r="B91" s="1">
         <v>7</v>
       </c>
       <c r="C91" s="1" t="s">
-        <v>1443</v>
+        <v>1447</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>1777</v>
+        <v>1781</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>1778</v>
+        <v>1782</v>
       </c>
       <c r="F91" s="1">
         <v>2310</v>
@@ -17615,7 +17827,7 @@
   <sheetData>
     <row r="1" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>1779</v>
+        <v>1783</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
@@ -17623,10 +17835,10 @@
     </row>
     <row r="2" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
-        <v>1780</v>
+        <v>1784</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>1781</v>
+        <v>1785</v>
       </c>
       <c r="C2" s="5" t="s">
         <v>929</v>
@@ -17640,13 +17852,13 @@
         <v>1</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>1782</v>
+        <v>1786</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>1783</v>
+        <v>1787</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>1784</v>
+        <v>1788</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -17654,13 +17866,13 @@
         <v>2</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>1785</v>
+        <v>1789</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>1786</v>
+        <v>1790</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>1787</v>
+        <v>1791</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -17668,13 +17880,13 @@
         <v>3</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>1788</v>
+        <v>1792</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>1789</v>
+        <v>1793</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>1790</v>
+        <v>1794</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -17682,13 +17894,13 @@
         <v>4</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>1791</v>
+        <v>1795</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>1792</v>
+        <v>1796</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>1793</v>
+        <v>1797</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -17696,13 +17908,13 @@
         <v>5</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>1794</v>
+        <v>1798</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>1795</v>
+        <v>1799</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>1796</v>
+        <v>1800</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -17710,13 +17922,13 @@
         <v>6</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>1797</v>
+        <v>1801</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>1798</v>
+        <v>1802</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>1799</v>
+        <v>1803</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -17724,13 +17936,13 @@
         <v>7</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>1800</v>
+        <v>1804</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>1801</v>
+        <v>1805</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>1802</v>
+        <v>1806</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -17738,13 +17950,13 @@
         <v>8</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>1803</v>
+        <v>1807</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>1804</v>
+        <v>1808</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>1805</v>
+        <v>1809</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -17752,13 +17964,13 @@
         <v>9</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>1806</v>
+        <v>1810</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>1807</v>
+        <v>1811</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>1808</v>
+        <v>1812</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -17766,13 +17978,13 @@
         <v>10</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>1809</v>
+        <v>1813</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>1810</v>
+        <v>1814</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>1811</v>
+        <v>1815</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -17780,13 +17992,13 @@
         <v>11</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>1812</v>
+        <v>1816</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>1813</v>
+        <v>1817</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>1814</v>
+        <v>1818</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -17794,13 +18006,13 @@
         <v>12</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>1815</v>
+        <v>1819</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>1816</v>
+        <v>1820</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>1817</v>
+        <v>1821</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -17808,13 +18020,13 @@
         <v>13</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>1818</v>
+        <v>1822</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>1819</v>
+        <v>1823</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>1820</v>
+        <v>1824</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -17822,13 +18034,13 @@
         <v>14</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>1821</v>
+        <v>1825</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>1822</v>
+        <v>1826</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>1823</v>
+        <v>1827</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
@@ -17836,13 +18048,13 @@
         <v>15</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>1824</v>
+        <v>1828</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>1825</v>
+        <v>1829</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>1826</v>
+        <v>1830</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
@@ -17850,13 +18062,13 @@
         <v>16</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>1827</v>
+        <v>1831</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>1828</v>
+        <v>1832</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>1829</v>
+        <v>1833</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -17864,13 +18076,13 @@
         <v>17</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>1830</v>
+        <v>1834</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>1831</v>
+        <v>1835</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>1832</v>
+        <v>1836</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -17878,13 +18090,13 @@
         <v>18</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>1833</v>
+        <v>1837</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>1834</v>
+        <v>1838</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>1835</v>
+        <v>1839</v>
       </c>
     </row>
   </sheetData>
@@ -17906,7 +18118,7 @@
   <sheetData>
     <row r="1" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>1836</v>
+        <v>1840</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
@@ -17921,10 +18133,10 @@
         <v>298</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>1837</v>
+        <v>1841</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>1838</v>
+        <v>1842</v>
       </c>
       <c r="E2" s="5" t="s">
         <v>301</v>
@@ -17932,33 +18144,33 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>1839</v>
+        <v>1843</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>1840</v>
+        <v>1844</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>1841</v>
+        <v>1845</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>1842</v>
+        <v>1846</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>1843</v>
+        <v>1847</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>1844</v>
+        <v>1848</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>1845</v>
+        <v>1849</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>1846</v>
+        <v>1850</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>1847</v>
+        <v>1851</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>55</v>
@@ -17966,53 +18178,53 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>1848</v>
+        <v>1852</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>1849</v>
+        <v>1853</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>1850</v>
+        <v>1854</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>1851</v>
+        <v>1855</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>1852</v>
+        <v>1856</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>1853</v>
+        <v>1857</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>1854</v>
+        <v>1858</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>1855</v>
+        <v>1859</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>1856</v>
+        <v>1860</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>1857</v>
+        <v>1861</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>1858</v>
+        <v>1862</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>1859</v>
+        <v>1863</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>1860</v>
+        <v>1864</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>1861</v>
+        <v>1865</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>1862</v>
+        <v>1866</v>
       </c>
     </row>
   </sheetData>

--- a/content.xlsx
+++ b/content.xlsx
@@ -8012,7 +8012,7 @@
     <t>ทวิภพ</t>
   </si>
   <si>
-    <t>บุญปัจจุบัน ≥ 8000 ประการ (REINCARNATE_THRESHOLD)</t>
+    <t>บุญปัจจุบัน ≥ 8500 ประการ (REINCARNATE_THRESHOLD)</t>
   </si>
   <si>
     <t>ย้อนเวลากลับไปเริ่มชาติที่ 1 ปี 1887 ใหม่ทั้งหมด</t>
